--- a/2. Components/2.1. Cloud Component/2.1.1. Autonomous_Database/3. autonomous_db_owner (wip)/4. dml/1. skill_area [13-17,5]/15. technology.xlsx
+++ b/2. Components/2.1. Cloud Component/2.1.1. Autonomous_Database/3. autonomous_db_owner (wip)/4. dml/1. skill_area [13-17,5]/15. technology.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github_projects\Tech_Hunt_Engine\2. Components\2.1. Cloud Component\2.1.1. Autonomous_Database\3. autonomous_db_owner (wip)\4. dml\1. skill_area [13-17,5]\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44236A16-AED6-410E-B1C9-98CA4DDC457B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5DBBB51-3E7D-4944-A928-931C6482736F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="60" yWindow="0" windowWidth="15840" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="technology" sheetId="2" r:id="rId1"/>
@@ -148,7 +148,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3772" uniqueCount="2961">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3772" uniqueCount="2960">
   <si>
     <t>name</t>
   </si>
@@ -7547,9 +7547,6 @@
   </si>
   <si>
     <t>strman-java</t>
-  </si>
-  <si>
-    <t>2020‑01‑0</t>
   </si>
   <si>
     <t>Shekhar Gulati</t>
@@ -9139,7 +9136,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -9189,9 +9186,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -9485,7 +9479,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41043218-9C94-410C-9ADE-FF0FB1887CD8}">
-  <dimension ref="A1:G1347"/>
+  <dimension ref="A1:F715"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.7109375" bestFit="1" customWidth="1"/>
@@ -10776,7 +10770,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="65" spans="1:7" s="4" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" s="4" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A65" s="5" t="s">
         <v>480</v>
       </c>
@@ -10796,7 +10790,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="66" spans="1:7" s="4" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6" s="4" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A66" s="5" t="s">
         <v>481</v>
       </c>
@@ -10816,7 +10810,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="67" spans="1:7" s="4" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6" s="4" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A67" s="5" t="s">
         <v>482</v>
       </c>
@@ -10836,7 +10830,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="68" spans="1:7" s="4" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6" s="4" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A68" s="5" t="s">
         <v>512</v>
       </c>
@@ -10856,7 +10850,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="69" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="5" t="s">
         <v>513</v>
       </c>
@@ -10869,13 +10863,12 @@
       <c r="D69" s="8" t="s">
         <v>526</v>
       </c>
-      <c r="E69" s="21"/>
+      <c r="E69" s="20"/>
       <c r="F69" s="5">
         <v>5</v>
       </c>
-      <c r="G69" s="20"/>
-    </row>
-    <row r="70" spans="1:7" s="4" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    </row>
+    <row r="70" spans="1:6" s="4" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A70" s="5" t="s">
         <v>514</v>
       </c>
@@ -10895,7 +10888,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="71" spans="1:7" s="4" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" s="4" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A71" s="5" t="s">
         <v>515</v>
       </c>
@@ -10915,7 +10908,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="72" spans="1:7" s="4" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" s="4" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A72" s="5" t="s">
         <v>528</v>
       </c>
@@ -10935,7 +10928,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="73" spans="1:7" s="4" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:6" s="4" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A73" s="5" t="s">
         <v>516</v>
       </c>
@@ -10955,7 +10948,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="74" spans="1:7" s="4" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:6" s="4" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A74" s="5" t="s">
         <v>517</v>
       </c>
@@ -10975,7 +10968,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="75" spans="1:7" s="4" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:6" s="4" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A75" s="5" t="s">
         <v>518</v>
       </c>
@@ -10995,7 +10988,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="76" spans="1:7" s="4" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:6" s="4" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A76" s="5" t="s">
         <v>519</v>
       </c>
@@ -11015,7 +11008,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="77" spans="1:7" s="4" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:6" s="4" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A77" s="5" t="s">
         <v>554</v>
       </c>
@@ -11035,7 +11028,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="78" spans="1:7" s="4" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6" s="4" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A78" s="5" t="s">
         <v>555</v>
       </c>
@@ -11055,7 +11048,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="79" spans="1:7" s="4" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:6" s="4" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A79" s="5" t="s">
         <v>556</v>
       </c>
@@ -11075,7 +11068,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="80" spans="1:7" s="4" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:6" s="4" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A80" s="5" t="s">
         <v>557</v>
       </c>
@@ -21140,16 +21133,16 @@
         <v>2465</v>
       </c>
       <c r="B583" s="6" t="s">
+        <v>391</v>
+      </c>
+      <c r="C583" s="7" t="s">
         <v>2466</v>
       </c>
-      <c r="C583" s="7" t="s">
+      <c r="D583" s="17" t="s">
         <v>2467</v>
       </c>
-      <c r="D583" s="17" t="s">
+      <c r="E583" s="7" t="s">
         <v>2468</v>
-      </c>
-      <c r="E583" s="7" t="s">
-        <v>2469</v>
       </c>
       <c r="F583" s="5">
         <v>72</v>
@@ -21157,19 +21150,19 @@
     </row>
     <row r="584" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A584" s="5" t="s">
-        <v>2470</v>
+        <v>2469</v>
       </c>
       <c r="B584" s="6" t="s">
         <v>921</v>
       </c>
       <c r="C584" s="7" t="s">
+        <v>2470</v>
+      </c>
+      <c r="D584" s="17" t="s">
         <v>2471</v>
       </c>
-      <c r="D584" s="17" t="s">
+      <c r="E584" s="7" t="s">
         <v>2472</v>
-      </c>
-      <c r="E584" s="7" t="s">
-        <v>2473</v>
       </c>
       <c r="F584" s="5">
         <v>72</v>
@@ -21177,19 +21170,19 @@
     </row>
     <row r="585" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A585" s="5" t="s">
+        <v>2473</v>
+      </c>
+      <c r="B585" s="6" t="s">
         <v>2474</v>
       </c>
-      <c r="B585" s="6" t="s">
+      <c r="C585" s="7" t="s">
         <v>2475</v>
       </c>
-      <c r="C585" s="7" t="s">
+      <c r="D585" s="17" t="s">
         <v>2476</v>
       </c>
-      <c r="D585" s="17" t="s">
+      <c r="E585" s="7" t="s">
         <v>2477</v>
-      </c>
-      <c r="E585" s="7" t="s">
-        <v>2478</v>
       </c>
       <c r="F585" s="5">
         <v>72</v>
@@ -21197,19 +21190,19 @@
     </row>
     <row r="586" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A586" s="5" t="s">
-        <v>2479</v>
+        <v>2478</v>
       </c>
       <c r="B586" s="6" t="s">
         <v>1133</v>
       </c>
       <c r="C586" s="7" t="s">
+        <v>2479</v>
+      </c>
+      <c r="D586" s="17" t="s">
         <v>2480</v>
       </c>
-      <c r="D586" s="17" t="s">
+      <c r="E586" s="7" t="s">
         <v>2481</v>
-      </c>
-      <c r="E586" s="7" t="s">
-        <v>2482</v>
       </c>
       <c r="F586" s="5">
         <v>72</v>
@@ -21217,19 +21210,19 @@
     </row>
     <row r="587" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A587" s="5" t="s">
-        <v>2483</v>
+        <v>2482</v>
       </c>
       <c r="B587" s="6" t="s">
         <v>391</v>
       </c>
       <c r="C587" s="7" t="s">
+        <v>2483</v>
+      </c>
+      <c r="D587" s="17" t="s">
+        <v>2488</v>
+      </c>
+      <c r="E587" s="7" t="s">
         <v>2484</v>
-      </c>
-      <c r="D587" s="17" t="s">
-        <v>2489</v>
-      </c>
-      <c r="E587" s="7" t="s">
-        <v>2485</v>
       </c>
       <c r="F587" s="5">
         <v>72</v>
@@ -21237,19 +21230,19 @@
     </row>
     <row r="588" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A588" s="5" t="s">
-        <v>2486</v>
+        <v>2485</v>
       </c>
       <c r="B588" s="6" t="s">
         <v>1140</v>
       </c>
       <c r="C588" s="7" t="s">
+        <v>2486</v>
+      </c>
+      <c r="D588" s="17" t="s">
         <v>2487</v>
       </c>
-      <c r="D588" s="17" t="s">
-        <v>2488</v>
-      </c>
       <c r="E588" s="7" t="s">
-        <v>2490</v>
+        <v>2489</v>
       </c>
       <c r="F588" s="5">
         <v>72</v>
@@ -21257,19 +21250,19 @@
     </row>
     <row r="589" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A589" s="5" t="s">
-        <v>2491</v>
+        <v>2490</v>
       </c>
       <c r="B589" s="6" t="s">
         <v>1133</v>
       </c>
       <c r="C589" s="7" t="s">
-        <v>2492</v>
+        <v>2491</v>
       </c>
       <c r="D589" s="17" t="s">
         <v>896</v>
       </c>
       <c r="E589" s="7" t="s">
-        <v>2493</v>
+        <v>2492</v>
       </c>
       <c r="F589" s="5">
         <v>73</v>
@@ -21277,7 +21270,7 @@
     </row>
     <row r="590" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A590" s="5" t="s">
-        <v>2494</v>
+        <v>2493</v>
       </c>
       <c r="B590" s="6" t="s">
         <v>921</v>
@@ -21286,10 +21279,10 @@
         <v>2445</v>
       </c>
       <c r="D590" s="17" t="s">
+        <v>2494</v>
+      </c>
+      <c r="E590" s="7" t="s">
         <v>2495</v>
-      </c>
-      <c r="E590" s="7" t="s">
-        <v>2496</v>
       </c>
       <c r="F590" s="5">
         <v>73</v>
@@ -21297,7 +21290,7 @@
     </row>
     <row r="591" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A591" s="5" t="s">
-        <v>2497</v>
+        <v>2496</v>
       </c>
       <c r="B591" s="6" t="s">
         <v>287</v>
@@ -21309,7 +21302,7 @@
         <v>892</v>
       </c>
       <c r="E591" s="7" t="s">
-        <v>2498</v>
+        <v>2497</v>
       </c>
       <c r="F591" s="5">
         <v>73</v>
@@ -21317,19 +21310,19 @@
     </row>
     <row r="592" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A592" s="5" t="s">
-        <v>2499</v>
+        <v>2498</v>
       </c>
       <c r="B592" s="6" t="s">
         <v>2164</v>
       </c>
       <c r="C592" s="7" t="s">
+        <v>2499</v>
+      </c>
+      <c r="D592" s="17" t="s">
         <v>2500</v>
       </c>
-      <c r="D592" s="17" t="s">
+      <c r="E592" s="7" t="s">
         <v>2501</v>
-      </c>
-      <c r="E592" s="7" t="s">
-        <v>2502</v>
       </c>
       <c r="F592" s="5">
         <v>73</v>
@@ -21337,19 +21330,19 @@
     </row>
     <row r="593" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A593" s="5" t="s">
-        <v>2503</v>
+        <v>2502</v>
       </c>
       <c r="B593" s="6" t="s">
         <v>845</v>
       </c>
       <c r="C593" s="7" t="s">
+        <v>2503</v>
+      </c>
+      <c r="D593" s="17" t="s">
         <v>2504</v>
       </c>
-      <c r="D593" s="17" t="s">
+      <c r="E593" s="7" t="s">
         <v>2505</v>
-      </c>
-      <c r="E593" s="7" t="s">
-        <v>2506</v>
       </c>
       <c r="F593" s="5">
         <v>73</v>
@@ -21357,19 +21350,19 @@
     </row>
     <row r="594" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A594" s="5" t="s">
-        <v>2507</v>
+        <v>2506</v>
       </c>
       <c r="B594" s="6" t="s">
         <v>1150</v>
       </c>
       <c r="C594" s="7" t="s">
+        <v>2507</v>
+      </c>
+      <c r="D594" s="17" t="s">
         <v>2508</v>
       </c>
-      <c r="D594" s="17" t="s">
+      <c r="E594" s="7" t="s">
         <v>2509</v>
-      </c>
-      <c r="E594" s="7" t="s">
-        <v>2510</v>
       </c>
       <c r="F594" s="5">
         <v>73</v>
@@ -21377,19 +21370,19 @@
     </row>
     <row r="595" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A595" s="5" t="s">
-        <v>2511</v>
+        <v>2510</v>
       </c>
       <c r="B595" s="6" t="s">
         <v>287</v>
       </c>
       <c r="C595" s="7" t="s">
+        <v>2511</v>
+      </c>
+      <c r="D595" s="17" t="s">
         <v>2512</v>
       </c>
-      <c r="D595" s="17" t="s">
+      <c r="E595" s="7" t="s">
         <v>2513</v>
-      </c>
-      <c r="E595" s="7" t="s">
-        <v>2514</v>
       </c>
       <c r="F595" s="5">
         <v>73</v>
@@ -21397,7 +21390,7 @@
     </row>
     <row r="596" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A596" s="5" t="s">
-        <v>2515</v>
+        <v>2514</v>
       </c>
       <c r="B596" s="6" t="s">
         <v>391</v>
@@ -21406,10 +21399,10 @@
         <v>252</v>
       </c>
       <c r="D596" s="17" t="s">
+        <v>2515</v>
+      </c>
+      <c r="E596" s="7" t="s">
         <v>2516</v>
-      </c>
-      <c r="E596" s="7" t="s">
-        <v>2517</v>
       </c>
       <c r="F596" s="5">
         <v>73</v>
@@ -21417,19 +21410,19 @@
     </row>
     <row r="597" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A597" s="5" t="s">
-        <v>2518</v>
+        <v>2517</v>
       </c>
       <c r="B597" s="6" t="s">
         <v>840</v>
       </c>
       <c r="C597" s="7" t="s">
+        <v>2518</v>
+      </c>
+      <c r="D597" s="17" t="s">
         <v>2519</v>
       </c>
-      <c r="D597" s="17" t="s">
+      <c r="E597" s="7" t="s">
         <v>2520</v>
-      </c>
-      <c r="E597" s="7" t="s">
-        <v>2521</v>
       </c>
       <c r="F597" s="5">
         <v>73</v>
@@ -21437,19 +21430,19 @@
     </row>
     <row r="598" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A598" s="5" t="s">
-        <v>2522</v>
+        <v>2521</v>
       </c>
       <c r="B598" s="6" t="s">
         <v>1150</v>
       </c>
       <c r="C598" s="7" t="s">
+        <v>2522</v>
+      </c>
+      <c r="D598" s="17" t="s">
         <v>2523</v>
       </c>
-      <c r="D598" s="17" t="s">
+      <c r="E598" s="7" t="s">
         <v>2524</v>
-      </c>
-      <c r="E598" s="7" t="s">
-        <v>2525</v>
       </c>
       <c r="F598" s="5">
         <v>74</v>
@@ -21457,19 +21450,19 @@
     </row>
     <row r="599" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A599" s="5" t="s">
-        <v>2526</v>
+        <v>2525</v>
       </c>
       <c r="B599" s="6" t="s">
         <v>840</v>
       </c>
       <c r="C599" s="7" t="s">
+        <v>2526</v>
+      </c>
+      <c r="D599" s="17" t="s">
         <v>2527</v>
       </c>
-      <c r="D599" s="17" t="s">
+      <c r="E599" s="7" t="s">
         <v>2528</v>
-      </c>
-      <c r="E599" s="7" t="s">
-        <v>2529</v>
       </c>
       <c r="F599" s="5">
         <v>74</v>
@@ -21477,7 +21470,7 @@
     </row>
     <row r="600" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A600" s="5" t="s">
-        <v>2530</v>
+        <v>2529</v>
       </c>
       <c r="B600" s="6" t="s">
         <v>287</v>
@@ -21486,10 +21479,10 @@
         <v>366</v>
       </c>
       <c r="D600" s="17" t="s">
+        <v>2530</v>
+      </c>
+      <c r="E600" s="7" t="s">
         <v>2531</v>
-      </c>
-      <c r="E600" s="7" t="s">
-        <v>2532</v>
       </c>
       <c r="F600" s="5">
         <v>74</v>
@@ -21497,19 +21490,19 @@
     </row>
     <row r="601" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A601" s="5" t="s">
-        <v>2533</v>
+        <v>2532</v>
       </c>
       <c r="B601" s="6" t="s">
         <v>287</v>
       </c>
       <c r="C601" s="7" t="s">
+        <v>2533</v>
+      </c>
+      <c r="D601" s="17" t="s">
         <v>2534</v>
       </c>
-      <c r="D601" s="17" t="s">
+      <c r="E601" s="7" t="s">
         <v>2535</v>
-      </c>
-      <c r="E601" s="7" t="s">
-        <v>2536</v>
       </c>
       <c r="F601" s="5">
         <v>74</v>
@@ -21517,19 +21510,19 @@
     </row>
     <row r="602" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A602" s="5" t="s">
-        <v>2537</v>
+        <v>2536</v>
       </c>
       <c r="B602" s="6" t="s">
         <v>990</v>
       </c>
       <c r="C602" s="7" t="s">
+        <v>2537</v>
+      </c>
+      <c r="D602" s="17" t="s">
         <v>2538</v>
       </c>
-      <c r="D602" s="17" t="s">
+      <c r="E602" s="7" t="s">
         <v>2539</v>
-      </c>
-      <c r="E602" s="7" t="s">
-        <v>2540</v>
       </c>
       <c r="F602" s="5">
         <v>74</v>
@@ -21537,19 +21530,19 @@
     </row>
     <row r="603" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A603" s="5" t="s">
-        <v>2541</v>
+        <v>2540</v>
       </c>
       <c r="B603" s="6" t="s">
         <v>1020</v>
       </c>
       <c r="C603" s="7" t="s">
+        <v>2541</v>
+      </c>
+      <c r="D603" s="17" t="s">
         <v>2542</v>
       </c>
-      <c r="D603" s="17" t="s">
+      <c r="E603" s="7" t="s">
         <v>2543</v>
-      </c>
-      <c r="E603" s="7" t="s">
-        <v>2544</v>
       </c>
       <c r="F603" s="5">
         <v>74</v>
@@ -21557,19 +21550,19 @@
     </row>
     <row r="604" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A604" s="5" t="s">
-        <v>2545</v>
+        <v>2544</v>
       </c>
       <c r="B604" s="6" t="s">
         <v>1150</v>
       </c>
       <c r="C604" s="7" t="s">
+        <v>2545</v>
+      </c>
+      <c r="D604" s="17" t="s">
         <v>2546</v>
       </c>
-      <c r="D604" s="17" t="s">
+      <c r="E604" s="7" t="s">
         <v>2547</v>
-      </c>
-      <c r="E604" s="7" t="s">
-        <v>2548</v>
       </c>
       <c r="F604" s="5">
         <v>74</v>
@@ -21577,19 +21570,19 @@
     </row>
     <row r="605" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A605" s="5" t="s">
-        <v>2549</v>
+        <v>2548</v>
       </c>
       <c r="B605" s="6" t="s">
         <v>1279</v>
       </c>
       <c r="C605" s="7" t="s">
+        <v>2549</v>
+      </c>
+      <c r="D605" s="17" t="s">
         <v>2550</v>
       </c>
-      <c r="D605" s="17" t="s">
+      <c r="E605" s="7" t="s">
         <v>2551</v>
-      </c>
-      <c r="E605" s="7" t="s">
-        <v>2552</v>
       </c>
       <c r="F605" s="5">
         <v>74</v>
@@ -21597,19 +21590,19 @@
     </row>
     <row r="606" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A606" s="5" t="s">
-        <v>2553</v>
+        <v>2552</v>
       </c>
       <c r="B606" s="6" t="s">
         <v>840</v>
       </c>
       <c r="C606" s="7" t="s">
+        <v>2553</v>
+      </c>
+      <c r="D606" s="17" t="s">
         <v>2554</v>
       </c>
-      <c r="D606" s="17" t="s">
+      <c r="E606" s="7" t="s">
         <v>2555</v>
-      </c>
-      <c r="E606" s="7" t="s">
-        <v>2556</v>
       </c>
       <c r="F606" s="5">
         <v>74</v>
@@ -21617,19 +21610,19 @@
     </row>
     <row r="607" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A607" s="5" t="s">
-        <v>2557</v>
+        <v>2556</v>
       </c>
       <c r="B607" s="6" t="s">
         <v>921</v>
       </c>
       <c r="C607" s="7" t="s">
+        <v>2557</v>
+      </c>
+      <c r="D607" s="17" t="s">
         <v>2558</v>
       </c>
-      <c r="D607" s="17" t="s">
+      <c r="E607" s="7" t="s">
         <v>2559</v>
-      </c>
-      <c r="E607" s="7" t="s">
-        <v>2560</v>
       </c>
       <c r="F607" s="5">
         <v>75</v>
@@ -21637,19 +21630,19 @@
     </row>
     <row r="608" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A608" s="5" t="s">
-        <v>2561</v>
+        <v>2560</v>
       </c>
       <c r="B608" s="6" t="s">
         <v>845</v>
       </c>
       <c r="C608" s="7" t="s">
+        <v>2561</v>
+      </c>
+      <c r="D608" s="17" t="s">
         <v>2562</v>
       </c>
-      <c r="D608" s="17" t="s">
+      <c r="E608" s="7" t="s">
         <v>2563</v>
-      </c>
-      <c r="E608" s="7" t="s">
-        <v>2564</v>
       </c>
       <c r="F608" s="5">
         <v>75</v>
@@ -21657,19 +21650,19 @@
     </row>
     <row r="609" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A609" s="5" t="s">
-        <v>2565</v>
+        <v>2564</v>
       </c>
       <c r="B609" s="6" t="s">
         <v>395</v>
       </c>
       <c r="C609" s="7" t="s">
+        <v>2565</v>
+      </c>
+      <c r="D609" s="17" t="s">
         <v>2566</v>
       </c>
-      <c r="D609" s="17" t="s">
+      <c r="E609" s="7" t="s">
         <v>2567</v>
-      </c>
-      <c r="E609" s="7" t="s">
-        <v>2568</v>
       </c>
       <c r="F609" s="5">
         <v>75</v>
@@ -21677,19 +21670,19 @@
     </row>
     <row r="610" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A610" s="5" t="s">
-        <v>2569</v>
+        <v>2568</v>
       </c>
       <c r="B610" s="6" t="s">
         <v>1140</v>
       </c>
       <c r="C610" s="7" t="s">
+        <v>2569</v>
+      </c>
+      <c r="D610" s="17" t="s">
         <v>2570</v>
       </c>
-      <c r="D610" s="17" t="s">
+      <c r="E610" s="7" t="s">
         <v>2571</v>
-      </c>
-      <c r="E610" s="7" t="s">
-        <v>2572</v>
       </c>
       <c r="F610" s="5">
         <v>75</v>
@@ -21697,19 +21690,19 @@
     </row>
     <row r="611" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A611" s="5" t="s">
-        <v>2573</v>
+        <v>2572</v>
       </c>
       <c r="B611" s="6" t="s">
         <v>1150</v>
       </c>
       <c r="C611" s="7" t="s">
+        <v>2573</v>
+      </c>
+      <c r="D611" s="17" t="s">
         <v>2574</v>
       </c>
-      <c r="D611" s="17" t="s">
+      <c r="E611" s="7" t="s">
         <v>2575</v>
-      </c>
-      <c r="E611" s="7" t="s">
-        <v>2576</v>
       </c>
       <c r="F611" s="5">
         <v>75</v>
@@ -21717,19 +21710,19 @@
     </row>
     <row r="612" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A612" s="5" t="s">
-        <v>2577</v>
+        <v>2576</v>
       </c>
       <c r="B612" s="6" t="s">
         <v>1973</v>
       </c>
       <c r="C612" s="7" t="s">
+        <v>2577</v>
+      </c>
+      <c r="D612" s="17" t="s">
         <v>2578</v>
       </c>
-      <c r="D612" s="17" t="s">
+      <c r="E612" s="7" t="s">
         <v>2579</v>
-      </c>
-      <c r="E612" s="7" t="s">
-        <v>2580</v>
       </c>
       <c r="F612" s="5">
         <v>75</v>
@@ -21737,19 +21730,19 @@
     </row>
     <row r="613" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A613" s="5" t="s">
-        <v>2581</v>
+        <v>2580</v>
       </c>
       <c r="B613" s="6" t="s">
         <v>1704</v>
       </c>
       <c r="C613" s="7" t="s">
+        <v>2581</v>
+      </c>
+      <c r="D613" s="17" t="s">
         <v>2582</v>
       </c>
-      <c r="D613" s="17" t="s">
+      <c r="E613" s="7" t="s">
         <v>2583</v>
-      </c>
-      <c r="E613" s="7" t="s">
-        <v>2584</v>
       </c>
       <c r="F613" s="5">
         <v>75</v>
@@ -21757,19 +21750,19 @@
     </row>
     <row r="614" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A614" s="5" t="s">
-        <v>2585</v>
+        <v>2584</v>
       </c>
       <c r="B614" s="6" t="s">
         <v>845</v>
       </c>
       <c r="C614" s="7" t="s">
+        <v>2585</v>
+      </c>
+      <c r="D614" s="17" t="s">
         <v>2586</v>
       </c>
-      <c r="D614" s="17" t="s">
+      <c r="E614" s="7" t="s">
         <v>2587</v>
-      </c>
-      <c r="E614" s="7" t="s">
-        <v>2588</v>
       </c>
       <c r="F614" s="5">
         <v>76</v>
@@ -21777,19 +21770,19 @@
     </row>
     <row r="615" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A615" s="5" t="s">
-        <v>2589</v>
+        <v>2588</v>
       </c>
       <c r="B615" s="6" t="s">
         <v>1508</v>
       </c>
       <c r="C615" s="7" t="s">
+        <v>2589</v>
+      </c>
+      <c r="D615" s="17" t="s">
         <v>2590</v>
       </c>
-      <c r="D615" s="17" t="s">
+      <c r="E615" s="7" t="s">
         <v>2591</v>
-      </c>
-      <c r="E615" s="7" t="s">
-        <v>2592</v>
       </c>
       <c r="F615" s="5">
         <v>76</v>
@@ -21797,19 +21790,19 @@
     </row>
     <row r="616" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A616" s="5" t="s">
-        <v>2593</v>
+        <v>2592</v>
       </c>
       <c r="B616" s="6" t="s">
         <v>1508</v>
       </c>
       <c r="C616" s="7" t="s">
+        <v>2593</v>
+      </c>
+      <c r="D616" s="17" t="s">
         <v>2594</v>
       </c>
-      <c r="D616" s="17" t="s">
+      <c r="E616" s="7" t="s">
         <v>2595</v>
-      </c>
-      <c r="E616" s="7" t="s">
-        <v>2596</v>
       </c>
       <c r="F616" s="5">
         <v>76</v>
@@ -21817,19 +21810,19 @@
     </row>
     <row r="617" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A617" s="5" t="s">
-        <v>2597</v>
+        <v>2596</v>
       </c>
       <c r="B617" s="6" t="s">
         <v>1624</v>
       </c>
       <c r="C617" s="7" t="s">
+        <v>2597</v>
+      </c>
+      <c r="D617" s="17" t="s">
         <v>2598</v>
       </c>
-      <c r="D617" s="17" t="s">
+      <c r="E617" s="7" t="s">
         <v>2599</v>
-      </c>
-      <c r="E617" s="7" t="s">
-        <v>2600</v>
       </c>
       <c r="F617" s="5">
         <v>76</v>
@@ -21837,19 +21830,19 @@
     </row>
     <row r="618" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A618" s="5" t="s">
-        <v>2601</v>
+        <v>2600</v>
       </c>
       <c r="B618" s="6" t="s">
         <v>287</v>
       </c>
       <c r="C618" s="7" t="s">
+        <v>2601</v>
+      </c>
+      <c r="D618" s="17" t="s">
         <v>2602</v>
       </c>
-      <c r="D618" s="17" t="s">
+      <c r="E618" s="7" t="s">
         <v>2603</v>
-      </c>
-      <c r="E618" s="7" t="s">
-        <v>2604</v>
       </c>
       <c r="F618" s="5">
         <v>77</v>
@@ -21857,19 +21850,19 @@
     </row>
     <row r="619" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A619" s="5" t="s">
-        <v>2605</v>
+        <v>2604</v>
       </c>
       <c r="B619" s="6" t="s">
         <v>930</v>
       </c>
       <c r="C619" s="7" t="s">
+        <v>2605</v>
+      </c>
+      <c r="D619" s="17" t="s">
         <v>2606</v>
       </c>
-      <c r="D619" s="17" t="s">
+      <c r="E619" s="7" t="s">
         <v>2607</v>
-      </c>
-      <c r="E619" s="7" t="s">
-        <v>2608</v>
       </c>
       <c r="F619" s="5">
         <v>77</v>
@@ -21877,7 +21870,7 @@
     </row>
     <row r="620" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A620" s="5" t="s">
-        <v>2609</v>
+        <v>2608</v>
       </c>
       <c r="B620" s="6" t="s">
         <v>342</v>
@@ -21889,7 +21882,7 @@
         <v>2023</v>
       </c>
       <c r="E620" s="7" t="s">
-        <v>2610</v>
+        <v>2609</v>
       </c>
       <c r="F620" s="5">
         <v>77</v>
@@ -21897,19 +21890,19 @@
     </row>
     <row r="621" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A621" s="5" t="s">
-        <v>2611</v>
+        <v>2610</v>
       </c>
       <c r="B621" s="6" t="s">
         <v>1242</v>
       </c>
       <c r="C621" s="7" t="s">
-        <v>2612</v>
+        <v>2611</v>
       </c>
       <c r="D621" s="17" t="s">
         <v>2029</v>
       </c>
       <c r="E621" s="7" t="s">
-        <v>2613</v>
+        <v>2612</v>
       </c>
       <c r="F621" s="5">
         <v>77</v>
@@ -21917,19 +21910,19 @@
     </row>
     <row r="622" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A622" s="5" t="s">
-        <v>2614</v>
+        <v>2613</v>
       </c>
       <c r="B622" s="6" t="s">
         <v>391</v>
       </c>
       <c r="C622" s="7" t="s">
+        <v>2614</v>
+      </c>
+      <c r="D622" s="17" t="s">
         <v>2615</v>
       </c>
-      <c r="D622" s="17" t="s">
+      <c r="E622" s="7" t="s">
         <v>2616</v>
-      </c>
-      <c r="E622" s="7" t="s">
-        <v>2617</v>
       </c>
       <c r="F622" s="5">
         <v>77</v>
@@ -21949,7 +21942,7 @@
         <v>2229</v>
       </c>
       <c r="E623" s="7" t="s">
-        <v>2618</v>
+        <v>2617</v>
       </c>
       <c r="F623" s="5">
         <v>78</v>
@@ -21969,7 +21962,7 @@
         <v>2158</v>
       </c>
       <c r="E624" s="7" t="s">
-        <v>2619</v>
+        <v>2618</v>
       </c>
       <c r="F624" s="5">
         <v>79</v>
@@ -21983,13 +21976,13 @@
         <v>1242</v>
       </c>
       <c r="C625" s="7" t="s">
-        <v>2620</v>
+        <v>2619</v>
       </c>
       <c r="D625" s="17" t="s">
         <v>2166</v>
       </c>
       <c r="E625" s="7" t="s">
-        <v>2621</v>
+        <v>2620</v>
       </c>
       <c r="F625" s="5">
         <v>79</v>
@@ -21997,19 +21990,19 @@
     </row>
     <row r="626" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A626" s="5" t="s">
-        <v>2622</v>
+        <v>2621</v>
       </c>
       <c r="B626" s="6" t="s">
         <v>1140</v>
       </c>
       <c r="C626" s="7" t="s">
+        <v>2622</v>
+      </c>
+      <c r="D626" s="17" t="s">
         <v>2623</v>
       </c>
-      <c r="D626" s="17" t="s">
+      <c r="E626" s="7" t="s">
         <v>2624</v>
-      </c>
-      <c r="E626" s="7" t="s">
-        <v>2625</v>
       </c>
       <c r="F626" s="5">
         <v>79</v>
@@ -22017,7 +22010,7 @@
     </row>
     <row r="627" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A627" s="5" t="s">
-        <v>2626</v>
+        <v>2625</v>
       </c>
       <c r="B627" s="6" t="s">
         <v>1150</v>
@@ -22029,7 +22022,7 @@
         <v>2173</v>
       </c>
       <c r="E627" s="7" t="s">
-        <v>2627</v>
+        <v>2626</v>
       </c>
       <c r="F627" s="5">
         <v>79</v>
@@ -22037,19 +22030,19 @@
     </row>
     <row r="628" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A628" s="5" t="s">
-        <v>2628</v>
+        <v>2627</v>
       </c>
       <c r="B628" s="6" t="s">
         <v>990</v>
       </c>
       <c r="C628" s="7" t="s">
+        <v>2628</v>
+      </c>
+      <c r="D628" s="17" t="s">
         <v>2629</v>
       </c>
-      <c r="D628" s="17" t="s">
+      <c r="E628" s="7" t="s">
         <v>2630</v>
-      </c>
-      <c r="E628" s="7" t="s">
-        <v>2631</v>
       </c>
       <c r="F628" s="5">
         <v>80</v>
@@ -22057,19 +22050,19 @@
     </row>
     <row r="629" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A629" s="5" t="s">
-        <v>2632</v>
+        <v>2631</v>
       </c>
       <c r="B629" s="6" t="s">
         <v>1150</v>
       </c>
       <c r="C629" s="7" t="s">
+        <v>2632</v>
+      </c>
+      <c r="D629" s="17" t="s">
         <v>2633</v>
       </c>
-      <c r="D629" s="17" t="s">
+      <c r="E629" s="7" t="s">
         <v>2634</v>
-      </c>
-      <c r="E629" s="7" t="s">
-        <v>2635</v>
       </c>
       <c r="F629" s="5">
         <v>80</v>
@@ -22077,19 +22070,19 @@
     </row>
     <row r="630" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A630" s="5" t="s">
-        <v>2636</v>
+        <v>2635</v>
       </c>
       <c r="B630" s="6" t="s">
         <v>1140</v>
       </c>
       <c r="C630" s="7" t="s">
+        <v>2636</v>
+      </c>
+      <c r="D630" s="17" t="s">
         <v>2637</v>
       </c>
-      <c r="D630" s="17" t="s">
+      <c r="E630" s="7" t="s">
         <v>2638</v>
-      </c>
-      <c r="E630" s="7" t="s">
-        <v>2639</v>
       </c>
       <c r="F630" s="5">
         <v>80</v>
@@ -22097,19 +22090,19 @@
     </row>
     <row r="631" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A631" s="5" t="s">
-        <v>2640</v>
+        <v>2639</v>
       </c>
       <c r="B631" s="6" t="s">
         <v>963</v>
       </c>
       <c r="C631" s="7" t="s">
+        <v>2640</v>
+      </c>
+      <c r="D631" s="17" t="s">
         <v>2641</v>
       </c>
-      <c r="D631" s="17" t="s">
+      <c r="E631" s="7" t="s">
         <v>2642</v>
-      </c>
-      <c r="E631" s="7" t="s">
-        <v>2643</v>
       </c>
       <c r="F631" s="5">
         <v>80</v>
@@ -22117,19 +22110,19 @@
     </row>
     <row r="632" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A632" s="5" t="s">
-        <v>2644</v>
+        <v>2643</v>
       </c>
       <c r="B632" s="6" t="s">
         <v>1133</v>
       </c>
       <c r="C632" s="7" t="s">
+        <v>2644</v>
+      </c>
+      <c r="D632" s="17" t="s">
         <v>2645</v>
       </c>
-      <c r="D632" s="17" t="s">
+      <c r="E632" s="7" t="s">
         <v>2646</v>
-      </c>
-      <c r="E632" s="7" t="s">
-        <v>2647</v>
       </c>
       <c r="F632" s="5">
         <v>80</v>
@@ -22137,19 +22130,19 @@
     </row>
     <row r="633" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A633" s="5" t="s">
-        <v>2648</v>
+        <v>2647</v>
       </c>
       <c r="B633" s="6" t="s">
         <v>840</v>
       </c>
       <c r="C633" s="7" t="s">
+        <v>2648</v>
+      </c>
+      <c r="D633" s="17" t="s">
         <v>2649</v>
       </c>
-      <c r="D633" s="17" t="s">
+      <c r="E633" s="7" t="s">
         <v>2650</v>
-      </c>
-      <c r="E633" s="7" t="s">
-        <v>2651</v>
       </c>
       <c r="F633" s="5">
         <v>80</v>
@@ -22157,7 +22150,7 @@
     </row>
     <row r="634" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A634" s="5" t="s">
-        <v>2652</v>
+        <v>2651</v>
       </c>
       <c r="B634" s="6" t="s">
         <v>921</v>
@@ -22166,10 +22159,10 @@
         <v>646</v>
       </c>
       <c r="D634" s="17" t="s">
+        <v>2652</v>
+      </c>
+      <c r="E634" s="7" t="s">
         <v>2653</v>
-      </c>
-      <c r="E634" s="7" t="s">
-        <v>2654</v>
       </c>
       <c r="F634" s="5">
         <v>80</v>
@@ -22177,19 +22170,19 @@
     </row>
     <row r="635" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A635" s="5" t="s">
-        <v>2655</v>
+        <v>2654</v>
       </c>
       <c r="B635" s="6" t="s">
         <v>1150</v>
       </c>
       <c r="C635" s="7" t="s">
+        <v>2655</v>
+      </c>
+      <c r="D635" s="17" t="s">
         <v>2656</v>
       </c>
-      <c r="D635" s="17" t="s">
+      <c r="E635" s="7" t="s">
         <v>2657</v>
-      </c>
-      <c r="E635" s="7" t="s">
-        <v>2658</v>
       </c>
       <c r="F635" s="5">
         <v>80</v>
@@ -22197,19 +22190,19 @@
     </row>
     <row r="636" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A636" s="5" t="s">
-        <v>2659</v>
+        <v>2658</v>
       </c>
       <c r="B636" s="6" t="s">
         <v>840</v>
       </c>
       <c r="C636" s="7" t="s">
+        <v>2659</v>
+      </c>
+      <c r="D636" s="17" t="s">
         <v>2660</v>
       </c>
-      <c r="D636" s="17" t="s">
+      <c r="E636" s="7" t="s">
         <v>2661</v>
-      </c>
-      <c r="E636" s="7" t="s">
-        <v>2662</v>
       </c>
       <c r="F636" s="5">
         <v>80</v>
@@ -22217,19 +22210,19 @@
     </row>
     <row r="637" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A637" s="5" t="s">
-        <v>2663</v>
+        <v>2662</v>
       </c>
       <c r="B637" s="6" t="s">
         <v>1150</v>
       </c>
       <c r="C637" s="7" t="s">
+        <v>2663</v>
+      </c>
+      <c r="D637" s="17" t="s">
         <v>2664</v>
       </c>
-      <c r="D637" s="17" t="s">
+      <c r="E637" s="7" t="s">
         <v>2665</v>
-      </c>
-      <c r="E637" s="7" t="s">
-        <v>2666</v>
       </c>
       <c r="F637" s="5">
         <v>80</v>
@@ -22237,19 +22230,19 @@
     </row>
     <row r="638" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A638" s="5" t="s">
+        <v>2666</v>
+      </c>
+      <c r="B638" s="6" t="s">
         <v>2667</v>
       </c>
-      <c r="B638" s="6" t="s">
+      <c r="C638" s="7" t="s">
         <v>2668</v>
       </c>
-      <c r="C638" s="7" t="s">
+      <c r="D638" s="17" t="s">
         <v>2669</v>
       </c>
-      <c r="D638" s="17" t="s">
+      <c r="E638" s="7" t="s">
         <v>2670</v>
-      </c>
-      <c r="E638" s="7" t="s">
-        <v>2671</v>
       </c>
       <c r="F638" s="5">
         <v>81</v>
@@ -22257,19 +22250,19 @@
     </row>
     <row r="639" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A639" s="5" t="s">
-        <v>2672</v>
+        <v>2671</v>
       </c>
       <c r="B639" s="6" t="s">
         <v>1150</v>
       </c>
       <c r="C639" s="7" t="s">
+        <v>2672</v>
+      </c>
+      <c r="D639" s="17" t="s">
         <v>2673</v>
       </c>
-      <c r="D639" s="17" t="s">
+      <c r="E639" s="7" t="s">
         <v>2674</v>
-      </c>
-      <c r="E639" s="7" t="s">
-        <v>2675</v>
       </c>
       <c r="F639" s="5">
         <v>81</v>
@@ -22277,19 +22270,19 @@
     </row>
     <row r="640" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A640" s="5" t="s">
-        <v>2676</v>
+        <v>2675</v>
       </c>
       <c r="B640" s="6" t="s">
         <v>2164</v>
       </c>
       <c r="C640" s="7" t="s">
+        <v>2676</v>
+      </c>
+      <c r="D640" s="17" t="s">
         <v>2677</v>
       </c>
-      <c r="D640" s="17" t="s">
+      <c r="E640" s="7" t="s">
         <v>2678</v>
-      </c>
-      <c r="E640" s="7" t="s">
-        <v>2679</v>
       </c>
       <c r="F640" s="5">
         <v>81</v>
@@ -22297,19 +22290,19 @@
     </row>
     <row r="641" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A641" s="5" t="s">
-        <v>2680</v>
+        <v>2679</v>
       </c>
       <c r="B641" s="6" t="s">
         <v>287</v>
       </c>
       <c r="C641" s="7" t="s">
-        <v>2673</v>
+        <v>2672</v>
       </c>
       <c r="D641" s="17" t="s">
+        <v>2680</v>
+      </c>
+      <c r="E641" s="7" t="s">
         <v>2681</v>
-      </c>
-      <c r="E641" s="7" t="s">
-        <v>2682</v>
       </c>
       <c r="F641" s="5">
         <v>81</v>
@@ -22317,19 +22310,19 @@
     </row>
     <row r="642" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A642" s="5" t="s">
-        <v>2683</v>
+        <v>2682</v>
       </c>
       <c r="B642" s="6" t="s">
         <v>840</v>
       </c>
       <c r="C642" s="7" t="s">
+        <v>2683</v>
+      </c>
+      <c r="D642" s="17" t="s">
         <v>2684</v>
       </c>
-      <c r="D642" s="17" t="s">
+      <c r="E642" s="7" t="s">
         <v>2685</v>
-      </c>
-      <c r="E642" s="7" t="s">
-        <v>2686</v>
       </c>
       <c r="F642" s="5">
         <v>81</v>
@@ -22337,19 +22330,19 @@
     </row>
     <row r="643" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A643" s="5" t="s">
-        <v>2687</v>
+        <v>2686</v>
       </c>
       <c r="B643" s="6" t="s">
         <v>1804</v>
       </c>
       <c r="C643" s="7" t="s">
+        <v>2687</v>
+      </c>
+      <c r="D643" s="17" t="s">
         <v>2688</v>
       </c>
-      <c r="D643" s="17" t="s">
+      <c r="E643" s="7" t="s">
         <v>2689</v>
-      </c>
-      <c r="E643" s="7" t="s">
-        <v>2690</v>
       </c>
       <c r="F643" s="5">
         <v>81</v>
@@ -22357,7 +22350,7 @@
     </row>
     <row r="644" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A644" s="5" t="s">
-        <v>2691</v>
+        <v>2690</v>
       </c>
       <c r="B644" s="6" t="s">
         <v>1624</v>
@@ -22366,10 +22359,10 @@
         <v>1484</v>
       </c>
       <c r="D644" s="17" t="s">
+        <v>2691</v>
+      </c>
+      <c r="E644" s="7" t="s">
         <v>2692</v>
-      </c>
-      <c r="E644" s="7" t="s">
-        <v>2693</v>
       </c>
       <c r="F644" s="5">
         <v>81</v>
@@ -22377,19 +22370,19 @@
     </row>
     <row r="645" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A645" s="5" t="s">
-        <v>2694</v>
+        <v>2693</v>
       </c>
       <c r="B645" s="6" t="s">
         <v>1028</v>
       </c>
       <c r="C645" s="7" t="s">
+        <v>2694</v>
+      </c>
+      <c r="D645" s="17" t="s">
         <v>2695</v>
       </c>
-      <c r="D645" s="17" t="s">
+      <c r="E645" s="7" t="s">
         <v>2696</v>
-      </c>
-      <c r="E645" s="7" t="s">
-        <v>2697</v>
       </c>
       <c r="F645" s="5">
         <v>81</v>
@@ -22409,7 +22402,7 @@
         <v>2252</v>
       </c>
       <c r="E646" s="7" t="s">
-        <v>2698</v>
+        <v>2697</v>
       </c>
       <c r="F646" s="5">
         <v>82</v>
@@ -22429,7 +22422,7 @@
         <v>2256</v>
       </c>
       <c r="E647" s="7" t="s">
-        <v>2699</v>
+        <v>2698</v>
       </c>
       <c r="F647" s="5">
         <v>82</v>
@@ -22437,7 +22430,7 @@
     </row>
     <row r="648" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A648" s="5" t="s">
-        <v>2700</v>
+        <v>2699</v>
       </c>
       <c r="B648" s="6" t="s">
         <v>840</v>
@@ -22449,7 +22442,7 @@
         <v>2260</v>
       </c>
       <c r="E648" s="7" t="s">
-        <v>2701</v>
+        <v>2700</v>
       </c>
       <c r="F648" s="5">
         <v>82</v>
@@ -22469,7 +22462,7 @@
         <v>2271</v>
       </c>
       <c r="E649" s="7" t="s">
-        <v>2702</v>
+        <v>2701</v>
       </c>
       <c r="F649" s="5">
         <v>82</v>
@@ -22477,19 +22470,19 @@
     </row>
     <row r="650" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A650" s="5" t="s">
-        <v>2703</v>
+        <v>2702</v>
       </c>
       <c r="B650" s="6" t="s">
         <v>899</v>
       </c>
       <c r="C650" s="7" t="s">
+        <v>2703</v>
+      </c>
+      <c r="D650" s="17" t="s">
         <v>2704</v>
       </c>
-      <c r="D650" s="17" t="s">
+      <c r="E650" s="7" t="s">
         <v>2705</v>
-      </c>
-      <c r="E650" s="7" t="s">
-        <v>2706</v>
       </c>
       <c r="F650" s="5">
         <v>83</v>
@@ -22497,19 +22490,19 @@
     </row>
     <row r="651" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A651" s="5" t="s">
-        <v>2707</v>
+        <v>2706</v>
       </c>
       <c r="B651" s="6" t="s">
         <v>921</v>
       </c>
       <c r="C651" s="7" t="s">
+        <v>2707</v>
+      </c>
+      <c r="D651" s="17" t="s">
+        <v>2709</v>
+      </c>
+      <c r="E651" s="7" t="s">
         <v>2708</v>
-      </c>
-      <c r="D651" s="17" t="s">
-        <v>2710</v>
-      </c>
-      <c r="E651" s="7" t="s">
-        <v>2709</v>
       </c>
       <c r="F651" s="5">
         <v>84</v>
@@ -22517,19 +22510,19 @@
     </row>
     <row r="652" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A652" s="5" t="s">
-        <v>2711</v>
+        <v>2710</v>
       </c>
       <c r="B652" s="6" t="s">
         <v>963</v>
       </c>
       <c r="C652" s="7" t="s">
+        <v>2711</v>
+      </c>
+      <c r="D652" s="17" t="s">
         <v>2712</v>
       </c>
-      <c r="D652" s="17" t="s">
+      <c r="E652" s="7" t="s">
         <v>2713</v>
-      </c>
-      <c r="E652" s="7" t="s">
-        <v>2714</v>
       </c>
       <c r="F652" s="5">
         <v>84</v>
@@ -22537,19 +22530,19 @@
     </row>
     <row r="653" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A653" s="5" t="s">
-        <v>2715</v>
+        <v>2714</v>
       </c>
       <c r="B653" s="6" t="s">
         <v>391</v>
       </c>
       <c r="C653" s="7" t="s">
+        <v>2715</v>
+      </c>
+      <c r="D653" s="17" t="s">
         <v>2716</v>
       </c>
-      <c r="D653" s="17" t="s">
+      <c r="E653" s="7" t="s">
         <v>2717</v>
-      </c>
-      <c r="E653" s="7" t="s">
-        <v>2718</v>
       </c>
       <c r="F653" s="5">
         <v>84</v>
@@ -22557,19 +22550,19 @@
     </row>
     <row r="654" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A654" s="5" t="s">
-        <v>2719</v>
+        <v>2718</v>
       </c>
       <c r="B654" s="6" t="s">
         <v>395</v>
       </c>
       <c r="C654" s="7" t="s">
+        <v>2719</v>
+      </c>
+      <c r="D654" s="17" t="s">
         <v>2720</v>
       </c>
-      <c r="D654" s="17" t="s">
+      <c r="E654" s="7" t="s">
         <v>2721</v>
-      </c>
-      <c r="E654" s="7" t="s">
-        <v>2722</v>
       </c>
       <c r="F654" s="5">
         <v>84</v>
@@ -22577,19 +22570,19 @@
     </row>
     <row r="655" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A655" s="5" t="s">
-        <v>2723</v>
+        <v>2722</v>
       </c>
       <c r="B655" s="6" t="s">
         <v>342</v>
       </c>
       <c r="C655" s="7" t="s">
+        <v>2723</v>
+      </c>
+      <c r="D655" s="17" t="s">
         <v>2724</v>
       </c>
-      <c r="D655" s="17" t="s">
+      <c r="E655" s="7" t="s">
         <v>2725</v>
-      </c>
-      <c r="E655" s="7" t="s">
-        <v>2726</v>
       </c>
       <c r="F655" s="5">
         <v>84</v>
@@ -22597,19 +22590,19 @@
     </row>
     <row r="656" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A656" s="5" t="s">
-        <v>2727</v>
+        <v>2726</v>
       </c>
       <c r="B656" s="6" t="s">
         <v>1140</v>
       </c>
       <c r="C656" s="7" t="s">
+        <v>2727</v>
+      </c>
+      <c r="D656" s="17" t="s">
         <v>2728</v>
       </c>
-      <c r="D656" s="17" t="s">
+      <c r="E656" s="7" t="s">
         <v>2729</v>
-      </c>
-      <c r="E656" s="7" t="s">
-        <v>2730</v>
       </c>
       <c r="F656" s="5">
         <v>84</v>
@@ -22617,19 +22610,19 @@
     </row>
     <row r="657" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A657" s="5" t="s">
-        <v>2731</v>
+        <v>2730</v>
       </c>
       <c r="B657" s="6" t="s">
         <v>963</v>
       </c>
       <c r="C657" s="7" t="s">
+        <v>2731</v>
+      </c>
+      <c r="D657" s="17" t="s">
         <v>2732</v>
       </c>
-      <c r="D657" s="17" t="s">
+      <c r="E657" s="7" t="s">
         <v>2733</v>
-      </c>
-      <c r="E657" s="7" t="s">
-        <v>2734</v>
       </c>
       <c r="F657" s="5">
         <v>84</v>
@@ -22637,19 +22630,19 @@
     </row>
     <row r="658" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A658" s="5" t="s">
-        <v>2735</v>
+        <v>2734</v>
       </c>
       <c r="B658" s="6" t="s">
         <v>845</v>
       </c>
       <c r="C658" s="7" t="s">
+        <v>2735</v>
+      </c>
+      <c r="D658" s="17" t="s">
         <v>2736</v>
       </c>
-      <c r="D658" s="17" t="s">
+      <c r="E658" s="7" t="s">
         <v>2737</v>
-      </c>
-      <c r="E658" s="7" t="s">
-        <v>2738</v>
       </c>
       <c r="F658" s="5">
         <v>85</v>
@@ -22657,19 +22650,19 @@
     </row>
     <row r="659" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A659" s="5" t="s">
-        <v>2739</v>
+        <v>2738</v>
       </c>
       <c r="B659" s="6" t="s">
         <v>395</v>
       </c>
       <c r="C659" s="7" t="s">
+        <v>2739</v>
+      </c>
+      <c r="D659" s="17" t="s">
         <v>2740</v>
       </c>
-      <c r="D659" s="17" t="s">
+      <c r="E659" s="7" t="s">
         <v>2741</v>
-      </c>
-      <c r="E659" s="7" t="s">
-        <v>2742</v>
       </c>
       <c r="F659" s="5">
         <v>85</v>
@@ -22677,19 +22670,19 @@
     </row>
     <row r="660" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A660" s="5" t="s">
-        <v>2743</v>
+        <v>2742</v>
       </c>
       <c r="B660" s="6" t="s">
         <v>395</v>
       </c>
       <c r="C660" s="7" t="s">
+        <v>2743</v>
+      </c>
+      <c r="D660" s="17" t="s">
         <v>2744</v>
       </c>
-      <c r="D660" s="17" t="s">
+      <c r="E660" s="7" t="s">
         <v>2745</v>
-      </c>
-      <c r="E660" s="7" t="s">
-        <v>2746</v>
       </c>
       <c r="F660" s="5">
         <v>85</v>
@@ -22697,19 +22690,19 @@
     </row>
     <row r="661" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A661" s="5" t="s">
-        <v>2747</v>
+        <v>2746</v>
       </c>
       <c r="B661" s="6" t="s">
         <v>921</v>
       </c>
       <c r="C661" s="7" t="s">
+        <v>2747</v>
+      </c>
+      <c r="D661" s="17" t="s">
         <v>2748</v>
       </c>
-      <c r="D661" s="17" t="s">
+      <c r="E661" s="7" t="s">
         <v>2749</v>
-      </c>
-      <c r="E661" s="7" t="s">
-        <v>2750</v>
       </c>
       <c r="F661" s="5">
         <v>85</v>
@@ -22717,19 +22710,19 @@
     </row>
     <row r="662" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A662" s="5" t="s">
-        <v>2751</v>
+        <v>2750</v>
       </c>
       <c r="B662" s="6" t="s">
         <v>391</v>
       </c>
       <c r="C662" s="7" t="s">
+        <v>2751</v>
+      </c>
+      <c r="D662" s="17" t="s">
         <v>2752</v>
       </c>
-      <c r="D662" s="17" t="s">
+      <c r="E662" s="7" t="s">
         <v>2753</v>
-      </c>
-      <c r="E662" s="7" t="s">
-        <v>2754</v>
       </c>
       <c r="F662" s="5">
         <v>85</v>
@@ -22737,19 +22730,19 @@
     </row>
     <row r="663" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A663" s="5" t="s">
-        <v>2755</v>
+        <v>2754</v>
       </c>
       <c r="B663" s="6" t="s">
         <v>930</v>
       </c>
       <c r="C663" s="7" t="s">
+        <v>2755</v>
+      </c>
+      <c r="D663" s="17" t="s">
         <v>2756</v>
       </c>
-      <c r="D663" s="17" t="s">
+      <c r="E663" s="7" t="s">
         <v>2757</v>
-      </c>
-      <c r="E663" s="7" t="s">
-        <v>2758</v>
       </c>
       <c r="F663" s="5">
         <v>86</v>
@@ -22757,19 +22750,19 @@
     </row>
     <row r="664" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A664" s="5" t="s">
-        <v>2759</v>
+        <v>2758</v>
       </c>
       <c r="B664" s="6" t="s">
         <v>840</v>
       </c>
       <c r="C664" s="7" t="s">
+        <v>2759</v>
+      </c>
+      <c r="D664" s="17" t="s">
         <v>2760</v>
       </c>
-      <c r="D664" s="17" t="s">
+      <c r="E664" s="7" t="s">
         <v>2761</v>
-      </c>
-      <c r="E664" s="7" t="s">
-        <v>2762</v>
       </c>
       <c r="F664" s="5">
         <v>86</v>
@@ -22777,19 +22770,19 @@
     </row>
     <row r="665" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A665" s="5" t="s">
-        <v>2763</v>
+        <v>2762</v>
       </c>
       <c r="B665" s="6" t="s">
         <v>899</v>
       </c>
       <c r="C665" s="7" t="s">
+        <v>2763</v>
+      </c>
+      <c r="D665" s="17" t="s">
         <v>2764</v>
       </c>
-      <c r="D665" s="17" t="s">
+      <c r="E665" s="7" t="s">
         <v>2765</v>
-      </c>
-      <c r="E665" s="7" t="s">
-        <v>2766</v>
       </c>
       <c r="F665" s="5">
         <v>86</v>
@@ -22797,19 +22790,19 @@
     </row>
     <row r="666" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A666" s="5" t="s">
-        <v>2767</v>
+        <v>2766</v>
       </c>
       <c r="B666" s="6" t="s">
         <v>963</v>
       </c>
       <c r="C666" s="7" t="s">
+        <v>2767</v>
+      </c>
+      <c r="D666" s="17" t="s">
         <v>2768</v>
       </c>
-      <c r="D666" s="17" t="s">
+      <c r="E666" s="7" t="s">
         <v>2769</v>
-      </c>
-      <c r="E666" s="7" t="s">
-        <v>2770</v>
       </c>
       <c r="F666" s="5">
         <v>86</v>
@@ -22817,19 +22810,19 @@
     </row>
     <row r="667" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A667" s="5" t="s">
+        <v>2770</v>
+      </c>
+      <c r="B667" s="6" t="s">
         <v>2771</v>
       </c>
-      <c r="B667" s="6" t="s">
+      <c r="C667" s="7" t="s">
+        <v>2774</v>
+      </c>
+      <c r="D667" s="17" t="s">
+        <v>2773</v>
+      </c>
+      <c r="E667" s="7" t="s">
         <v>2772</v>
-      </c>
-      <c r="C667" s="7" t="s">
-        <v>2775</v>
-      </c>
-      <c r="D667" s="17" t="s">
-        <v>2774</v>
-      </c>
-      <c r="E667" s="7" t="s">
-        <v>2773</v>
       </c>
       <c r="F667" s="5">
         <v>86</v>
@@ -22837,19 +22830,19 @@
     </row>
     <row r="668" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A668" s="5" t="s">
-        <v>2776</v>
+        <v>2775</v>
       </c>
       <c r="B668" s="6" t="s">
         <v>1008</v>
       </c>
       <c r="C668" s="7" t="s">
+        <v>2776</v>
+      </c>
+      <c r="D668" s="17" t="s">
         <v>2777</v>
       </c>
-      <c r="D668" s="17" t="s">
+      <c r="E668" s="7" t="s">
         <v>2778</v>
-      </c>
-      <c r="E668" s="7" t="s">
-        <v>2779</v>
       </c>
       <c r="F668" s="5">
         <v>86</v>
@@ -22857,19 +22850,19 @@
     </row>
     <row r="669" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A669" s="5" t="s">
-        <v>2780</v>
+        <v>2779</v>
       </c>
       <c r="B669" s="6" t="s">
         <v>1020</v>
       </c>
       <c r="C669" s="7" t="s">
+        <v>2780</v>
+      </c>
+      <c r="D669" s="17" t="s">
         <v>2781</v>
       </c>
-      <c r="D669" s="17" t="s">
+      <c r="E669" s="7" t="s">
         <v>2782</v>
-      </c>
-      <c r="E669" s="7" t="s">
-        <v>2783</v>
       </c>
       <c r="F669" s="5">
         <v>86</v>
@@ -22877,19 +22870,19 @@
     </row>
     <row r="670" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A670" s="5" t="s">
+        <v>2783</v>
+      </c>
+      <c r="B670" s="6" t="s">
         <v>2784</v>
-      </c>
-      <c r="B670" s="6" t="s">
-        <v>2785</v>
       </c>
       <c r="C670" s="7" t="s">
         <v>991</v>
       </c>
       <c r="D670" s="17" t="s">
+        <v>2785</v>
+      </c>
+      <c r="E670" s="7" t="s">
         <v>2786</v>
-      </c>
-      <c r="E670" s="7" t="s">
-        <v>2787</v>
       </c>
       <c r="F670" s="5">
         <v>87</v>
@@ -22897,19 +22890,19 @@
     </row>
     <row r="671" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A671" s="5" t="s">
-        <v>2788</v>
+        <v>2787</v>
       </c>
       <c r="B671" s="6" t="s">
         <v>1046</v>
       </c>
       <c r="C671" s="7" t="s">
+        <v>2788</v>
+      </c>
+      <c r="D671" s="17" t="s">
         <v>2789</v>
       </c>
-      <c r="D671" s="17" t="s">
+      <c r="E671" s="7" t="s">
         <v>2790</v>
-      </c>
-      <c r="E671" s="7" t="s">
-        <v>2791</v>
       </c>
       <c r="F671" s="5">
         <v>87</v>
@@ -22917,19 +22910,19 @@
     </row>
     <row r="672" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A672" s="5" t="s">
+        <v>2791</v>
+      </c>
+      <c r="B672" s="6" t="s">
         <v>2792</v>
       </c>
-      <c r="B672" s="6" t="s">
+      <c r="C672" s="7" t="s">
+        <v>2788</v>
+      </c>
+      <c r="D672" s="17" t="s">
+        <v>2794</v>
+      </c>
+      <c r="E672" s="7" t="s">
         <v>2793</v>
-      </c>
-      <c r="C672" s="7" t="s">
-        <v>2789</v>
-      </c>
-      <c r="D672" s="17" t="s">
-        <v>2795</v>
-      </c>
-      <c r="E672" s="7" t="s">
-        <v>2794</v>
       </c>
       <c r="F672" s="5">
         <v>87</v>
@@ -22937,19 +22930,19 @@
     </row>
     <row r="673" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A673" s="5" t="s">
-        <v>2796</v>
+        <v>2795</v>
       </c>
       <c r="B673" s="6" t="s">
         <v>342</v>
       </c>
       <c r="C673" s="7" t="s">
+        <v>2796</v>
+      </c>
+      <c r="D673" s="17" t="s">
         <v>2797</v>
       </c>
-      <c r="D673" s="17" t="s">
+      <c r="E673" s="7" t="s">
         <v>2798</v>
-      </c>
-      <c r="E673" s="7" t="s">
-        <v>2799</v>
       </c>
       <c r="F673" s="5">
         <v>87</v>
@@ -22957,19 +22950,19 @@
     </row>
     <row r="674" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A674" s="5" t="s">
-        <v>2800</v>
+        <v>2799</v>
       </c>
       <c r="B674" s="6" t="s">
         <v>395</v>
       </c>
       <c r="C674" s="7" t="s">
+        <v>2800</v>
+      </c>
+      <c r="D674" s="17" t="s">
         <v>2801</v>
       </c>
-      <c r="D674" s="17" t="s">
+      <c r="E674" s="7" t="s">
         <v>2802</v>
-      </c>
-      <c r="E674" s="7" t="s">
-        <v>2803</v>
       </c>
       <c r="F674" s="5">
         <v>87</v>
@@ -22977,19 +22970,19 @@
     </row>
     <row r="675" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A675" s="5" t="s">
-        <v>2804</v>
+        <v>2803</v>
       </c>
       <c r="B675" s="6" t="s">
         <v>840</v>
       </c>
       <c r="C675" s="7" t="s">
+        <v>2804</v>
+      </c>
+      <c r="D675" s="17" t="s">
         <v>2805</v>
       </c>
-      <c r="D675" s="17" t="s">
+      <c r="E675" s="7" t="s">
         <v>2806</v>
-      </c>
-      <c r="E675" s="7" t="s">
-        <v>2807</v>
       </c>
       <c r="F675" s="5">
         <v>87</v>
@@ -22997,19 +22990,19 @@
     </row>
     <row r="676" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A676" s="5" t="s">
+        <v>2807</v>
+      </c>
+      <c r="B676" s="6" t="s">
         <v>2808</v>
       </c>
-      <c r="B676" s="6" t="s">
+      <c r="C676" s="7" t="s">
+        <v>2731</v>
+      </c>
+      <c r="D676" s="17" t="s">
         <v>2809</v>
       </c>
-      <c r="C676" s="7" t="s">
-        <v>2732</v>
-      </c>
-      <c r="D676" s="17" t="s">
+      <c r="E676" s="7" t="s">
         <v>2810</v>
-      </c>
-      <c r="E676" s="7" t="s">
-        <v>2811</v>
       </c>
       <c r="F676" s="5">
         <v>87</v>
@@ -23017,7 +23010,7 @@
     </row>
     <row r="677" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A677" s="5" t="s">
-        <v>2812</v>
+        <v>2811</v>
       </c>
       <c r="B677" s="6" t="s">
         <v>840</v>
@@ -23026,10 +23019,10 @@
         <v>248</v>
       </c>
       <c r="D677" s="17" t="s">
+        <v>2812</v>
+      </c>
+      <c r="E677" s="7" t="s">
         <v>2813</v>
-      </c>
-      <c r="E677" s="7" t="s">
-        <v>2814</v>
       </c>
       <c r="F677" s="5">
         <v>88</v>
@@ -23037,7 +23030,7 @@
     </row>
     <row r="678" spans="1:6" ht="120" x14ac:dyDescent="0.25">
       <c r="A678" s="5" t="s">
-        <v>2815</v>
+        <v>2814</v>
       </c>
       <c r="B678" s="6" t="s">
         <v>342</v>
@@ -23046,10 +23039,10 @@
         <v>248</v>
       </c>
       <c r="D678" s="17" t="s">
+        <v>2815</v>
+      </c>
+      <c r="E678" s="7" t="s">
         <v>2816</v>
-      </c>
-      <c r="E678" s="7" t="s">
-        <v>2817</v>
       </c>
       <c r="F678" s="5">
         <v>88</v>
@@ -23057,7 +23050,7 @@
     </row>
     <row r="679" spans="1:6" ht="105" x14ac:dyDescent="0.25">
       <c r="A679" s="5" t="s">
-        <v>2818</v>
+        <v>2817</v>
       </c>
       <c r="B679" s="6" t="s">
         <v>342</v>
@@ -23066,10 +23059,10 @@
         <v>248</v>
       </c>
       <c r="D679" s="17" t="s">
+        <v>2818</v>
+      </c>
+      <c r="E679" s="7" t="s">
         <v>2819</v>
-      </c>
-      <c r="E679" s="7" t="s">
-        <v>2820</v>
       </c>
       <c r="F679" s="5">
         <v>91</v>
@@ -23077,19 +23070,19 @@
     </row>
     <row r="680" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A680" s="5" t="s">
+        <v>2820</v>
+      </c>
+      <c r="B680" s="6" t="s">
         <v>2821</v>
-      </c>
-      <c r="B680" s="6" t="s">
-        <v>2822</v>
       </c>
       <c r="C680" s="7" t="s">
         <v>248</v>
       </c>
       <c r="D680" s="17" t="s">
+        <v>2822</v>
+      </c>
+      <c r="E680" s="7" t="s">
         <v>2823</v>
-      </c>
-      <c r="E680" s="7" t="s">
-        <v>2824</v>
       </c>
       <c r="F680" s="5">
         <v>91</v>
@@ -23097,19 +23090,19 @@
     </row>
     <row r="681" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A681" s="5" t="s">
-        <v>2825</v>
+        <v>2824</v>
       </c>
       <c r="B681" s="6" t="s">
         <v>1721</v>
       </c>
       <c r="C681" s="7" t="s">
+        <v>2825</v>
+      </c>
+      <c r="D681" s="17" t="s">
         <v>2826</v>
       </c>
-      <c r="D681" s="17" t="s">
+      <c r="E681" s="7" t="s">
         <v>2827</v>
-      </c>
-      <c r="E681" s="7" t="s">
-        <v>2828</v>
       </c>
       <c r="F681" s="5">
         <v>92</v>
@@ -23117,19 +23110,19 @@
     </row>
     <row r="682" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A682" s="5" t="s">
+        <v>2828</v>
+      </c>
+      <c r="B682" s="6" t="s">
         <v>2829</v>
       </c>
-      <c r="B682" s="6" t="s">
+      <c r="C682" s="7" t="s">
         <v>2830</v>
       </c>
-      <c r="C682" s="7" t="s">
+      <c r="D682" s="17" t="s">
         <v>2831</v>
       </c>
-      <c r="D682" s="17" t="s">
+      <c r="E682" s="7" t="s">
         <v>2832</v>
-      </c>
-      <c r="E682" s="7" t="s">
-        <v>2833</v>
       </c>
       <c r="F682" s="5">
         <v>92</v>
@@ -23137,19 +23130,19 @@
     </row>
     <row r="683" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A683" s="5" t="s">
-        <v>2834</v>
+        <v>2833</v>
       </c>
       <c r="B683" s="6" t="s">
         <v>1150</v>
       </c>
       <c r="C683" s="7" t="s">
+        <v>2834</v>
+      </c>
+      <c r="D683" s="17" t="s">
         <v>2835</v>
       </c>
-      <c r="D683" s="17" t="s">
+      <c r="E683" s="7" t="s">
         <v>2836</v>
-      </c>
-      <c r="E683" s="7" t="s">
-        <v>2837</v>
       </c>
       <c r="F683" s="5">
         <v>92</v>
@@ -23157,7 +23150,7 @@
     </row>
     <row r="684" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A684" s="5" t="s">
-        <v>2838</v>
+        <v>2837</v>
       </c>
       <c r="B684" s="6" t="s">
         <v>840</v>
@@ -23166,10 +23159,10 @@
         <v>814</v>
       </c>
       <c r="D684" s="17" t="s">
+        <v>2838</v>
+      </c>
+      <c r="E684" s="7" t="s">
         <v>2839</v>
-      </c>
-      <c r="E684" s="7" t="s">
-        <v>2840</v>
       </c>
       <c r="F684" s="5">
         <v>92</v>
@@ -23177,19 +23170,19 @@
     </row>
     <row r="685" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A685" s="5" t="s">
-        <v>2841</v>
+        <v>2840</v>
       </c>
       <c r="B685" s="6" t="s">
         <v>899</v>
       </c>
       <c r="C685" s="7" t="s">
+        <v>2841</v>
+      </c>
+      <c r="D685" s="17" t="s">
+        <v>2843</v>
+      </c>
+      <c r="E685" s="7" t="s">
         <v>2842</v>
-      </c>
-      <c r="D685" s="17" t="s">
-        <v>2844</v>
-      </c>
-      <c r="E685" s="7" t="s">
-        <v>2843</v>
       </c>
       <c r="F685" s="5">
         <v>92</v>
@@ -23197,7 +23190,7 @@
     </row>
     <row r="686" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A686" s="5" t="s">
-        <v>2845</v>
+        <v>2844</v>
       </c>
       <c r="B686" s="6" t="s">
         <v>990</v>
@@ -23206,10 +23199,10 @@
         <v>248</v>
       </c>
       <c r="D686" s="17" t="s">
+        <v>2845</v>
+      </c>
+      <c r="E686" s="7" t="s">
         <v>2846</v>
-      </c>
-      <c r="E686" s="7" t="s">
-        <v>2847</v>
       </c>
       <c r="F686" s="5">
         <v>93</v>
@@ -23217,7 +23210,7 @@
     </row>
     <row r="687" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A687" s="5" t="s">
-        <v>2848</v>
+        <v>2847</v>
       </c>
       <c r="B687" s="6" t="s">
         <v>930</v>
@@ -23226,10 +23219,10 @@
         <v>991</v>
       </c>
       <c r="D687" s="17" t="s">
+        <v>2848</v>
+      </c>
+      <c r="E687" s="7" t="s">
         <v>2849</v>
-      </c>
-      <c r="E687" s="7" t="s">
-        <v>2850</v>
       </c>
       <c r="F687" s="5">
         <v>93</v>
@@ -23237,7 +23230,7 @@
     </row>
     <row r="688" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A688" s="5" t="s">
-        <v>2851</v>
+        <v>2850</v>
       </c>
       <c r="B688" s="6" t="s">
         <v>840</v>
@@ -23246,10 +23239,10 @@
         <v>248</v>
       </c>
       <c r="D688" s="17" t="s">
+        <v>2851</v>
+      </c>
+      <c r="E688" s="7" t="s">
         <v>2852</v>
-      </c>
-      <c r="E688" s="7" t="s">
-        <v>2853</v>
       </c>
       <c r="F688" s="5">
         <v>93</v>
@@ -23257,19 +23250,19 @@
     </row>
     <row r="689" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A689" s="5" t="s">
-        <v>2854</v>
+        <v>2853</v>
       </c>
       <c r="B689" s="6" t="s">
         <v>845</v>
       </c>
       <c r="C689" s="7" t="s">
+        <v>2854</v>
+      </c>
+      <c r="D689" s="17" t="s">
         <v>2855</v>
       </c>
-      <c r="D689" s="17" t="s">
+      <c r="E689" s="7" t="s">
         <v>2856</v>
-      </c>
-      <c r="E689" s="7" t="s">
-        <v>2857</v>
       </c>
       <c r="F689" s="5">
         <v>93</v>
@@ -23277,7 +23270,7 @@
     </row>
     <row r="690" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A690" s="5" t="s">
-        <v>2858</v>
+        <v>2857</v>
       </c>
       <c r="B690" s="6" t="s">
         <v>930</v>
@@ -23286,10 +23279,10 @@
         <v>1958</v>
       </c>
       <c r="D690" s="17" t="s">
+        <v>2858</v>
+      </c>
+      <c r="E690" s="7" t="s">
         <v>2859</v>
-      </c>
-      <c r="E690" s="7" t="s">
-        <v>2860</v>
       </c>
       <c r="F690" s="5">
         <v>93</v>
@@ -23297,7 +23290,7 @@
     </row>
     <row r="691" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A691" s="5" t="s">
-        <v>2861</v>
+        <v>2860</v>
       </c>
       <c r="B691" s="6" t="s">
         <v>921</v>
@@ -23306,10 +23299,10 @@
         <v>252</v>
       </c>
       <c r="D691" s="17" t="s">
+        <v>2861</v>
+      </c>
+      <c r="E691" s="7" t="s">
         <v>2862</v>
-      </c>
-      <c r="E691" s="7" t="s">
-        <v>2863</v>
       </c>
       <c r="F691" s="5">
         <v>93</v>
@@ -23317,7 +23310,7 @@
     </row>
     <row r="692" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A692" s="5" t="s">
-        <v>2864</v>
+        <v>2863</v>
       </c>
       <c r="B692" s="6" t="s">
         <v>999</v>
@@ -23326,10 +23319,10 @@
         <v>991</v>
       </c>
       <c r="D692" s="17" t="s">
-        <v>2866</v>
+        <v>2865</v>
       </c>
       <c r="E692" s="7" t="s">
-        <v>2865</v>
+        <v>2864</v>
       </c>
       <c r="F692" s="5">
         <v>93</v>
@@ -23337,19 +23330,19 @@
     </row>
     <row r="693" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A693" s="5" t="s">
-        <v>2867</v>
+        <v>2866</v>
       </c>
       <c r="B693" s="6" t="s">
         <v>342</v>
       </c>
       <c r="C693" s="7" t="s">
+        <v>2867</v>
+      </c>
+      <c r="D693" s="17" t="s">
         <v>2868</v>
       </c>
-      <c r="D693" s="17" t="s">
+      <c r="E693" s="7" t="s">
         <v>2869</v>
-      </c>
-      <c r="E693" s="7" t="s">
-        <v>2870</v>
       </c>
       <c r="F693" s="5">
         <v>93</v>
@@ -23357,19 +23350,19 @@
     </row>
     <row r="694" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A694" s="5" t="s">
-        <v>2871</v>
+        <v>2870</v>
       </c>
       <c r="B694" s="6" t="s">
         <v>1133</v>
       </c>
       <c r="C694" s="7" t="s">
+        <v>2871</v>
+      </c>
+      <c r="D694" s="17" t="s">
         <v>2872</v>
       </c>
-      <c r="D694" s="17" t="s">
+      <c r="E694" s="7" t="s">
         <v>2873</v>
-      </c>
-      <c r="E694" s="7" t="s">
-        <v>2874</v>
       </c>
       <c r="F694" s="5">
         <v>93</v>
@@ -23377,19 +23370,19 @@
     </row>
     <row r="695" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A695" s="5" t="s">
-        <v>2875</v>
+        <v>2874</v>
       </c>
       <c r="B695" s="6" t="s">
         <v>395</v>
       </c>
       <c r="C695" s="7" t="s">
+        <v>2875</v>
+      </c>
+      <c r="D695" s="17" t="s">
         <v>2876</v>
       </c>
-      <c r="D695" s="17" t="s">
+      <c r="E695" s="7" t="s">
         <v>2877</v>
-      </c>
-      <c r="E695" s="7" t="s">
-        <v>2878</v>
       </c>
       <c r="F695" s="5">
         <v>94</v>
@@ -23397,19 +23390,19 @@
     </row>
     <row r="696" spans="1:6" ht="105" x14ac:dyDescent="0.25">
       <c r="A696" s="5" t="s">
-        <v>2879</v>
+        <v>2878</v>
       </c>
       <c r="B696" s="6" t="s">
         <v>342</v>
       </c>
       <c r="C696" s="7" t="s">
+        <v>2879</v>
+      </c>
+      <c r="D696" s="17" t="s">
+        <v>2881</v>
+      </c>
+      <c r="E696" s="7" t="s">
         <v>2880</v>
-      </c>
-      <c r="D696" s="17" t="s">
-        <v>2882</v>
-      </c>
-      <c r="E696" s="7" t="s">
-        <v>2881</v>
       </c>
       <c r="F696" s="5">
         <v>94</v>
@@ -23417,19 +23410,19 @@
     </row>
     <row r="697" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A697" s="5" t="s">
-        <v>2883</v>
+        <v>2882</v>
       </c>
       <c r="B697" s="6" t="s">
         <v>287</v>
       </c>
       <c r="C697" s="7" t="s">
+        <v>2883</v>
+      </c>
+      <c r="D697" s="17" t="s">
         <v>2884</v>
       </c>
-      <c r="D697" s="17" t="s">
+      <c r="E697" s="7" t="s">
         <v>2885</v>
-      </c>
-      <c r="E697" s="7" t="s">
-        <v>2886</v>
       </c>
       <c r="F697" s="5">
         <v>94</v>
@@ -23437,19 +23430,19 @@
     </row>
     <row r="698" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A698" s="5" t="s">
+        <v>2886</v>
+      </c>
+      <c r="B698" s="7" t="s">
         <v>2887</v>
       </c>
-      <c r="B698" s="7" t="s">
+      <c r="C698" s="7" t="s">
         <v>2888</v>
       </c>
-      <c r="C698" s="7" t="s">
+      <c r="D698" s="17" t="s">
         <v>2889</v>
       </c>
-      <c r="D698" s="17" t="s">
+      <c r="E698" s="7" t="s">
         <v>2890</v>
-      </c>
-      <c r="E698" s="7" t="s">
-        <v>2891</v>
       </c>
       <c r="F698" s="5">
         <v>94</v>
@@ -23457,19 +23450,19 @@
     </row>
     <row r="699" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A699" s="5" t="s">
-        <v>2892</v>
+        <v>2891</v>
       </c>
       <c r="B699" s="6" t="s">
         <v>391</v>
       </c>
       <c r="C699" s="7" t="s">
+        <v>2892</v>
+      </c>
+      <c r="D699" s="17" t="s">
         <v>2893</v>
       </c>
-      <c r="D699" s="17" t="s">
+      <c r="E699" s="7" t="s">
         <v>2894</v>
-      </c>
-      <c r="E699" s="7" t="s">
-        <v>2895</v>
       </c>
       <c r="F699" s="5">
         <v>95</v>
@@ -23477,19 +23470,19 @@
     </row>
     <row r="700" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A700" s="5" t="s">
-        <v>2896</v>
+        <v>2895</v>
       </c>
       <c r="B700" s="6" t="s">
         <v>899</v>
       </c>
       <c r="C700" s="7" t="s">
+        <v>2896</v>
+      </c>
+      <c r="D700" s="17" t="s">
         <v>2897</v>
       </c>
-      <c r="D700" s="17" t="s">
+      <c r="E700" s="7" t="s">
         <v>2898</v>
-      </c>
-      <c r="E700" s="7" t="s">
-        <v>2899</v>
       </c>
       <c r="F700" s="5">
         <v>95</v>
@@ -23497,19 +23490,19 @@
     </row>
     <row r="701" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A701" s="5" t="s">
-        <v>2900</v>
+        <v>2899</v>
       </c>
       <c r="B701" s="6" t="s">
         <v>1133</v>
       </c>
       <c r="C701" s="7" t="s">
+        <v>2900</v>
+      </c>
+      <c r="D701" s="17" t="s">
         <v>2901</v>
       </c>
-      <c r="D701" s="17" t="s">
+      <c r="E701" s="7" t="s">
         <v>2902</v>
-      </c>
-      <c r="E701" s="7" t="s">
-        <v>2903</v>
       </c>
       <c r="F701" s="5">
         <v>95</v>
@@ -23517,19 +23510,19 @@
     </row>
     <row r="702" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A702" s="5" t="s">
-        <v>2904</v>
+        <v>2903</v>
       </c>
       <c r="B702" s="6" t="s">
         <v>845</v>
       </c>
       <c r="C702" s="7" t="s">
+        <v>2904</v>
+      </c>
+      <c r="D702" s="17" t="s">
+        <v>2906</v>
+      </c>
+      <c r="E702" s="7" t="s">
         <v>2905</v>
-      </c>
-      <c r="D702" s="17" t="s">
-        <v>2907</v>
-      </c>
-      <c r="E702" s="7" t="s">
-        <v>2906</v>
       </c>
       <c r="F702" s="5">
         <v>95</v>
@@ -23537,19 +23530,19 @@
     </row>
     <row r="703" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A703" s="5" t="s">
-        <v>2908</v>
+        <v>2907</v>
       </c>
       <c r="B703" s="6" t="s">
         <v>1140</v>
       </c>
       <c r="C703" s="7" t="s">
+        <v>2908</v>
+      </c>
+      <c r="D703" s="17" t="s">
         <v>2909</v>
       </c>
-      <c r="D703" s="17" t="s">
+      <c r="E703" s="7" t="s">
         <v>2910</v>
-      </c>
-      <c r="E703" s="7" t="s">
-        <v>2911</v>
       </c>
       <c r="F703" s="5">
         <v>95</v>
@@ -23557,19 +23550,19 @@
     </row>
     <row r="704" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A704" s="5" t="s">
-        <v>2912</v>
+        <v>2911</v>
       </c>
       <c r="B704" s="6" t="s">
         <v>342</v>
       </c>
       <c r="C704" s="7" t="s">
+        <v>2912</v>
+      </c>
+      <c r="D704" s="17" t="s">
         <v>2913</v>
       </c>
-      <c r="D704" s="17" t="s">
+      <c r="E704" s="7" t="s">
         <v>2914</v>
-      </c>
-      <c r="E704" s="7" t="s">
-        <v>2915</v>
       </c>
       <c r="F704" s="5">
         <v>96</v>
@@ -23577,19 +23570,19 @@
     </row>
     <row r="705" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A705" s="5" t="s">
-        <v>2916</v>
+        <v>2915</v>
       </c>
       <c r="B705" s="6" t="s">
         <v>342</v>
       </c>
       <c r="C705" s="7" t="s">
+        <v>2916</v>
+      </c>
+      <c r="D705" s="17" t="s">
         <v>2917</v>
       </c>
-      <c r="D705" s="17" t="s">
+      <c r="E705" s="7" t="s">
         <v>2918</v>
-      </c>
-      <c r="E705" s="7" t="s">
-        <v>2919</v>
       </c>
       <c r="F705" s="5">
         <v>96</v>
@@ -23597,19 +23590,19 @@
     </row>
     <row r="706" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A706" s="5" t="s">
-        <v>2581</v>
+        <v>2580</v>
       </c>
       <c r="B706" s="6" t="s">
         <v>1704</v>
       </c>
       <c r="C706" s="7" t="s">
+        <v>2919</v>
+      </c>
+      <c r="D706" s="17" t="s">
+        <v>2582</v>
+      </c>
+      <c r="E706" s="7" t="s">
         <v>2920</v>
-      </c>
-      <c r="D706" s="17" t="s">
-        <v>2583</v>
-      </c>
-      <c r="E706" s="7" t="s">
-        <v>2921</v>
       </c>
       <c r="F706" s="5">
         <v>96</v>
@@ -23617,19 +23610,19 @@
     </row>
     <row r="707" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A707" s="5" t="s">
-        <v>2922</v>
+        <v>2921</v>
       </c>
       <c r="B707" s="6" t="s">
         <v>1984</v>
       </c>
       <c r="C707" s="7" t="s">
+        <v>2922</v>
+      </c>
+      <c r="D707" s="17" t="s">
         <v>2923</v>
       </c>
-      <c r="D707" s="17" t="s">
+      <c r="E707" s="7" t="s">
         <v>2924</v>
-      </c>
-      <c r="E707" s="7" t="s">
-        <v>2925</v>
       </c>
       <c r="F707" s="5">
         <v>96</v>
@@ -23637,19 +23630,19 @@
     </row>
     <row r="708" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A708" s="5" t="s">
+        <v>2925</v>
+      </c>
+      <c r="B708" s="6" t="s">
         <v>2926</v>
       </c>
-      <c r="B708" s="6" t="s">
+      <c r="C708" s="7" t="s">
         <v>2927</v>
       </c>
-      <c r="C708" s="7" t="s">
+      <c r="D708" s="17" t="s">
         <v>2928</v>
       </c>
-      <c r="D708" s="17" t="s">
+      <c r="E708" s="7" t="s">
         <v>2929</v>
-      </c>
-      <c r="E708" s="7" t="s">
-        <v>2930</v>
       </c>
       <c r="F708" s="5">
         <v>97</v>
@@ -23657,19 +23650,19 @@
     </row>
     <row r="709" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A709" s="5" t="s">
+        <v>2930</v>
+      </c>
+      <c r="B709" s="6" t="s">
         <v>2931</v>
       </c>
-      <c r="B709" s="6" t="s">
+      <c r="C709" s="7" t="s">
         <v>2932</v>
       </c>
-      <c r="C709" s="7" t="s">
+      <c r="D709" s="17" t="s">
         <v>2933</v>
       </c>
-      <c r="D709" s="17" t="s">
+      <c r="E709" s="7" t="s">
         <v>2934</v>
-      </c>
-      <c r="E709" s="7" t="s">
-        <v>2935</v>
       </c>
       <c r="F709" s="5">
         <v>97</v>
@@ -23677,19 +23670,19 @@
     </row>
     <row r="710" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A710" s="5" t="s">
+        <v>2935</v>
+      </c>
+      <c r="B710" s="6" t="s">
         <v>2936</v>
       </c>
-      <c r="B710" s="6" t="s">
+      <c r="C710" s="7" t="s">
         <v>2937</v>
       </c>
-      <c r="C710" s="7" t="s">
+      <c r="D710" s="17" t="s">
         <v>2938</v>
       </c>
-      <c r="D710" s="17" t="s">
+      <c r="E710" s="7" t="s">
         <v>2939</v>
-      </c>
-      <c r="E710" s="7" t="s">
-        <v>2940</v>
       </c>
       <c r="F710" s="5">
         <v>97</v>
@@ -23697,19 +23690,19 @@
     </row>
     <row r="711" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A711" s="5" t="s">
+        <v>2940</v>
+      </c>
+      <c r="B711" s="6" t="s">
         <v>2941</v>
       </c>
-      <c r="B711" s="6" t="s">
+      <c r="C711" s="7" t="s">
         <v>2942</v>
       </c>
-      <c r="C711" s="7" t="s">
+      <c r="D711" s="17" t="s">
         <v>2943</v>
       </c>
-      <c r="D711" s="17" t="s">
+      <c r="E711" s="7" t="s">
         <v>2944</v>
-      </c>
-      <c r="E711" s="7" t="s">
-        <v>2945</v>
       </c>
       <c r="F711" s="5">
         <v>97</v>
@@ -23717,19 +23710,19 @@
     </row>
     <row r="712" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A712" s="5" t="s">
+        <v>2945</v>
+      </c>
+      <c r="B712" s="6" t="s">
+        <v>2941</v>
+      </c>
+      <c r="C712" s="7" t="s">
+        <v>2942</v>
+      </c>
+      <c r="D712" s="17" t="s">
         <v>2946</v>
       </c>
-      <c r="B712" s="6" t="s">
-        <v>2942</v>
-      </c>
-      <c r="C712" s="7" t="s">
-        <v>2943</v>
-      </c>
-      <c r="D712" s="17" t="s">
+      <c r="E712" s="7" t="s">
         <v>2947</v>
-      </c>
-      <c r="E712" s="7" t="s">
-        <v>2948</v>
       </c>
       <c r="F712" s="5">
         <v>97</v>
@@ -23737,19 +23730,19 @@
     </row>
     <row r="713" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A713" s="5" t="s">
-        <v>2949</v>
+        <v>2948</v>
       </c>
       <c r="B713" s="6" t="s">
         <v>1051</v>
       </c>
       <c r="C713" s="7" t="s">
+        <v>2949</v>
+      </c>
+      <c r="D713" s="17" t="s">
         <v>2950</v>
       </c>
-      <c r="D713" s="17" t="s">
+      <c r="E713" s="7" t="s">
         <v>2951</v>
-      </c>
-      <c r="E713" s="7" t="s">
-        <v>2952</v>
       </c>
       <c r="F713" s="5">
         <v>97</v>
@@ -23757,19 +23750,19 @@
     </row>
     <row r="714" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A714" s="5" t="s">
-        <v>2953</v>
+        <v>2952</v>
       </c>
       <c r="B714" s="6" t="s">
         <v>1497</v>
       </c>
       <c r="C714" s="7" t="s">
+        <v>2953</v>
+      </c>
+      <c r="D714" s="17" t="s">
         <v>2954</v>
       </c>
-      <c r="D714" s="17" t="s">
+      <c r="E714" s="7" t="s">
         <v>2955</v>
-      </c>
-      <c r="E714" s="7" t="s">
-        <v>2956</v>
       </c>
       <c r="F714" s="5">
         <v>97</v>
@@ -23777,5079 +23770,23 @@
     </row>
     <row r="715" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A715" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="B715" s="6" t="s">
         <v>1056</v>
       </c>
       <c r="C715" s="7" t="s">
+        <v>2957</v>
+      </c>
+      <c r="D715" s="17" t="s">
         <v>2958</v>
       </c>
-      <c r="D715" s="17" t="s">
+      <c r="E715" s="7" t="s">
         <v>2959</v>
-      </c>
-      <c r="E715" s="7" t="s">
-        <v>2960</v>
       </c>
       <c r="F715" s="5">
         <v>97</v>
       </c>
-    </row>
-    <row r="716" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A716" s="5"/>
-      <c r="B716" s="6"/>
-      <c r="C716" s="7"/>
-      <c r="D716" s="17"/>
-      <c r="E716" s="7"/>
-      <c r="F716" s="5"/>
-    </row>
-    <row r="717" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A717" s="5"/>
-      <c r="B717" s="6"/>
-      <c r="C717" s="7"/>
-      <c r="D717" s="17"/>
-      <c r="E717" s="7"/>
-      <c r="F717" s="5"/>
-    </row>
-    <row r="718" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A718" s="5"/>
-      <c r="B718" s="6"/>
-      <c r="C718" s="7"/>
-      <c r="D718" s="17"/>
-      <c r="E718" s="7"/>
-      <c r="F718" s="5"/>
-    </row>
-    <row r="719" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A719" s="5"/>
-      <c r="B719" s="6"/>
-      <c r="C719" s="7"/>
-      <c r="D719" s="17"/>
-      <c r="E719" s="7"/>
-      <c r="F719" s="5"/>
-    </row>
-    <row r="720" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A720" s="5"/>
-      <c r="B720" s="6"/>
-      <c r="C720" s="7"/>
-      <c r="D720" s="17"/>
-      <c r="E720" s="7"/>
-      <c r="F720" s="5"/>
-    </row>
-    <row r="721" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A721" s="5"/>
-      <c r="B721" s="6"/>
-      <c r="C721" s="7"/>
-      <c r="D721" s="17"/>
-      <c r="E721" s="7"/>
-      <c r="F721" s="5"/>
-    </row>
-    <row r="722" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A722" s="5"/>
-      <c r="B722" s="6"/>
-      <c r="C722" s="7"/>
-      <c r="D722" s="17"/>
-      <c r="E722" s="7"/>
-      <c r="F722" s="5"/>
-    </row>
-    <row r="723" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A723" s="5"/>
-      <c r="B723" s="6"/>
-      <c r="C723" s="7"/>
-      <c r="D723" s="17"/>
-      <c r="E723" s="7"/>
-      <c r="F723" s="5"/>
-    </row>
-    <row r="724" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A724" s="5"/>
-      <c r="B724" s="6"/>
-      <c r="C724" s="7"/>
-      <c r="D724" s="17"/>
-      <c r="E724" s="7"/>
-      <c r="F724" s="5"/>
-    </row>
-    <row r="725" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A725" s="5"/>
-      <c r="B725" s="6"/>
-      <c r="C725" s="7"/>
-      <c r="D725" s="17"/>
-      <c r="E725" s="7"/>
-      <c r="F725" s="5"/>
-    </row>
-    <row r="726" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A726" s="5"/>
-      <c r="B726" s="6"/>
-      <c r="C726" s="7"/>
-      <c r="D726" s="17"/>
-      <c r="E726" s="7"/>
-      <c r="F726" s="5"/>
-    </row>
-    <row r="727" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A727" s="5"/>
-      <c r="B727" s="6"/>
-      <c r="C727" s="7"/>
-      <c r="D727" s="17"/>
-      <c r="E727" s="7"/>
-      <c r="F727" s="5"/>
-    </row>
-    <row r="728" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A728" s="5"/>
-      <c r="B728" s="6"/>
-      <c r="C728" s="7"/>
-      <c r="D728" s="17"/>
-      <c r="E728" s="7"/>
-      <c r="F728" s="5"/>
-    </row>
-    <row r="729" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A729" s="5"/>
-      <c r="B729" s="6"/>
-      <c r="C729" s="7"/>
-      <c r="D729" s="17"/>
-      <c r="E729" s="7"/>
-      <c r="F729" s="5"/>
-    </row>
-    <row r="730" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A730" s="5"/>
-      <c r="B730" s="6"/>
-      <c r="C730" s="7"/>
-      <c r="D730" s="17"/>
-      <c r="E730" s="7"/>
-      <c r="F730" s="5"/>
-    </row>
-    <row r="731" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A731" s="5"/>
-      <c r="B731" s="6"/>
-      <c r="C731" s="7"/>
-      <c r="D731" s="17"/>
-      <c r="E731" s="7"/>
-      <c r="F731" s="5"/>
-    </row>
-    <row r="732" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A732" s="5"/>
-      <c r="B732" s="6"/>
-      <c r="C732" s="7"/>
-      <c r="D732" s="17"/>
-      <c r="E732" s="7"/>
-      <c r="F732" s="5"/>
-    </row>
-    <row r="733" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A733" s="5"/>
-      <c r="B733" s="6"/>
-      <c r="C733" s="7"/>
-      <c r="D733" s="17"/>
-      <c r="E733" s="7"/>
-      <c r="F733" s="5"/>
-    </row>
-    <row r="734" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A734" s="5"/>
-      <c r="B734" s="6"/>
-      <c r="C734" s="7"/>
-      <c r="D734" s="17"/>
-      <c r="E734" s="7"/>
-      <c r="F734" s="5"/>
-    </row>
-    <row r="735" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A735" s="5"/>
-      <c r="B735" s="6"/>
-      <c r="C735" s="7"/>
-      <c r="D735" s="17"/>
-      <c r="E735" s="7"/>
-      <c r="F735" s="5"/>
-    </row>
-    <row r="736" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A736" s="5"/>
-      <c r="B736" s="6"/>
-      <c r="C736" s="7"/>
-      <c r="D736" s="17"/>
-      <c r="E736" s="7"/>
-      <c r="F736" s="5"/>
-    </row>
-    <row r="737" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A737" s="5"/>
-      <c r="B737" s="6"/>
-      <c r="C737" s="7"/>
-      <c r="D737" s="17"/>
-      <c r="E737" s="7"/>
-      <c r="F737" s="5"/>
-    </row>
-    <row r="738" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A738" s="5"/>
-      <c r="B738" s="6"/>
-      <c r="C738" s="7"/>
-      <c r="D738" s="17"/>
-      <c r="E738" s="7"/>
-      <c r="F738" s="5"/>
-    </row>
-    <row r="739" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A739" s="5"/>
-      <c r="B739" s="6"/>
-      <c r="C739" s="7"/>
-      <c r="D739" s="17"/>
-      <c r="E739" s="7"/>
-      <c r="F739" s="5"/>
-    </row>
-    <row r="740" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A740" s="5"/>
-      <c r="B740" s="6"/>
-      <c r="C740" s="7"/>
-      <c r="D740" s="17"/>
-      <c r="E740" s="7"/>
-      <c r="F740" s="5"/>
-    </row>
-    <row r="741" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A741" s="5"/>
-      <c r="B741" s="6"/>
-      <c r="C741" s="7"/>
-      <c r="D741" s="17"/>
-      <c r="E741" s="7"/>
-      <c r="F741" s="5"/>
-    </row>
-    <row r="742" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A742" s="5"/>
-      <c r="B742" s="6"/>
-      <c r="C742" s="7"/>
-      <c r="D742" s="17"/>
-      <c r="E742" s="7"/>
-      <c r="F742" s="5"/>
-    </row>
-    <row r="743" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A743" s="5"/>
-      <c r="B743" s="6"/>
-      <c r="C743" s="7"/>
-      <c r="D743" s="17"/>
-      <c r="E743" s="7"/>
-      <c r="F743" s="5"/>
-    </row>
-    <row r="744" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A744" s="5"/>
-      <c r="B744" s="6"/>
-      <c r="C744" s="7"/>
-      <c r="D744" s="17"/>
-      <c r="E744" s="7"/>
-      <c r="F744" s="5"/>
-    </row>
-    <row r="745" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A745" s="5"/>
-      <c r="B745" s="6"/>
-      <c r="C745" s="7"/>
-      <c r="D745" s="17"/>
-      <c r="E745" s="7"/>
-      <c r="F745" s="5"/>
-    </row>
-    <row r="746" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A746" s="5"/>
-      <c r="B746" s="6"/>
-      <c r="C746" s="7"/>
-      <c r="D746" s="17"/>
-      <c r="E746" s="7"/>
-      <c r="F746" s="5"/>
-    </row>
-    <row r="747" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A747" s="5"/>
-      <c r="B747" s="6"/>
-      <c r="C747" s="7"/>
-      <c r="D747" s="17"/>
-      <c r="E747" s="7"/>
-      <c r="F747" s="5"/>
-    </row>
-    <row r="748" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A748" s="5"/>
-      <c r="B748" s="6"/>
-      <c r="C748" s="7"/>
-      <c r="D748" s="17"/>
-      <c r="E748" s="7"/>
-      <c r="F748" s="5"/>
-    </row>
-    <row r="749" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A749" s="5"/>
-      <c r="B749" s="6"/>
-      <c r="C749" s="7"/>
-      <c r="D749" s="17"/>
-      <c r="E749" s="7"/>
-      <c r="F749" s="5"/>
-    </row>
-    <row r="750" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A750" s="5"/>
-      <c r="B750" s="6"/>
-      <c r="C750" s="7"/>
-      <c r="D750" s="17"/>
-      <c r="E750" s="7"/>
-      <c r="F750" s="5"/>
-    </row>
-    <row r="751" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A751" s="5"/>
-      <c r="B751" s="6"/>
-      <c r="C751" s="7"/>
-      <c r="D751" s="17"/>
-      <c r="E751" s="7"/>
-      <c r="F751" s="5"/>
-    </row>
-    <row r="752" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A752" s="5"/>
-      <c r="B752" s="6"/>
-      <c r="C752" s="7"/>
-      <c r="D752" s="17"/>
-      <c r="E752" s="7"/>
-      <c r="F752" s="5"/>
-    </row>
-    <row r="753" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A753" s="5"/>
-      <c r="B753" s="6"/>
-      <c r="C753" s="7"/>
-      <c r="D753" s="17"/>
-      <c r="E753" s="7"/>
-      <c r="F753" s="5"/>
-    </row>
-    <row r="754" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A754" s="5"/>
-      <c r="B754" s="6"/>
-      <c r="C754" s="7"/>
-      <c r="D754" s="17"/>
-      <c r="E754" s="7"/>
-      <c r="F754" s="5"/>
-    </row>
-    <row r="755" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A755" s="5"/>
-      <c r="B755" s="6"/>
-      <c r="C755" s="7"/>
-      <c r="D755" s="17"/>
-      <c r="E755" s="7"/>
-      <c r="F755" s="5"/>
-    </row>
-    <row r="756" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A756" s="5"/>
-      <c r="B756" s="6"/>
-      <c r="C756" s="7"/>
-      <c r="D756" s="17"/>
-      <c r="E756" s="7"/>
-      <c r="F756" s="5"/>
-    </row>
-    <row r="757" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A757" s="5"/>
-      <c r="B757" s="6"/>
-      <c r="C757" s="7"/>
-      <c r="D757" s="17"/>
-      <c r="E757" s="7"/>
-      <c r="F757" s="5"/>
-    </row>
-    <row r="758" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A758" s="5"/>
-      <c r="B758" s="6"/>
-      <c r="C758" s="7"/>
-      <c r="D758" s="17"/>
-      <c r="E758" s="7"/>
-      <c r="F758" s="5"/>
-    </row>
-    <row r="759" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A759" s="5"/>
-      <c r="B759" s="6"/>
-      <c r="C759" s="7"/>
-      <c r="D759" s="17"/>
-      <c r="E759" s="7"/>
-      <c r="F759" s="5"/>
-    </row>
-    <row r="760" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A760" s="5"/>
-      <c r="B760" s="6"/>
-      <c r="C760" s="7"/>
-      <c r="D760" s="17"/>
-      <c r="E760" s="7"/>
-      <c r="F760" s="5"/>
-    </row>
-    <row r="761" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A761" s="5"/>
-      <c r="B761" s="6"/>
-      <c r="C761" s="7"/>
-      <c r="D761" s="17"/>
-      <c r="E761" s="7"/>
-      <c r="F761" s="5"/>
-    </row>
-    <row r="762" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A762" s="5"/>
-      <c r="B762" s="6"/>
-      <c r="C762" s="7"/>
-      <c r="D762" s="17"/>
-      <c r="E762" s="7"/>
-      <c r="F762" s="5"/>
-    </row>
-    <row r="763" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A763" s="5"/>
-      <c r="B763" s="6"/>
-      <c r="C763" s="7"/>
-      <c r="D763" s="17"/>
-      <c r="E763" s="7"/>
-      <c r="F763" s="5"/>
-    </row>
-    <row r="764" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A764" s="5"/>
-      <c r="B764" s="6"/>
-      <c r="C764" s="7"/>
-      <c r="D764" s="17"/>
-      <c r="E764" s="7"/>
-      <c r="F764" s="5"/>
-    </row>
-    <row r="765" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A765" s="5"/>
-      <c r="B765" s="6"/>
-      <c r="C765" s="7"/>
-      <c r="D765" s="17"/>
-      <c r="E765" s="7"/>
-      <c r="F765" s="5"/>
-    </row>
-    <row r="766" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A766" s="5"/>
-      <c r="B766" s="6"/>
-      <c r="C766" s="7"/>
-      <c r="D766" s="17"/>
-      <c r="E766" s="7"/>
-      <c r="F766" s="5"/>
-    </row>
-    <row r="767" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A767" s="5"/>
-      <c r="B767" s="6"/>
-      <c r="C767" s="7"/>
-      <c r="D767" s="17"/>
-      <c r="E767" s="7"/>
-      <c r="F767" s="5"/>
-    </row>
-    <row r="768" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A768" s="5"/>
-      <c r="B768" s="6"/>
-      <c r="C768" s="7"/>
-      <c r="D768" s="17"/>
-      <c r="E768" s="7"/>
-      <c r="F768" s="5"/>
-    </row>
-    <row r="769" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A769" s="5"/>
-      <c r="B769" s="6"/>
-      <c r="C769" s="7"/>
-      <c r="D769" s="17"/>
-      <c r="E769" s="7"/>
-      <c r="F769" s="5"/>
-    </row>
-    <row r="770" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A770" s="5"/>
-      <c r="B770" s="6"/>
-      <c r="C770" s="7"/>
-      <c r="D770" s="17"/>
-      <c r="E770" s="7"/>
-      <c r="F770" s="5"/>
-    </row>
-    <row r="771" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A771" s="5"/>
-      <c r="B771" s="6"/>
-      <c r="C771" s="7"/>
-      <c r="D771" s="17"/>
-      <c r="E771" s="7"/>
-      <c r="F771" s="5"/>
-    </row>
-    <row r="772" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A772" s="5"/>
-      <c r="B772" s="6"/>
-      <c r="C772" s="7"/>
-      <c r="D772" s="17"/>
-      <c r="E772" s="7"/>
-      <c r="F772" s="5"/>
-    </row>
-    <row r="773" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A773" s="5"/>
-      <c r="B773" s="6"/>
-      <c r="C773" s="7"/>
-      <c r="D773" s="17"/>
-      <c r="E773" s="7"/>
-      <c r="F773" s="5"/>
-    </row>
-    <row r="774" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A774" s="5"/>
-      <c r="B774" s="6"/>
-      <c r="C774" s="7"/>
-      <c r="D774" s="17"/>
-      <c r="E774" s="7"/>
-      <c r="F774" s="5"/>
-    </row>
-    <row r="775" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A775" s="5"/>
-      <c r="B775" s="6"/>
-      <c r="C775" s="7"/>
-      <c r="D775" s="17"/>
-      <c r="E775" s="7"/>
-      <c r="F775" s="5"/>
-    </row>
-    <row r="776" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A776" s="5"/>
-      <c r="B776" s="6"/>
-      <c r="C776" s="7"/>
-      <c r="D776" s="17"/>
-      <c r="E776" s="7"/>
-      <c r="F776" s="5"/>
-    </row>
-    <row r="777" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A777" s="5"/>
-      <c r="B777" s="6"/>
-      <c r="C777" s="7"/>
-      <c r="D777" s="17"/>
-      <c r="E777" s="7"/>
-      <c r="F777" s="5"/>
-    </row>
-    <row r="778" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A778" s="5"/>
-      <c r="B778" s="6"/>
-      <c r="C778" s="7"/>
-      <c r="D778" s="17"/>
-      <c r="E778" s="7"/>
-      <c r="F778" s="5"/>
-    </row>
-    <row r="779" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A779" s="5"/>
-      <c r="B779" s="6"/>
-      <c r="C779" s="7"/>
-      <c r="D779" s="17"/>
-      <c r="E779" s="7"/>
-      <c r="F779" s="5"/>
-    </row>
-    <row r="780" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A780" s="5"/>
-      <c r="B780" s="6"/>
-      <c r="C780" s="7"/>
-      <c r="D780" s="17"/>
-      <c r="E780" s="7"/>
-      <c r="F780" s="5"/>
-    </row>
-    <row r="781" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A781" s="5"/>
-      <c r="B781" s="6"/>
-      <c r="C781" s="7"/>
-      <c r="D781" s="17"/>
-      <c r="E781" s="7"/>
-      <c r="F781" s="5"/>
-    </row>
-    <row r="782" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A782" s="5"/>
-      <c r="B782" s="6"/>
-      <c r="C782" s="7"/>
-      <c r="D782" s="17"/>
-      <c r="E782" s="7"/>
-      <c r="F782" s="5"/>
-    </row>
-    <row r="783" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A783" s="5"/>
-      <c r="B783" s="6"/>
-      <c r="C783" s="7"/>
-      <c r="D783" s="17"/>
-      <c r="E783" s="7"/>
-      <c r="F783" s="5"/>
-    </row>
-    <row r="784" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A784" s="5"/>
-      <c r="B784" s="6"/>
-      <c r="C784" s="7"/>
-      <c r="D784" s="17"/>
-      <c r="E784" s="7"/>
-      <c r="F784" s="5"/>
-    </row>
-    <row r="785" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A785" s="5"/>
-      <c r="B785" s="6"/>
-      <c r="C785" s="7"/>
-      <c r="D785" s="17"/>
-      <c r="E785" s="7"/>
-      <c r="F785" s="5"/>
-    </row>
-    <row r="786" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A786" s="5"/>
-      <c r="B786" s="6"/>
-      <c r="C786" s="7"/>
-      <c r="D786" s="17"/>
-      <c r="E786" s="7"/>
-      <c r="F786" s="5"/>
-    </row>
-    <row r="787" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A787" s="5"/>
-      <c r="B787" s="6"/>
-      <c r="C787" s="7"/>
-      <c r="D787" s="17"/>
-      <c r="E787" s="7"/>
-      <c r="F787" s="5"/>
-    </row>
-    <row r="788" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A788" s="5"/>
-      <c r="B788" s="6"/>
-      <c r="C788" s="7"/>
-      <c r="D788" s="17"/>
-      <c r="E788" s="7"/>
-      <c r="F788" s="5"/>
-    </row>
-    <row r="789" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A789" s="5"/>
-      <c r="B789" s="6"/>
-      <c r="C789" s="7"/>
-      <c r="D789" s="17"/>
-      <c r="E789" s="7"/>
-      <c r="F789" s="5"/>
-    </row>
-    <row r="790" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A790" s="5"/>
-      <c r="B790" s="6"/>
-      <c r="C790" s="7"/>
-      <c r="D790" s="17"/>
-      <c r="E790" s="7"/>
-      <c r="F790" s="5"/>
-    </row>
-    <row r="791" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A791" s="5"/>
-      <c r="B791" s="6"/>
-      <c r="C791" s="7"/>
-      <c r="D791" s="17"/>
-      <c r="E791" s="7"/>
-      <c r="F791" s="5"/>
-    </row>
-    <row r="792" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A792" s="5"/>
-      <c r="B792" s="6"/>
-      <c r="C792" s="7"/>
-      <c r="D792" s="17"/>
-      <c r="E792" s="7"/>
-      <c r="F792" s="5"/>
-    </row>
-    <row r="793" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A793" s="5"/>
-      <c r="B793" s="6"/>
-      <c r="C793" s="7"/>
-      <c r="D793" s="17"/>
-      <c r="E793" s="7"/>
-      <c r="F793" s="5"/>
-    </row>
-    <row r="794" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A794" s="5"/>
-      <c r="B794" s="6"/>
-      <c r="C794" s="7"/>
-      <c r="D794" s="17"/>
-      <c r="E794" s="7"/>
-      <c r="F794" s="5"/>
-    </row>
-    <row r="795" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A795" s="5"/>
-      <c r="B795" s="6"/>
-      <c r="C795" s="7"/>
-      <c r="D795" s="17"/>
-      <c r="E795" s="7"/>
-      <c r="F795" s="5"/>
-    </row>
-    <row r="796" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A796" s="5"/>
-      <c r="B796" s="6"/>
-      <c r="C796" s="7"/>
-      <c r="D796" s="17"/>
-      <c r="E796" s="7"/>
-      <c r="F796" s="5"/>
-    </row>
-    <row r="797" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A797" s="5"/>
-      <c r="B797" s="6"/>
-      <c r="C797" s="7"/>
-      <c r="D797" s="17"/>
-      <c r="E797" s="7"/>
-      <c r="F797" s="5"/>
-    </row>
-    <row r="798" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A798" s="5"/>
-      <c r="B798" s="6"/>
-      <c r="C798" s="7"/>
-      <c r="D798" s="17"/>
-      <c r="E798" s="7"/>
-      <c r="F798" s="5"/>
-    </row>
-    <row r="799" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A799" s="5"/>
-      <c r="B799" s="6"/>
-      <c r="C799" s="7"/>
-      <c r="D799" s="17"/>
-      <c r="E799" s="7"/>
-      <c r="F799" s="5"/>
-    </row>
-    <row r="800" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A800" s="5"/>
-      <c r="B800" s="6"/>
-      <c r="C800" s="7"/>
-      <c r="D800" s="17"/>
-      <c r="E800" s="7"/>
-      <c r="F800" s="5"/>
-    </row>
-    <row r="801" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A801" s="5"/>
-      <c r="B801" s="6"/>
-      <c r="C801" s="7"/>
-      <c r="D801" s="17"/>
-      <c r="E801" s="7"/>
-      <c r="F801" s="5"/>
-    </row>
-    <row r="802" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A802" s="5"/>
-      <c r="B802" s="6"/>
-      <c r="C802" s="7"/>
-      <c r="D802" s="17"/>
-      <c r="E802" s="7"/>
-      <c r="F802" s="5"/>
-    </row>
-    <row r="803" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A803" s="5"/>
-      <c r="B803" s="6"/>
-      <c r="C803" s="7"/>
-      <c r="D803" s="17"/>
-      <c r="E803" s="7"/>
-      <c r="F803" s="5"/>
-    </row>
-    <row r="804" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A804" s="5"/>
-      <c r="B804" s="6"/>
-      <c r="C804" s="7"/>
-      <c r="D804" s="17"/>
-      <c r="E804" s="7"/>
-      <c r="F804" s="5"/>
-    </row>
-    <row r="805" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A805" s="5"/>
-      <c r="B805" s="6"/>
-      <c r="C805" s="7"/>
-      <c r="D805" s="17"/>
-      <c r="E805" s="7"/>
-      <c r="F805" s="5"/>
-    </row>
-    <row r="806" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A806" s="5"/>
-      <c r="B806" s="6"/>
-      <c r="C806" s="7"/>
-      <c r="D806" s="17"/>
-      <c r="E806" s="7"/>
-      <c r="F806" s="5"/>
-    </row>
-    <row r="807" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A807" s="5"/>
-      <c r="B807" s="6"/>
-      <c r="C807" s="7"/>
-      <c r="D807" s="17"/>
-      <c r="E807" s="7"/>
-      <c r="F807" s="5"/>
-    </row>
-    <row r="808" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A808" s="5"/>
-      <c r="B808" s="6"/>
-      <c r="C808" s="7"/>
-      <c r="D808" s="17"/>
-      <c r="E808" s="7"/>
-      <c r="F808" s="5"/>
-    </row>
-    <row r="809" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A809" s="5"/>
-      <c r="B809" s="6"/>
-      <c r="C809" s="7"/>
-      <c r="D809" s="17"/>
-      <c r="E809" s="7"/>
-      <c r="F809" s="5"/>
-    </row>
-    <row r="810" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A810" s="5"/>
-      <c r="B810" s="6"/>
-      <c r="C810" s="7"/>
-      <c r="D810" s="17"/>
-      <c r="E810" s="7"/>
-      <c r="F810" s="5"/>
-    </row>
-    <row r="811" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A811" s="5"/>
-      <c r="B811" s="6"/>
-      <c r="C811" s="7"/>
-      <c r="D811" s="17"/>
-      <c r="E811" s="7"/>
-      <c r="F811" s="5"/>
-    </row>
-    <row r="812" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A812" s="5"/>
-      <c r="B812" s="6"/>
-      <c r="C812" s="7"/>
-      <c r="D812" s="17"/>
-      <c r="E812" s="7"/>
-      <c r="F812" s="5"/>
-    </row>
-    <row r="813" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A813" s="5"/>
-      <c r="B813" s="6"/>
-      <c r="C813" s="7"/>
-      <c r="D813" s="17"/>
-      <c r="E813" s="7"/>
-      <c r="F813" s="5"/>
-    </row>
-    <row r="814" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A814" s="5"/>
-      <c r="B814" s="6"/>
-      <c r="C814" s="7"/>
-      <c r="D814" s="17"/>
-      <c r="E814" s="7"/>
-      <c r="F814" s="5"/>
-    </row>
-    <row r="815" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A815" s="5"/>
-      <c r="B815" s="6"/>
-      <c r="C815" s="7"/>
-      <c r="D815" s="17"/>
-      <c r="E815" s="7"/>
-      <c r="F815" s="5"/>
-    </row>
-    <row r="816" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A816" s="5"/>
-      <c r="B816" s="6"/>
-      <c r="C816" s="7"/>
-      <c r="D816" s="17"/>
-      <c r="E816" s="7"/>
-      <c r="F816" s="5"/>
-    </row>
-    <row r="817" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A817" s="5"/>
-      <c r="B817" s="6"/>
-      <c r="C817" s="7"/>
-      <c r="D817" s="17"/>
-      <c r="E817" s="7"/>
-      <c r="F817" s="5"/>
-    </row>
-    <row r="818" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A818" s="5"/>
-      <c r="B818" s="6"/>
-      <c r="C818" s="7"/>
-      <c r="D818" s="17"/>
-      <c r="E818" s="7"/>
-      <c r="F818" s="5"/>
-    </row>
-    <row r="819" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A819" s="5"/>
-      <c r="B819" s="6"/>
-      <c r="C819" s="7"/>
-      <c r="D819" s="17"/>
-      <c r="E819" s="7"/>
-      <c r="F819" s="5"/>
-    </row>
-    <row r="820" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A820" s="5"/>
-      <c r="B820" s="6"/>
-      <c r="C820" s="7"/>
-      <c r="D820" s="17"/>
-      <c r="E820" s="7"/>
-      <c r="F820" s="5"/>
-    </row>
-    <row r="821" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A821" s="5"/>
-      <c r="B821" s="6"/>
-      <c r="C821" s="7"/>
-      <c r="D821" s="17"/>
-      <c r="E821" s="7"/>
-      <c r="F821" s="5"/>
-    </row>
-    <row r="822" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A822" s="5"/>
-      <c r="B822" s="6"/>
-      <c r="C822" s="7"/>
-      <c r="D822" s="17"/>
-      <c r="E822" s="7"/>
-      <c r="F822" s="5"/>
-    </row>
-    <row r="823" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A823" s="5"/>
-      <c r="B823" s="6"/>
-      <c r="C823" s="7"/>
-      <c r="D823" s="17"/>
-      <c r="E823" s="7"/>
-      <c r="F823" s="5"/>
-    </row>
-    <row r="824" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A824" s="5"/>
-      <c r="B824" s="6"/>
-      <c r="C824" s="7"/>
-      <c r="D824" s="17"/>
-      <c r="E824" s="7"/>
-      <c r="F824" s="5"/>
-    </row>
-    <row r="825" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A825" s="5"/>
-      <c r="B825" s="6"/>
-      <c r="C825" s="7"/>
-      <c r="D825" s="17"/>
-      <c r="E825" s="7"/>
-      <c r="F825" s="5"/>
-    </row>
-    <row r="826" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A826" s="5"/>
-      <c r="B826" s="6"/>
-      <c r="C826" s="7"/>
-      <c r="D826" s="17"/>
-      <c r="E826" s="7"/>
-      <c r="F826" s="5"/>
-    </row>
-    <row r="827" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A827" s="5"/>
-      <c r="B827" s="6"/>
-      <c r="C827" s="7"/>
-      <c r="D827" s="17"/>
-      <c r="E827" s="7"/>
-      <c r="F827" s="5"/>
-    </row>
-    <row r="828" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A828" s="5"/>
-      <c r="B828" s="6"/>
-      <c r="C828" s="7"/>
-      <c r="D828" s="17"/>
-      <c r="E828" s="7"/>
-      <c r="F828" s="5"/>
-    </row>
-    <row r="829" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A829" s="5"/>
-      <c r="B829" s="6"/>
-      <c r="C829" s="7"/>
-      <c r="D829" s="17"/>
-      <c r="E829" s="7"/>
-      <c r="F829" s="5"/>
-    </row>
-    <row r="830" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A830" s="5"/>
-      <c r="B830" s="6"/>
-      <c r="C830" s="7"/>
-      <c r="D830" s="17"/>
-      <c r="E830" s="7"/>
-      <c r="F830" s="5"/>
-    </row>
-    <row r="831" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A831" s="5"/>
-      <c r="B831" s="6"/>
-      <c r="C831" s="7"/>
-      <c r="D831" s="17"/>
-      <c r="E831" s="7"/>
-      <c r="F831" s="5"/>
-    </row>
-    <row r="832" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A832" s="5"/>
-      <c r="B832" s="6"/>
-      <c r="C832" s="7"/>
-      <c r="D832" s="17"/>
-      <c r="E832" s="7"/>
-      <c r="F832" s="5"/>
-    </row>
-    <row r="833" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A833" s="5"/>
-      <c r="B833" s="6"/>
-      <c r="C833" s="7"/>
-      <c r="D833" s="17"/>
-      <c r="E833" s="7"/>
-      <c r="F833" s="5"/>
-    </row>
-    <row r="834" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A834" s="5"/>
-      <c r="B834" s="6"/>
-      <c r="C834" s="7"/>
-      <c r="D834" s="17"/>
-      <c r="E834" s="7"/>
-      <c r="F834" s="5"/>
-    </row>
-    <row r="835" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A835" s="5"/>
-      <c r="B835" s="6"/>
-      <c r="C835" s="7"/>
-      <c r="D835" s="17"/>
-      <c r="E835" s="7"/>
-      <c r="F835" s="5"/>
-    </row>
-    <row r="836" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A836" s="5"/>
-      <c r="B836" s="6"/>
-      <c r="C836" s="7"/>
-      <c r="D836" s="17"/>
-      <c r="E836" s="7"/>
-      <c r="F836" s="5"/>
-    </row>
-    <row r="837" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A837" s="5"/>
-      <c r="B837" s="6"/>
-      <c r="C837" s="7"/>
-      <c r="D837" s="17"/>
-      <c r="E837" s="7"/>
-      <c r="F837" s="5"/>
-    </row>
-    <row r="838" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A838" s="5"/>
-      <c r="B838" s="6"/>
-      <c r="C838" s="7"/>
-      <c r="D838" s="17"/>
-      <c r="E838" s="7"/>
-      <c r="F838" s="5"/>
-    </row>
-    <row r="839" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A839" s="5"/>
-      <c r="B839" s="6"/>
-      <c r="C839" s="7"/>
-      <c r="D839" s="17"/>
-      <c r="E839" s="7"/>
-      <c r="F839" s="5"/>
-    </row>
-    <row r="840" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A840" s="5"/>
-      <c r="B840" s="6"/>
-      <c r="C840" s="7"/>
-      <c r="D840" s="17"/>
-      <c r="E840" s="7"/>
-      <c r="F840" s="5"/>
-    </row>
-    <row r="841" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A841" s="5"/>
-      <c r="B841" s="6"/>
-      <c r="C841" s="7"/>
-      <c r="D841" s="17"/>
-      <c r="E841" s="7"/>
-      <c r="F841" s="5"/>
-    </row>
-    <row r="842" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A842" s="5"/>
-      <c r="B842" s="6"/>
-      <c r="C842" s="7"/>
-      <c r="D842" s="17"/>
-      <c r="E842" s="7"/>
-      <c r="F842" s="5"/>
-    </row>
-    <row r="843" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A843" s="5"/>
-      <c r="B843" s="6"/>
-      <c r="C843" s="7"/>
-      <c r="D843" s="17"/>
-      <c r="E843" s="7"/>
-      <c r="F843" s="5"/>
-    </row>
-    <row r="844" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A844" s="5"/>
-      <c r="B844" s="6"/>
-      <c r="C844" s="7"/>
-      <c r="D844" s="17"/>
-      <c r="E844" s="7"/>
-      <c r="F844" s="5"/>
-    </row>
-    <row r="845" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A845" s="5"/>
-      <c r="B845" s="6"/>
-      <c r="C845" s="7"/>
-      <c r="D845" s="17"/>
-      <c r="E845" s="7"/>
-      <c r="F845" s="5"/>
-    </row>
-    <row r="846" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A846" s="5"/>
-      <c r="B846" s="6"/>
-      <c r="C846" s="7"/>
-      <c r="D846" s="17"/>
-      <c r="E846" s="7"/>
-      <c r="F846" s="5"/>
-    </row>
-    <row r="847" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A847" s="5"/>
-      <c r="B847" s="6"/>
-      <c r="C847" s="7"/>
-      <c r="D847" s="17"/>
-      <c r="E847" s="7"/>
-      <c r="F847" s="5"/>
-    </row>
-    <row r="848" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A848" s="5"/>
-      <c r="B848" s="6"/>
-      <c r="C848" s="7"/>
-      <c r="D848" s="17"/>
-      <c r="E848" s="7"/>
-      <c r="F848" s="5"/>
-    </row>
-    <row r="849" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A849" s="5"/>
-      <c r="B849" s="6"/>
-      <c r="C849" s="7"/>
-      <c r="D849" s="17"/>
-      <c r="E849" s="7"/>
-      <c r="F849" s="5"/>
-    </row>
-    <row r="850" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A850" s="5"/>
-      <c r="B850" s="6"/>
-      <c r="C850" s="7"/>
-      <c r="D850" s="17"/>
-      <c r="E850" s="7"/>
-      <c r="F850" s="5"/>
-    </row>
-    <row r="851" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A851" s="5"/>
-      <c r="B851" s="6"/>
-      <c r="C851" s="7"/>
-      <c r="D851" s="17"/>
-      <c r="E851" s="7"/>
-      <c r="F851" s="5"/>
-    </row>
-    <row r="852" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A852" s="5"/>
-      <c r="B852" s="6"/>
-      <c r="C852" s="7"/>
-      <c r="D852" s="17"/>
-      <c r="E852" s="7"/>
-      <c r="F852" s="5"/>
-    </row>
-    <row r="853" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A853" s="5"/>
-      <c r="B853" s="6"/>
-      <c r="C853" s="7"/>
-      <c r="D853" s="17"/>
-      <c r="E853" s="7"/>
-      <c r="F853" s="5"/>
-    </row>
-    <row r="854" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A854" s="5"/>
-      <c r="B854" s="6"/>
-      <c r="C854" s="7"/>
-      <c r="D854" s="17"/>
-      <c r="E854" s="7"/>
-      <c r="F854" s="5"/>
-    </row>
-    <row r="855" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A855" s="5"/>
-      <c r="B855" s="6"/>
-      <c r="C855" s="7"/>
-      <c r="D855" s="17"/>
-      <c r="E855" s="7"/>
-      <c r="F855" s="5"/>
-    </row>
-    <row r="856" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A856" s="5"/>
-      <c r="B856" s="6"/>
-      <c r="C856" s="7"/>
-      <c r="D856" s="17"/>
-      <c r="E856" s="7"/>
-      <c r="F856" s="5"/>
-    </row>
-    <row r="857" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A857" s="5"/>
-      <c r="B857" s="6"/>
-      <c r="C857" s="7"/>
-      <c r="D857" s="17"/>
-      <c r="E857" s="7"/>
-      <c r="F857" s="5"/>
-    </row>
-    <row r="858" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A858" s="5"/>
-      <c r="B858" s="6"/>
-      <c r="C858" s="7"/>
-      <c r="D858" s="17"/>
-      <c r="E858" s="7"/>
-      <c r="F858" s="5"/>
-    </row>
-    <row r="859" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A859" s="5"/>
-      <c r="B859" s="6"/>
-      <c r="C859" s="7"/>
-      <c r="D859" s="17"/>
-      <c r="E859" s="7"/>
-      <c r="F859" s="5"/>
-    </row>
-    <row r="860" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A860" s="5"/>
-      <c r="B860" s="6"/>
-      <c r="C860" s="7"/>
-      <c r="D860" s="17"/>
-      <c r="E860" s="7"/>
-      <c r="F860" s="5"/>
-    </row>
-    <row r="861" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A861" s="5"/>
-      <c r="B861" s="6"/>
-      <c r="C861" s="7"/>
-      <c r="D861" s="17"/>
-      <c r="E861" s="7"/>
-      <c r="F861" s="5"/>
-    </row>
-    <row r="862" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A862" s="5"/>
-      <c r="B862" s="6"/>
-      <c r="C862" s="7"/>
-      <c r="D862" s="17"/>
-      <c r="E862" s="7"/>
-      <c r="F862" s="5"/>
-    </row>
-    <row r="863" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A863" s="5"/>
-      <c r="B863" s="6"/>
-      <c r="C863" s="7"/>
-      <c r="D863" s="17"/>
-      <c r="E863" s="7"/>
-      <c r="F863" s="5"/>
-    </row>
-    <row r="864" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A864" s="5"/>
-      <c r="B864" s="6"/>
-      <c r="C864" s="7"/>
-      <c r="D864" s="17"/>
-      <c r="E864" s="7"/>
-      <c r="F864" s="5"/>
-    </row>
-    <row r="865" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A865" s="5"/>
-      <c r="B865" s="6"/>
-      <c r="C865" s="7"/>
-      <c r="D865" s="17"/>
-      <c r="E865" s="7"/>
-      <c r="F865" s="5"/>
-    </row>
-    <row r="866" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A866" s="5"/>
-      <c r="B866" s="6"/>
-      <c r="C866" s="7"/>
-      <c r="D866" s="17"/>
-      <c r="E866" s="7"/>
-      <c r="F866" s="5"/>
-    </row>
-    <row r="867" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A867" s="5"/>
-      <c r="B867" s="6"/>
-      <c r="C867" s="7"/>
-      <c r="D867" s="17"/>
-      <c r="E867" s="7"/>
-      <c r="F867" s="5"/>
-    </row>
-    <row r="868" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A868" s="5"/>
-      <c r="B868" s="6"/>
-      <c r="C868" s="7"/>
-      <c r="D868" s="17"/>
-      <c r="E868" s="7"/>
-      <c r="F868" s="5"/>
-    </row>
-    <row r="869" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A869" s="5"/>
-      <c r="B869" s="6"/>
-      <c r="C869" s="7"/>
-      <c r="D869" s="17"/>
-      <c r="E869" s="7"/>
-      <c r="F869" s="5"/>
-    </row>
-    <row r="870" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A870" s="5"/>
-      <c r="B870" s="6"/>
-      <c r="C870" s="7"/>
-      <c r="D870" s="17"/>
-      <c r="E870" s="7"/>
-      <c r="F870" s="5"/>
-    </row>
-    <row r="871" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A871" s="5"/>
-      <c r="B871" s="6"/>
-      <c r="C871" s="7"/>
-      <c r="D871" s="17"/>
-      <c r="E871" s="7"/>
-      <c r="F871" s="5"/>
-    </row>
-    <row r="872" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A872" s="5"/>
-      <c r="B872" s="6"/>
-      <c r="C872" s="7"/>
-      <c r="D872" s="17"/>
-      <c r="E872" s="7"/>
-      <c r="F872" s="5"/>
-    </row>
-    <row r="873" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A873" s="5"/>
-      <c r="B873" s="6"/>
-      <c r="C873" s="7"/>
-      <c r="D873" s="17"/>
-      <c r="E873" s="7"/>
-      <c r="F873" s="5"/>
-    </row>
-    <row r="874" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A874" s="5"/>
-      <c r="B874" s="6"/>
-      <c r="C874" s="7"/>
-      <c r="D874" s="17"/>
-      <c r="E874" s="7"/>
-      <c r="F874" s="5"/>
-    </row>
-    <row r="875" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A875" s="5"/>
-      <c r="B875" s="6"/>
-      <c r="C875" s="7"/>
-      <c r="D875" s="17"/>
-      <c r="E875" s="7"/>
-      <c r="F875" s="5"/>
-    </row>
-    <row r="876" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A876" s="5"/>
-      <c r="B876" s="6"/>
-      <c r="C876" s="7"/>
-      <c r="D876" s="17"/>
-      <c r="E876" s="7"/>
-      <c r="F876" s="5"/>
-    </row>
-    <row r="877" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A877" s="5"/>
-      <c r="B877" s="6"/>
-      <c r="C877" s="7"/>
-      <c r="D877" s="17"/>
-      <c r="E877" s="7"/>
-      <c r="F877" s="5"/>
-    </row>
-    <row r="878" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A878" s="5"/>
-      <c r="B878" s="6"/>
-      <c r="C878" s="7"/>
-      <c r="D878" s="17"/>
-      <c r="E878" s="7"/>
-      <c r="F878" s="5"/>
-    </row>
-    <row r="879" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A879" s="5"/>
-      <c r="B879" s="6"/>
-      <c r="C879" s="7"/>
-      <c r="D879" s="17"/>
-      <c r="E879" s="7"/>
-      <c r="F879" s="5"/>
-    </row>
-    <row r="880" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A880" s="5"/>
-      <c r="B880" s="6"/>
-      <c r="C880" s="7"/>
-      <c r="D880" s="17"/>
-      <c r="E880" s="7"/>
-      <c r="F880" s="5"/>
-    </row>
-    <row r="881" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A881" s="5"/>
-      <c r="B881" s="6"/>
-      <c r="C881" s="7"/>
-      <c r="D881" s="17"/>
-      <c r="E881" s="7"/>
-      <c r="F881" s="5"/>
-    </row>
-    <row r="882" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A882" s="5"/>
-      <c r="B882" s="6"/>
-      <c r="C882" s="7"/>
-      <c r="D882" s="17"/>
-      <c r="E882" s="7"/>
-      <c r="F882" s="5"/>
-    </row>
-    <row r="883" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A883" s="5"/>
-      <c r="B883" s="6"/>
-      <c r="C883" s="7"/>
-      <c r="D883" s="17"/>
-      <c r="E883" s="7"/>
-      <c r="F883" s="5"/>
-    </row>
-    <row r="884" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A884" s="5"/>
-      <c r="B884" s="6"/>
-      <c r="C884" s="7"/>
-      <c r="D884" s="17"/>
-      <c r="E884" s="7"/>
-      <c r="F884" s="5"/>
-    </row>
-    <row r="885" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A885" s="5"/>
-      <c r="B885" s="6"/>
-      <c r="C885" s="7"/>
-      <c r="D885" s="17"/>
-      <c r="E885" s="7"/>
-      <c r="F885" s="5"/>
-    </row>
-    <row r="886" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A886" s="5"/>
-      <c r="B886" s="6"/>
-      <c r="C886" s="7"/>
-      <c r="D886" s="17"/>
-      <c r="E886" s="7"/>
-      <c r="F886" s="5"/>
-    </row>
-    <row r="887" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A887" s="5"/>
-      <c r="B887" s="6"/>
-      <c r="C887" s="7"/>
-      <c r="D887" s="17"/>
-      <c r="E887" s="7"/>
-      <c r="F887" s="5"/>
-    </row>
-    <row r="888" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A888" s="5"/>
-      <c r="B888" s="6"/>
-      <c r="C888" s="7"/>
-      <c r="D888" s="17"/>
-      <c r="E888" s="7"/>
-      <c r="F888" s="5"/>
-    </row>
-    <row r="889" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A889" s="5"/>
-      <c r="B889" s="6"/>
-      <c r="C889" s="7"/>
-      <c r="D889" s="17"/>
-      <c r="E889" s="7"/>
-      <c r="F889" s="5"/>
-    </row>
-    <row r="890" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A890" s="5"/>
-      <c r="B890" s="6"/>
-      <c r="C890" s="7"/>
-      <c r="D890" s="17"/>
-      <c r="E890" s="7"/>
-      <c r="F890" s="5"/>
-    </row>
-    <row r="891" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A891" s="5"/>
-      <c r="B891" s="6"/>
-      <c r="C891" s="7"/>
-      <c r="D891" s="17"/>
-      <c r="E891" s="7"/>
-      <c r="F891" s="5"/>
-    </row>
-    <row r="892" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A892" s="5"/>
-      <c r="B892" s="6"/>
-      <c r="C892" s="7"/>
-      <c r="D892" s="17"/>
-      <c r="E892" s="7"/>
-      <c r="F892" s="5"/>
-    </row>
-    <row r="893" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A893" s="5"/>
-      <c r="B893" s="6"/>
-      <c r="C893" s="7"/>
-      <c r="D893" s="17"/>
-      <c r="E893" s="7"/>
-      <c r="F893" s="5"/>
-    </row>
-    <row r="894" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A894" s="5"/>
-      <c r="B894" s="6"/>
-      <c r="C894" s="7"/>
-      <c r="D894" s="17"/>
-      <c r="E894" s="7"/>
-      <c r="F894" s="5"/>
-    </row>
-    <row r="895" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A895" s="5"/>
-      <c r="B895" s="6"/>
-      <c r="C895" s="7"/>
-      <c r="D895" s="17"/>
-      <c r="E895" s="7"/>
-      <c r="F895" s="5"/>
-    </row>
-    <row r="896" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A896" s="5"/>
-      <c r="B896" s="6"/>
-      <c r="C896" s="7"/>
-      <c r="D896" s="17"/>
-      <c r="E896" s="7"/>
-      <c r="F896" s="5"/>
-    </row>
-    <row r="897" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A897" s="5"/>
-      <c r="B897" s="6"/>
-      <c r="C897" s="7"/>
-      <c r="D897" s="17"/>
-      <c r="E897" s="7"/>
-      <c r="F897" s="5"/>
-    </row>
-    <row r="898" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A898" s="5"/>
-      <c r="B898" s="6"/>
-      <c r="C898" s="7"/>
-      <c r="D898" s="17"/>
-      <c r="E898" s="7"/>
-      <c r="F898" s="5"/>
-    </row>
-    <row r="899" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A899" s="5"/>
-      <c r="B899" s="6"/>
-      <c r="C899" s="7"/>
-      <c r="D899" s="17"/>
-      <c r="E899" s="7"/>
-      <c r="F899" s="5"/>
-    </row>
-    <row r="900" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A900" s="5"/>
-      <c r="B900" s="6"/>
-      <c r="C900" s="7"/>
-      <c r="D900" s="17"/>
-      <c r="E900" s="7"/>
-      <c r="F900" s="5"/>
-    </row>
-    <row r="901" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A901" s="5"/>
-      <c r="B901" s="6"/>
-      <c r="C901" s="7"/>
-      <c r="D901" s="17"/>
-      <c r="E901" s="7"/>
-      <c r="F901" s="5"/>
-    </row>
-    <row r="902" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A902" s="5"/>
-      <c r="B902" s="6"/>
-      <c r="C902" s="7"/>
-      <c r="D902" s="17"/>
-      <c r="E902" s="7"/>
-      <c r="F902" s="5"/>
-    </row>
-    <row r="903" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A903" s="5"/>
-      <c r="B903" s="6"/>
-      <c r="C903" s="7"/>
-      <c r="D903" s="17"/>
-      <c r="E903" s="7"/>
-      <c r="F903" s="5"/>
-    </row>
-    <row r="904" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A904" s="5"/>
-      <c r="B904" s="6"/>
-      <c r="C904" s="7"/>
-      <c r="D904" s="17"/>
-      <c r="E904" s="7"/>
-      <c r="F904" s="5"/>
-    </row>
-    <row r="905" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A905" s="5"/>
-      <c r="B905" s="6"/>
-      <c r="C905" s="7"/>
-      <c r="D905" s="17"/>
-      <c r="E905" s="7"/>
-      <c r="F905" s="5"/>
-    </row>
-    <row r="906" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A906" s="5"/>
-      <c r="B906" s="6"/>
-      <c r="C906" s="7"/>
-      <c r="D906" s="17"/>
-      <c r="E906" s="7"/>
-      <c r="F906" s="5"/>
-    </row>
-    <row r="907" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A907" s="5"/>
-      <c r="B907" s="6"/>
-      <c r="C907" s="7"/>
-      <c r="D907" s="17"/>
-      <c r="E907" s="7"/>
-      <c r="F907" s="5"/>
-    </row>
-    <row r="908" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A908" s="5"/>
-      <c r="B908" s="6"/>
-      <c r="C908" s="7"/>
-      <c r="D908" s="17"/>
-      <c r="E908" s="7"/>
-      <c r="F908" s="5"/>
-    </row>
-    <row r="909" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A909" s="5"/>
-      <c r="B909" s="6"/>
-      <c r="C909" s="7"/>
-      <c r="D909" s="17"/>
-      <c r="E909" s="7"/>
-      <c r="F909" s="5"/>
-    </row>
-    <row r="910" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A910" s="5"/>
-      <c r="B910" s="6"/>
-      <c r="C910" s="7"/>
-      <c r="D910" s="17"/>
-      <c r="E910" s="7"/>
-      <c r="F910" s="5"/>
-    </row>
-    <row r="911" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A911" s="5"/>
-      <c r="B911" s="6"/>
-      <c r="C911" s="7"/>
-      <c r="D911" s="17"/>
-      <c r="E911" s="7"/>
-      <c r="F911" s="5"/>
-    </row>
-    <row r="912" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A912" s="5"/>
-      <c r="B912" s="6"/>
-      <c r="C912" s="7"/>
-      <c r="D912" s="17"/>
-      <c r="E912" s="7"/>
-      <c r="F912" s="5"/>
-    </row>
-    <row r="913" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A913" s="5"/>
-      <c r="B913" s="6"/>
-      <c r="C913" s="7"/>
-      <c r="D913" s="17"/>
-      <c r="E913" s="7"/>
-      <c r="F913" s="5"/>
-    </row>
-    <row r="914" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A914" s="5"/>
-      <c r="B914" s="6"/>
-      <c r="C914" s="7"/>
-      <c r="D914" s="17"/>
-      <c r="E914" s="7"/>
-      <c r="F914" s="5"/>
-    </row>
-    <row r="915" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A915" s="5"/>
-      <c r="B915" s="6"/>
-      <c r="C915" s="7"/>
-      <c r="D915" s="17"/>
-      <c r="E915" s="7"/>
-      <c r="F915" s="5"/>
-    </row>
-    <row r="916" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A916" s="5"/>
-      <c r="B916" s="6"/>
-      <c r="C916" s="7"/>
-      <c r="D916" s="17"/>
-      <c r="E916" s="7"/>
-      <c r="F916" s="5"/>
-    </row>
-    <row r="917" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A917" s="5"/>
-      <c r="B917" s="6"/>
-      <c r="C917" s="7"/>
-      <c r="D917" s="17"/>
-      <c r="E917" s="7"/>
-      <c r="F917" s="5"/>
-    </row>
-    <row r="918" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A918" s="5"/>
-      <c r="B918" s="6"/>
-      <c r="C918" s="7"/>
-      <c r="D918" s="17"/>
-      <c r="E918" s="7"/>
-      <c r="F918" s="5"/>
-    </row>
-    <row r="919" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A919" s="5"/>
-      <c r="B919" s="6"/>
-      <c r="C919" s="7"/>
-      <c r="D919" s="17"/>
-      <c r="E919" s="7"/>
-      <c r="F919" s="5"/>
-    </row>
-    <row r="920" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A920" s="5"/>
-      <c r="B920" s="6"/>
-      <c r="C920" s="7"/>
-      <c r="D920" s="17"/>
-      <c r="E920" s="7"/>
-      <c r="F920" s="5"/>
-    </row>
-    <row r="921" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A921" s="5"/>
-      <c r="B921" s="6"/>
-      <c r="C921" s="7"/>
-      <c r="D921" s="17"/>
-      <c r="E921" s="7"/>
-      <c r="F921" s="5"/>
-    </row>
-    <row r="922" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A922" s="5"/>
-      <c r="B922" s="6"/>
-      <c r="C922" s="7"/>
-      <c r="D922" s="17"/>
-      <c r="E922" s="7"/>
-      <c r="F922" s="5"/>
-    </row>
-    <row r="923" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A923" s="5"/>
-      <c r="B923" s="6"/>
-      <c r="C923" s="7"/>
-      <c r="D923" s="17"/>
-      <c r="E923" s="7"/>
-      <c r="F923" s="5"/>
-    </row>
-    <row r="924" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A924" s="5"/>
-      <c r="B924" s="6"/>
-      <c r="C924" s="7"/>
-      <c r="D924" s="17"/>
-      <c r="E924" s="7"/>
-      <c r="F924" s="5"/>
-    </row>
-    <row r="925" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A925" s="5"/>
-      <c r="B925" s="6"/>
-      <c r="C925" s="7"/>
-      <c r="D925" s="17"/>
-      <c r="E925" s="7"/>
-      <c r="F925" s="5"/>
-    </row>
-    <row r="926" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A926" s="5"/>
-      <c r="B926" s="6"/>
-      <c r="C926" s="7"/>
-      <c r="D926" s="17"/>
-      <c r="E926" s="7"/>
-      <c r="F926" s="5"/>
-    </row>
-    <row r="927" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A927" s="5"/>
-      <c r="B927" s="6"/>
-      <c r="C927" s="7"/>
-      <c r="D927" s="17"/>
-      <c r="E927" s="7"/>
-      <c r="F927" s="5"/>
-    </row>
-    <row r="928" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A928" s="5"/>
-      <c r="B928" s="6"/>
-      <c r="C928" s="7"/>
-      <c r="D928" s="17"/>
-      <c r="E928" s="7"/>
-      <c r="F928" s="5"/>
-    </row>
-    <row r="929" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A929" s="5"/>
-      <c r="B929" s="6"/>
-      <c r="C929" s="7"/>
-      <c r="D929" s="17"/>
-      <c r="E929" s="7"/>
-      <c r="F929" s="5"/>
-    </row>
-    <row r="930" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A930" s="5"/>
-      <c r="B930" s="6"/>
-      <c r="C930" s="7"/>
-      <c r="D930" s="17"/>
-      <c r="E930" s="7"/>
-      <c r="F930" s="5"/>
-    </row>
-    <row r="931" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A931" s="5"/>
-      <c r="B931" s="6"/>
-      <c r="C931" s="7"/>
-      <c r="D931" s="17"/>
-      <c r="E931" s="7"/>
-      <c r="F931" s="5"/>
-    </row>
-    <row r="932" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A932" s="5"/>
-      <c r="B932" s="6"/>
-      <c r="C932" s="7"/>
-      <c r="D932" s="17"/>
-      <c r="E932" s="7"/>
-      <c r="F932" s="5"/>
-    </row>
-    <row r="933" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A933" s="5"/>
-      <c r="B933" s="6"/>
-      <c r="C933" s="7"/>
-      <c r="D933" s="17"/>
-      <c r="E933" s="7"/>
-      <c r="F933" s="5"/>
-    </row>
-    <row r="934" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A934" s="5"/>
-      <c r="B934" s="6"/>
-      <c r="C934" s="7"/>
-      <c r="D934" s="17"/>
-      <c r="E934" s="7"/>
-      <c r="F934" s="5"/>
-    </row>
-    <row r="935" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A935" s="5"/>
-      <c r="B935" s="6"/>
-      <c r="C935" s="7"/>
-      <c r="D935" s="17"/>
-      <c r="E935" s="7"/>
-      <c r="F935" s="5"/>
-    </row>
-    <row r="936" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A936" s="5"/>
-      <c r="B936" s="6"/>
-      <c r="C936" s="7"/>
-      <c r="D936" s="17"/>
-      <c r="E936" s="7"/>
-      <c r="F936" s="5"/>
-    </row>
-    <row r="937" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A937" s="5"/>
-      <c r="B937" s="6"/>
-      <c r="C937" s="7"/>
-      <c r="D937" s="17"/>
-      <c r="E937" s="7"/>
-      <c r="F937" s="5"/>
-    </row>
-    <row r="938" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A938" s="5"/>
-      <c r="B938" s="6"/>
-      <c r="C938" s="7"/>
-      <c r="D938" s="17"/>
-      <c r="E938" s="7"/>
-      <c r="F938" s="5"/>
-    </row>
-    <row r="939" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A939" s="5"/>
-      <c r="B939" s="6"/>
-      <c r="C939" s="7"/>
-      <c r="D939" s="17"/>
-      <c r="E939" s="7"/>
-      <c r="F939" s="5"/>
-    </row>
-    <row r="940" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A940" s="5"/>
-      <c r="B940" s="6"/>
-      <c r="C940" s="7"/>
-      <c r="D940" s="17"/>
-      <c r="E940" s="7"/>
-      <c r="F940" s="5"/>
-    </row>
-    <row r="941" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A941" s="5"/>
-      <c r="B941" s="6"/>
-      <c r="C941" s="7"/>
-      <c r="D941" s="17"/>
-      <c r="E941" s="7"/>
-      <c r="F941" s="5"/>
-    </row>
-    <row r="942" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A942" s="5"/>
-      <c r="B942" s="6"/>
-      <c r="C942" s="7"/>
-      <c r="D942" s="17"/>
-      <c r="E942" s="7"/>
-      <c r="F942" s="5"/>
-    </row>
-    <row r="943" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A943" s="5"/>
-      <c r="B943" s="6"/>
-      <c r="C943" s="7"/>
-      <c r="D943" s="17"/>
-      <c r="E943" s="7"/>
-      <c r="F943" s="5"/>
-    </row>
-    <row r="944" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A944" s="5"/>
-      <c r="B944" s="6"/>
-      <c r="C944" s="7"/>
-      <c r="D944" s="17"/>
-      <c r="E944" s="7"/>
-      <c r="F944" s="5"/>
-    </row>
-    <row r="945" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A945" s="5"/>
-      <c r="B945" s="6"/>
-      <c r="C945" s="7"/>
-      <c r="D945" s="17"/>
-      <c r="E945" s="7"/>
-      <c r="F945" s="5"/>
-    </row>
-    <row r="946" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A946" s="5"/>
-      <c r="B946" s="6"/>
-      <c r="C946" s="7"/>
-      <c r="D946" s="17"/>
-      <c r="E946" s="7"/>
-      <c r="F946" s="5"/>
-    </row>
-    <row r="947" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A947" s="5"/>
-      <c r="B947" s="6"/>
-      <c r="C947" s="7"/>
-      <c r="D947" s="17"/>
-      <c r="E947" s="7"/>
-      <c r="F947" s="5"/>
-    </row>
-    <row r="948" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A948" s="5"/>
-      <c r="B948" s="6"/>
-      <c r="C948" s="7"/>
-      <c r="D948" s="17"/>
-      <c r="E948" s="7"/>
-      <c r="F948" s="5"/>
-    </row>
-    <row r="949" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A949" s="5"/>
-      <c r="B949" s="6"/>
-      <c r="C949" s="7"/>
-      <c r="D949" s="17"/>
-      <c r="E949" s="7"/>
-      <c r="F949" s="5"/>
-    </row>
-    <row r="950" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A950" s="5"/>
-      <c r="B950" s="6"/>
-      <c r="C950" s="7"/>
-      <c r="D950" s="17"/>
-      <c r="E950" s="7"/>
-      <c r="F950" s="5"/>
-    </row>
-    <row r="951" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A951" s="5"/>
-      <c r="B951" s="6"/>
-      <c r="C951" s="7"/>
-      <c r="D951" s="17"/>
-      <c r="E951" s="7"/>
-      <c r="F951" s="5"/>
-    </row>
-    <row r="952" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A952" s="5"/>
-      <c r="B952" s="6"/>
-      <c r="C952" s="7"/>
-      <c r="D952" s="17"/>
-      <c r="E952" s="7"/>
-      <c r="F952" s="5"/>
-    </row>
-    <row r="953" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A953" s="5"/>
-      <c r="B953" s="6"/>
-      <c r="C953" s="7"/>
-      <c r="D953" s="17"/>
-      <c r="E953" s="7"/>
-      <c r="F953" s="5"/>
-    </row>
-    <row r="954" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A954" s="5"/>
-      <c r="B954" s="6"/>
-      <c r="C954" s="7"/>
-      <c r="D954" s="17"/>
-      <c r="E954" s="7"/>
-      <c r="F954" s="5"/>
-    </row>
-    <row r="955" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A955" s="5"/>
-      <c r="B955" s="6"/>
-      <c r="C955" s="7"/>
-      <c r="D955" s="17"/>
-      <c r="E955" s="7"/>
-      <c r="F955" s="5"/>
-    </row>
-    <row r="956" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A956" s="5"/>
-      <c r="B956" s="6"/>
-      <c r="C956" s="7"/>
-      <c r="D956" s="17"/>
-      <c r="E956" s="7"/>
-      <c r="F956" s="5"/>
-    </row>
-    <row r="957" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A957" s="5"/>
-      <c r="B957" s="6"/>
-      <c r="C957" s="7"/>
-      <c r="D957" s="17"/>
-      <c r="E957" s="7"/>
-      <c r="F957" s="5"/>
-    </row>
-    <row r="958" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A958" s="5"/>
-      <c r="B958" s="6"/>
-      <c r="C958" s="7"/>
-      <c r="D958" s="17"/>
-      <c r="E958" s="7"/>
-      <c r="F958" s="5"/>
-    </row>
-    <row r="959" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A959" s="5"/>
-      <c r="B959" s="6"/>
-      <c r="C959" s="7"/>
-      <c r="D959" s="17"/>
-      <c r="E959" s="7"/>
-      <c r="F959" s="5"/>
-    </row>
-    <row r="960" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A960" s="5"/>
-      <c r="B960" s="6"/>
-      <c r="C960" s="7"/>
-      <c r="D960" s="17"/>
-      <c r="E960" s="7"/>
-      <c r="F960" s="5"/>
-    </row>
-    <row r="961" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A961" s="5"/>
-      <c r="B961" s="6"/>
-      <c r="C961" s="7"/>
-      <c r="D961" s="17"/>
-      <c r="E961" s="7"/>
-      <c r="F961" s="5"/>
-    </row>
-    <row r="962" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A962" s="5"/>
-      <c r="B962" s="6"/>
-      <c r="C962" s="7"/>
-      <c r="D962" s="17"/>
-      <c r="E962" s="7"/>
-      <c r="F962" s="5"/>
-    </row>
-    <row r="963" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A963" s="5"/>
-      <c r="B963" s="6"/>
-      <c r="C963" s="7"/>
-      <c r="D963" s="17"/>
-      <c r="E963" s="7"/>
-      <c r="F963" s="5"/>
-    </row>
-    <row r="964" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A964" s="5"/>
-      <c r="B964" s="6"/>
-      <c r="C964" s="7"/>
-      <c r="D964" s="17"/>
-      <c r="E964" s="7"/>
-      <c r="F964" s="5"/>
-    </row>
-    <row r="965" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A965" s="5"/>
-      <c r="B965" s="6"/>
-      <c r="C965" s="7"/>
-      <c r="D965" s="17"/>
-      <c r="E965" s="7"/>
-      <c r="F965" s="5"/>
-    </row>
-    <row r="966" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A966" s="5"/>
-      <c r="B966" s="6"/>
-      <c r="C966" s="7"/>
-      <c r="D966" s="17"/>
-      <c r="E966" s="7"/>
-      <c r="F966" s="5"/>
-    </row>
-    <row r="967" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A967" s="5"/>
-      <c r="B967" s="6"/>
-      <c r="C967" s="7"/>
-      <c r="D967" s="17"/>
-      <c r="E967" s="7"/>
-      <c r="F967" s="5"/>
-    </row>
-    <row r="968" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A968" s="5"/>
-      <c r="B968" s="6"/>
-      <c r="C968" s="7"/>
-      <c r="D968" s="17"/>
-      <c r="E968" s="7"/>
-      <c r="F968" s="5"/>
-    </row>
-    <row r="969" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A969" s="5"/>
-      <c r="B969" s="6"/>
-      <c r="C969" s="7"/>
-      <c r="D969" s="17"/>
-      <c r="E969" s="7"/>
-      <c r="F969" s="5"/>
-    </row>
-    <row r="970" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A970" s="5"/>
-      <c r="B970" s="6"/>
-      <c r="C970" s="7"/>
-      <c r="D970" s="17"/>
-      <c r="E970" s="7"/>
-      <c r="F970" s="5"/>
-    </row>
-    <row r="971" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A971" s="5"/>
-      <c r="B971" s="6"/>
-      <c r="C971" s="7"/>
-      <c r="D971" s="17"/>
-      <c r="E971" s="7"/>
-      <c r="F971" s="5"/>
-    </row>
-    <row r="972" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A972" s="5"/>
-      <c r="B972" s="6"/>
-      <c r="C972" s="7"/>
-      <c r="D972" s="17"/>
-      <c r="E972" s="7"/>
-      <c r="F972" s="5"/>
-    </row>
-    <row r="973" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A973" s="5"/>
-      <c r="B973" s="6"/>
-      <c r="C973" s="7"/>
-      <c r="D973" s="17"/>
-      <c r="E973" s="7"/>
-      <c r="F973" s="5"/>
-    </row>
-    <row r="974" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A974" s="5"/>
-      <c r="B974" s="6"/>
-      <c r="C974" s="7"/>
-      <c r="D974" s="17"/>
-      <c r="E974" s="7"/>
-      <c r="F974" s="5"/>
-    </row>
-    <row r="975" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A975" s="5"/>
-      <c r="B975" s="6"/>
-      <c r="C975" s="7"/>
-      <c r="D975" s="17"/>
-      <c r="E975" s="7"/>
-      <c r="F975" s="5"/>
-    </row>
-    <row r="976" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A976" s="5"/>
-      <c r="B976" s="6"/>
-      <c r="C976" s="7"/>
-      <c r="D976" s="17"/>
-      <c r="E976" s="7"/>
-      <c r="F976" s="5"/>
-    </row>
-    <row r="977" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A977" s="5"/>
-      <c r="B977" s="6"/>
-      <c r="C977" s="7"/>
-      <c r="D977" s="17"/>
-      <c r="E977" s="7"/>
-      <c r="F977" s="5"/>
-    </row>
-    <row r="978" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A978" s="5"/>
-      <c r="B978" s="6"/>
-      <c r="C978" s="7"/>
-      <c r="D978" s="17"/>
-      <c r="E978" s="7"/>
-      <c r="F978" s="5"/>
-    </row>
-    <row r="979" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A979" s="5"/>
-      <c r="B979" s="6"/>
-      <c r="C979" s="7"/>
-      <c r="D979" s="17"/>
-      <c r="E979" s="7"/>
-      <c r="F979" s="5"/>
-    </row>
-    <row r="980" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A980" s="5"/>
-      <c r="B980" s="6"/>
-      <c r="C980" s="7"/>
-      <c r="D980" s="17"/>
-      <c r="E980" s="7"/>
-      <c r="F980" s="5"/>
-    </row>
-    <row r="981" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A981" s="5"/>
-      <c r="B981" s="6"/>
-      <c r="C981" s="7"/>
-      <c r="D981" s="17"/>
-      <c r="E981" s="7"/>
-      <c r="F981" s="5"/>
-    </row>
-    <row r="982" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A982" s="5"/>
-      <c r="B982" s="6"/>
-      <c r="C982" s="7"/>
-      <c r="D982" s="17"/>
-      <c r="E982" s="7"/>
-      <c r="F982" s="5"/>
-    </row>
-    <row r="983" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A983" s="5"/>
-      <c r="B983" s="6"/>
-      <c r="C983" s="7"/>
-      <c r="D983" s="17"/>
-      <c r="E983" s="7"/>
-      <c r="F983" s="5"/>
-    </row>
-    <row r="984" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A984" s="5"/>
-      <c r="B984" s="6"/>
-      <c r="C984" s="7"/>
-      <c r="D984" s="17"/>
-      <c r="E984" s="7"/>
-      <c r="F984" s="5"/>
-    </row>
-    <row r="985" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A985" s="5"/>
-      <c r="B985" s="6"/>
-      <c r="C985" s="7"/>
-      <c r="D985" s="17"/>
-      <c r="E985" s="7"/>
-      <c r="F985" s="5"/>
-    </row>
-    <row r="986" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A986" s="5"/>
-      <c r="B986" s="6"/>
-      <c r="C986" s="7"/>
-      <c r="D986" s="17"/>
-      <c r="E986" s="7"/>
-      <c r="F986" s="5"/>
-    </row>
-    <row r="987" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A987" s="5"/>
-      <c r="B987" s="6"/>
-      <c r="C987" s="7"/>
-      <c r="D987" s="17"/>
-      <c r="E987" s="7"/>
-      <c r="F987" s="5"/>
-    </row>
-    <row r="988" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A988" s="5"/>
-      <c r="B988" s="6"/>
-      <c r="C988" s="7"/>
-      <c r="D988" s="17"/>
-      <c r="E988" s="7"/>
-      <c r="F988" s="5"/>
-    </row>
-    <row r="989" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A989" s="5"/>
-      <c r="B989" s="6"/>
-      <c r="C989" s="7"/>
-      <c r="D989" s="17"/>
-      <c r="E989" s="7"/>
-      <c r="F989" s="5"/>
-    </row>
-    <row r="990" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A990" s="5"/>
-      <c r="B990" s="6"/>
-      <c r="C990" s="7"/>
-      <c r="D990" s="17"/>
-      <c r="E990" s="7"/>
-      <c r="F990" s="5"/>
-    </row>
-    <row r="991" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A991" s="5"/>
-      <c r="B991" s="6"/>
-      <c r="C991" s="7"/>
-      <c r="D991" s="17"/>
-      <c r="E991" s="7"/>
-      <c r="F991" s="5"/>
-    </row>
-    <row r="992" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A992" s="5"/>
-      <c r="B992" s="6"/>
-      <c r="C992" s="7"/>
-      <c r="D992" s="17"/>
-      <c r="E992" s="7"/>
-      <c r="F992" s="5"/>
-    </row>
-    <row r="993" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A993" s="5"/>
-      <c r="B993" s="6"/>
-      <c r="C993" s="7"/>
-      <c r="D993" s="17"/>
-      <c r="E993" s="7"/>
-      <c r="F993" s="5"/>
-    </row>
-    <row r="994" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A994" s="5"/>
-      <c r="B994" s="6"/>
-      <c r="C994" s="7"/>
-      <c r="D994" s="17"/>
-      <c r="E994" s="7"/>
-      <c r="F994" s="5"/>
-    </row>
-    <row r="995" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A995" s="5"/>
-      <c r="B995" s="6"/>
-      <c r="C995" s="7"/>
-      <c r="D995" s="17"/>
-      <c r="E995" s="7"/>
-      <c r="F995" s="5"/>
-    </row>
-    <row r="996" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A996" s="5"/>
-      <c r="B996" s="6"/>
-      <c r="C996" s="7"/>
-      <c r="D996" s="17"/>
-      <c r="E996" s="7"/>
-      <c r="F996" s="5"/>
-    </row>
-    <row r="997" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A997" s="5"/>
-      <c r="B997" s="6"/>
-      <c r="C997" s="7"/>
-      <c r="D997" s="17"/>
-      <c r="E997" s="7"/>
-      <c r="F997" s="5"/>
-    </row>
-    <row r="998" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A998" s="5"/>
-      <c r="B998" s="6"/>
-      <c r="C998" s="7"/>
-      <c r="D998" s="17"/>
-      <c r="E998" s="7"/>
-      <c r="F998" s="5"/>
-    </row>
-    <row r="999" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A999" s="5"/>
-      <c r="B999" s="6"/>
-      <c r="C999" s="7"/>
-      <c r="D999" s="17"/>
-      <c r="E999" s="7"/>
-      <c r="F999" s="5"/>
-    </row>
-    <row r="1000" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1000" s="5"/>
-      <c r="B1000" s="6"/>
-      <c r="C1000" s="7"/>
-      <c r="D1000" s="17"/>
-      <c r="E1000" s="7"/>
-      <c r="F1000" s="5"/>
-    </row>
-    <row r="1001" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1001" s="5"/>
-      <c r="B1001" s="6"/>
-      <c r="C1001" s="7"/>
-      <c r="D1001" s="17"/>
-      <c r="E1001" s="7"/>
-      <c r="F1001" s="5"/>
-    </row>
-    <row r="1002" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1002" s="5"/>
-      <c r="B1002" s="6"/>
-      <c r="C1002" s="7"/>
-      <c r="D1002" s="17"/>
-      <c r="E1002" s="7"/>
-      <c r="F1002" s="5"/>
-    </row>
-    <row r="1003" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1003" s="5"/>
-      <c r="B1003" s="6"/>
-      <c r="C1003" s="7"/>
-      <c r="D1003" s="17"/>
-      <c r="E1003" s="7"/>
-      <c r="F1003" s="5"/>
-    </row>
-    <row r="1004" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1004" s="5"/>
-      <c r="B1004" s="6"/>
-      <c r="C1004" s="7"/>
-      <c r="D1004" s="17"/>
-      <c r="E1004" s="7"/>
-      <c r="F1004" s="5"/>
-    </row>
-    <row r="1005" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1005" s="5"/>
-      <c r="B1005" s="6"/>
-      <c r="C1005" s="7"/>
-      <c r="D1005" s="17"/>
-      <c r="E1005" s="7"/>
-      <c r="F1005" s="5"/>
-    </row>
-    <row r="1006" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1006" s="5"/>
-      <c r="B1006" s="6"/>
-      <c r="C1006" s="7"/>
-      <c r="D1006" s="17"/>
-      <c r="E1006" s="7"/>
-      <c r="F1006" s="5"/>
-    </row>
-    <row r="1007" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1007" s="5"/>
-      <c r="B1007" s="6"/>
-      <c r="C1007" s="7"/>
-      <c r="D1007" s="17"/>
-      <c r="E1007" s="7"/>
-      <c r="F1007" s="5"/>
-    </row>
-    <row r="1008" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1008" s="5"/>
-      <c r="B1008" s="6"/>
-      <c r="C1008" s="7"/>
-      <c r="D1008" s="17"/>
-      <c r="E1008" s="7"/>
-      <c r="F1008" s="5"/>
-    </row>
-    <row r="1009" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1009" s="5"/>
-      <c r="B1009" s="6"/>
-      <c r="C1009" s="7"/>
-      <c r="D1009" s="17"/>
-      <c r="E1009" s="7"/>
-      <c r="F1009" s="5"/>
-    </row>
-    <row r="1010" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1010" s="5"/>
-      <c r="B1010" s="6"/>
-      <c r="C1010" s="7"/>
-      <c r="D1010" s="17"/>
-      <c r="E1010" s="7"/>
-      <c r="F1010" s="5"/>
-    </row>
-    <row r="1011" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1011" s="5"/>
-      <c r="B1011" s="6"/>
-      <c r="C1011" s="7"/>
-      <c r="D1011" s="17"/>
-      <c r="E1011" s="7"/>
-      <c r="F1011" s="5"/>
-    </row>
-    <row r="1012" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1012" s="5"/>
-      <c r="B1012" s="6"/>
-      <c r="C1012" s="7"/>
-      <c r="D1012" s="17"/>
-      <c r="E1012" s="7"/>
-      <c r="F1012" s="5"/>
-    </row>
-    <row r="1013" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1013" s="5"/>
-      <c r="B1013" s="6"/>
-      <c r="C1013" s="7"/>
-      <c r="D1013" s="17"/>
-      <c r="E1013" s="7"/>
-      <c r="F1013" s="5"/>
-    </row>
-    <row r="1014" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1014" s="5"/>
-      <c r="B1014" s="6"/>
-      <c r="C1014" s="7"/>
-      <c r="D1014" s="17"/>
-      <c r="E1014" s="7"/>
-      <c r="F1014" s="5"/>
-    </row>
-    <row r="1015" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1015" s="5"/>
-      <c r="B1015" s="6"/>
-      <c r="C1015" s="7"/>
-      <c r="D1015" s="17"/>
-      <c r="E1015" s="7"/>
-      <c r="F1015" s="5"/>
-    </row>
-    <row r="1016" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1016" s="5"/>
-      <c r="B1016" s="6"/>
-      <c r="C1016" s="7"/>
-      <c r="D1016" s="17"/>
-      <c r="E1016" s="7"/>
-      <c r="F1016" s="5"/>
-    </row>
-    <row r="1017" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1017" s="5"/>
-      <c r="B1017" s="6"/>
-      <c r="C1017" s="7"/>
-      <c r="D1017" s="17"/>
-      <c r="E1017" s="7"/>
-      <c r="F1017" s="5"/>
-    </row>
-    <row r="1018" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1018" s="5"/>
-      <c r="B1018" s="6"/>
-      <c r="C1018" s="7"/>
-      <c r="D1018" s="17"/>
-      <c r="E1018" s="7"/>
-      <c r="F1018" s="5"/>
-    </row>
-    <row r="1019" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1019" s="5"/>
-      <c r="B1019" s="6"/>
-      <c r="C1019" s="7"/>
-      <c r="D1019" s="17"/>
-      <c r="E1019" s="7"/>
-      <c r="F1019" s="5"/>
-    </row>
-    <row r="1020" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1020" s="5"/>
-      <c r="B1020" s="6"/>
-      <c r="C1020" s="7"/>
-      <c r="D1020" s="17"/>
-      <c r="E1020" s="7"/>
-      <c r="F1020" s="5"/>
-    </row>
-    <row r="1021" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1021" s="5"/>
-      <c r="B1021" s="6"/>
-      <c r="C1021" s="7"/>
-      <c r="D1021" s="17"/>
-      <c r="E1021" s="7"/>
-      <c r="F1021" s="5"/>
-    </row>
-    <row r="1022" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1022" s="5"/>
-      <c r="B1022" s="6"/>
-      <c r="C1022" s="7"/>
-      <c r="D1022" s="17"/>
-      <c r="E1022" s="7"/>
-      <c r="F1022" s="5"/>
-    </row>
-    <row r="1023" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1023" s="5"/>
-      <c r="B1023" s="6"/>
-      <c r="C1023" s="7"/>
-      <c r="D1023" s="17"/>
-      <c r="E1023" s="7"/>
-      <c r="F1023" s="5"/>
-    </row>
-    <row r="1024" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1024" s="5"/>
-      <c r="B1024" s="6"/>
-      <c r="C1024" s="7"/>
-      <c r="D1024" s="17"/>
-      <c r="E1024" s="7"/>
-      <c r="F1024" s="5"/>
-    </row>
-    <row r="1025" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1025" s="5"/>
-      <c r="B1025" s="6"/>
-      <c r="C1025" s="7"/>
-      <c r="D1025" s="17"/>
-      <c r="E1025" s="7"/>
-      <c r="F1025" s="5"/>
-    </row>
-    <row r="1026" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1026" s="5"/>
-      <c r="B1026" s="6"/>
-      <c r="C1026" s="7"/>
-      <c r="D1026" s="17"/>
-      <c r="E1026" s="7"/>
-      <c r="F1026" s="5"/>
-    </row>
-    <row r="1027" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1027" s="5"/>
-      <c r="B1027" s="6"/>
-      <c r="C1027" s="7"/>
-      <c r="D1027" s="17"/>
-      <c r="E1027" s="7"/>
-      <c r="F1027" s="5"/>
-    </row>
-    <row r="1028" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1028" s="5"/>
-      <c r="B1028" s="6"/>
-      <c r="C1028" s="7"/>
-      <c r="D1028" s="17"/>
-      <c r="E1028" s="7"/>
-      <c r="F1028" s="5"/>
-    </row>
-    <row r="1029" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1029" s="5"/>
-      <c r="B1029" s="6"/>
-      <c r="C1029" s="7"/>
-      <c r="D1029" s="17"/>
-      <c r="E1029" s="7"/>
-      <c r="F1029" s="5"/>
-    </row>
-    <row r="1030" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1030" s="5"/>
-      <c r="B1030" s="6"/>
-      <c r="C1030" s="7"/>
-      <c r="D1030" s="17"/>
-      <c r="E1030" s="7"/>
-      <c r="F1030" s="5"/>
-    </row>
-    <row r="1031" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1031" s="5"/>
-      <c r="B1031" s="6"/>
-      <c r="C1031" s="7"/>
-      <c r="D1031" s="17"/>
-      <c r="E1031" s="7"/>
-      <c r="F1031" s="5"/>
-    </row>
-    <row r="1032" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1032" s="5"/>
-      <c r="B1032" s="6"/>
-      <c r="C1032" s="7"/>
-      <c r="D1032" s="17"/>
-      <c r="E1032" s="7"/>
-      <c r="F1032" s="5"/>
-    </row>
-    <row r="1033" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1033" s="5"/>
-      <c r="B1033" s="6"/>
-      <c r="C1033" s="7"/>
-      <c r="D1033" s="17"/>
-      <c r="E1033" s="7"/>
-      <c r="F1033" s="5"/>
-    </row>
-    <row r="1034" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1034" s="5"/>
-      <c r="B1034" s="6"/>
-      <c r="C1034" s="7"/>
-      <c r="D1034" s="17"/>
-      <c r="E1034" s="7"/>
-      <c r="F1034" s="5"/>
-    </row>
-    <row r="1035" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1035" s="5"/>
-      <c r="B1035" s="6"/>
-      <c r="C1035" s="7"/>
-      <c r="D1035" s="17"/>
-      <c r="E1035" s="7"/>
-      <c r="F1035" s="5"/>
-    </row>
-    <row r="1036" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1036" s="5"/>
-      <c r="B1036" s="6"/>
-      <c r="C1036" s="7"/>
-      <c r="D1036" s="17"/>
-      <c r="E1036" s="7"/>
-      <c r="F1036" s="5"/>
-    </row>
-    <row r="1037" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1037" s="5"/>
-      <c r="B1037" s="6"/>
-      <c r="C1037" s="7"/>
-      <c r="D1037" s="17"/>
-      <c r="E1037" s="7"/>
-      <c r="F1037" s="5"/>
-    </row>
-    <row r="1038" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1038" s="5"/>
-      <c r="B1038" s="6"/>
-      <c r="C1038" s="7"/>
-      <c r="D1038" s="17"/>
-      <c r="E1038" s="7"/>
-      <c r="F1038" s="5"/>
-    </row>
-    <row r="1039" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1039" s="5"/>
-      <c r="B1039" s="6"/>
-      <c r="C1039" s="7"/>
-      <c r="D1039" s="17"/>
-      <c r="E1039" s="7"/>
-      <c r="F1039" s="5"/>
-    </row>
-    <row r="1040" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1040" s="5"/>
-      <c r="B1040" s="6"/>
-      <c r="C1040" s="7"/>
-      <c r="D1040" s="17"/>
-      <c r="E1040" s="7"/>
-      <c r="F1040" s="5"/>
-    </row>
-    <row r="1041" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1041" s="5"/>
-      <c r="B1041" s="6"/>
-      <c r="C1041" s="7"/>
-      <c r="D1041" s="17"/>
-      <c r="E1041" s="7"/>
-      <c r="F1041" s="5"/>
-    </row>
-    <row r="1042" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1042" s="5"/>
-      <c r="B1042" s="6"/>
-      <c r="C1042" s="7"/>
-      <c r="D1042" s="17"/>
-      <c r="E1042" s="7"/>
-      <c r="F1042" s="5"/>
-    </row>
-    <row r="1043" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1043" s="5"/>
-      <c r="B1043" s="6"/>
-      <c r="C1043" s="7"/>
-      <c r="D1043" s="17"/>
-      <c r="E1043" s="7"/>
-      <c r="F1043" s="5"/>
-    </row>
-    <row r="1044" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1044" s="5"/>
-      <c r="B1044" s="6"/>
-      <c r="C1044" s="7"/>
-      <c r="D1044" s="17"/>
-      <c r="E1044" s="7"/>
-      <c r="F1044" s="5"/>
-    </row>
-    <row r="1045" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1045" s="5"/>
-      <c r="B1045" s="6"/>
-      <c r="C1045" s="7"/>
-      <c r="D1045" s="17"/>
-      <c r="E1045" s="7"/>
-      <c r="F1045" s="5"/>
-    </row>
-    <row r="1046" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1046" s="5"/>
-      <c r="B1046" s="6"/>
-      <c r="C1046" s="7"/>
-      <c r="D1046" s="17"/>
-      <c r="E1046" s="7"/>
-      <c r="F1046" s="5"/>
-    </row>
-    <row r="1047" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1047" s="5"/>
-      <c r="B1047" s="6"/>
-      <c r="C1047" s="7"/>
-      <c r="D1047" s="17"/>
-      <c r="E1047" s="7"/>
-      <c r="F1047" s="5"/>
-    </row>
-    <row r="1048" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1048" s="5"/>
-      <c r="B1048" s="6"/>
-      <c r="C1048" s="7"/>
-      <c r="D1048" s="17"/>
-      <c r="E1048" s="7"/>
-      <c r="F1048" s="5"/>
-    </row>
-    <row r="1049" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1049" s="5"/>
-      <c r="B1049" s="6"/>
-      <c r="C1049" s="7"/>
-      <c r="D1049" s="17"/>
-      <c r="E1049" s="7"/>
-      <c r="F1049" s="5"/>
-    </row>
-    <row r="1050" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1050" s="5"/>
-      <c r="B1050" s="6"/>
-      <c r="C1050" s="7"/>
-      <c r="D1050" s="17"/>
-      <c r="E1050" s="7"/>
-      <c r="F1050" s="5"/>
-    </row>
-    <row r="1051" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1051" s="5"/>
-      <c r="B1051" s="6"/>
-      <c r="C1051" s="7"/>
-      <c r="D1051" s="17"/>
-      <c r="E1051" s="7"/>
-      <c r="F1051" s="5"/>
-    </row>
-    <row r="1052" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1052" s="5"/>
-      <c r="B1052" s="6"/>
-      <c r="C1052" s="7"/>
-      <c r="D1052" s="17"/>
-      <c r="E1052" s="7"/>
-      <c r="F1052" s="5"/>
-    </row>
-    <row r="1053" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1053" s="5"/>
-      <c r="B1053" s="6"/>
-      <c r="C1053" s="7"/>
-      <c r="D1053" s="17"/>
-      <c r="E1053" s="7"/>
-      <c r="F1053" s="5"/>
-    </row>
-    <row r="1054" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1054" s="5"/>
-      <c r="B1054" s="6"/>
-      <c r="C1054" s="7"/>
-      <c r="D1054" s="17"/>
-      <c r="E1054" s="7"/>
-      <c r="F1054" s="5"/>
-    </row>
-    <row r="1055" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1055" s="5"/>
-      <c r="B1055" s="6"/>
-      <c r="C1055" s="7"/>
-      <c r="D1055" s="17"/>
-      <c r="E1055" s="7"/>
-      <c r="F1055" s="5"/>
-    </row>
-    <row r="1056" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1056" s="5"/>
-      <c r="B1056" s="6"/>
-      <c r="C1056" s="7"/>
-      <c r="D1056" s="17"/>
-      <c r="E1056" s="7"/>
-      <c r="F1056" s="5"/>
-    </row>
-    <row r="1057" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1057" s="5"/>
-      <c r="B1057" s="6"/>
-      <c r="C1057" s="7"/>
-      <c r="D1057" s="17"/>
-      <c r="E1057" s="7"/>
-      <c r="F1057" s="5"/>
-    </row>
-    <row r="1058" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1058" s="5"/>
-      <c r="B1058" s="6"/>
-      <c r="C1058" s="7"/>
-      <c r="D1058" s="17"/>
-      <c r="E1058" s="7"/>
-      <c r="F1058" s="5"/>
-    </row>
-    <row r="1059" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1059" s="5"/>
-      <c r="B1059" s="6"/>
-      <c r="C1059" s="7"/>
-      <c r="D1059" s="17"/>
-      <c r="E1059" s="7"/>
-      <c r="F1059" s="5"/>
-    </row>
-    <row r="1060" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1060" s="5"/>
-      <c r="B1060" s="6"/>
-      <c r="C1060" s="7"/>
-      <c r="D1060" s="17"/>
-      <c r="E1060" s="7"/>
-      <c r="F1060" s="5"/>
-    </row>
-    <row r="1061" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1061" s="5"/>
-      <c r="B1061" s="6"/>
-      <c r="C1061" s="7"/>
-      <c r="D1061" s="17"/>
-      <c r="E1061" s="7"/>
-      <c r="F1061" s="5"/>
-    </row>
-    <row r="1062" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1062" s="5"/>
-      <c r="B1062" s="6"/>
-      <c r="C1062" s="7"/>
-      <c r="D1062" s="17"/>
-      <c r="E1062" s="7"/>
-      <c r="F1062" s="5"/>
-    </row>
-    <row r="1063" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1063" s="5"/>
-      <c r="B1063" s="6"/>
-      <c r="C1063" s="7"/>
-      <c r="D1063" s="17"/>
-      <c r="E1063" s="7"/>
-      <c r="F1063" s="5"/>
-    </row>
-    <row r="1064" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1064" s="5"/>
-      <c r="B1064" s="6"/>
-      <c r="C1064" s="7"/>
-      <c r="D1064" s="17"/>
-      <c r="E1064" s="7"/>
-      <c r="F1064" s="5"/>
-    </row>
-    <row r="1065" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1065" s="5"/>
-      <c r="B1065" s="6"/>
-      <c r="C1065" s="7"/>
-      <c r="D1065" s="17"/>
-      <c r="E1065" s="7"/>
-      <c r="F1065" s="5"/>
-    </row>
-    <row r="1066" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1066" s="5"/>
-      <c r="B1066" s="6"/>
-      <c r="C1066" s="7"/>
-      <c r="D1066" s="17"/>
-      <c r="E1066" s="7"/>
-      <c r="F1066" s="5"/>
-    </row>
-    <row r="1067" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1067" s="5"/>
-      <c r="B1067" s="6"/>
-      <c r="C1067" s="7"/>
-      <c r="D1067" s="17"/>
-      <c r="E1067" s="7"/>
-      <c r="F1067" s="5"/>
-    </row>
-    <row r="1068" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1068" s="5"/>
-      <c r="B1068" s="6"/>
-      <c r="C1068" s="7"/>
-      <c r="D1068" s="17"/>
-      <c r="E1068" s="7"/>
-      <c r="F1068" s="5"/>
-    </row>
-    <row r="1069" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1069" s="5"/>
-      <c r="B1069" s="6"/>
-      <c r="C1069" s="7"/>
-      <c r="D1069" s="17"/>
-      <c r="E1069" s="7"/>
-      <c r="F1069" s="5"/>
-    </row>
-    <row r="1070" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1070" s="5"/>
-      <c r="B1070" s="6"/>
-      <c r="C1070" s="7"/>
-      <c r="D1070" s="17"/>
-      <c r="E1070" s="7"/>
-      <c r="F1070" s="5"/>
-    </row>
-    <row r="1071" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1071" s="5"/>
-      <c r="B1071" s="6"/>
-      <c r="C1071" s="7"/>
-      <c r="D1071" s="17"/>
-      <c r="E1071" s="7"/>
-      <c r="F1071" s="5"/>
-    </row>
-    <row r="1072" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1072" s="5"/>
-      <c r="B1072" s="6"/>
-      <c r="C1072" s="7"/>
-      <c r="D1072" s="17"/>
-      <c r="E1072" s="7"/>
-      <c r="F1072" s="5"/>
-    </row>
-    <row r="1073" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1073" s="5"/>
-      <c r="B1073" s="6"/>
-      <c r="C1073" s="7"/>
-      <c r="D1073" s="17"/>
-      <c r="E1073" s="7"/>
-      <c r="F1073" s="5"/>
-    </row>
-    <row r="1074" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1074" s="5"/>
-      <c r="B1074" s="6"/>
-      <c r="C1074" s="7"/>
-      <c r="D1074" s="17"/>
-      <c r="E1074" s="7"/>
-      <c r="F1074" s="5"/>
-    </row>
-    <row r="1075" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1075" s="5"/>
-      <c r="B1075" s="6"/>
-      <c r="C1075" s="7"/>
-      <c r="D1075" s="17"/>
-      <c r="E1075" s="7"/>
-      <c r="F1075" s="5"/>
-    </row>
-    <row r="1076" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1076" s="5"/>
-      <c r="B1076" s="6"/>
-      <c r="C1076" s="7"/>
-      <c r="D1076" s="17"/>
-      <c r="E1076" s="7"/>
-      <c r="F1076" s="5"/>
-    </row>
-    <row r="1077" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1077" s="5"/>
-      <c r="B1077" s="6"/>
-      <c r="C1077" s="7"/>
-      <c r="D1077" s="17"/>
-      <c r="E1077" s="7"/>
-      <c r="F1077" s="5"/>
-    </row>
-    <row r="1078" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1078" s="5"/>
-      <c r="B1078" s="6"/>
-      <c r="C1078" s="7"/>
-      <c r="D1078" s="17"/>
-      <c r="E1078" s="7"/>
-      <c r="F1078" s="5"/>
-    </row>
-    <row r="1079" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1079" s="5"/>
-      <c r="B1079" s="6"/>
-      <c r="C1079" s="7"/>
-      <c r="D1079" s="17"/>
-      <c r="E1079" s="7"/>
-      <c r="F1079" s="5"/>
-    </row>
-    <row r="1080" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1080" s="5"/>
-      <c r="B1080" s="6"/>
-      <c r="C1080" s="7"/>
-      <c r="D1080" s="17"/>
-      <c r="E1080" s="7"/>
-      <c r="F1080" s="5"/>
-    </row>
-    <row r="1081" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1081" s="5"/>
-      <c r="B1081" s="6"/>
-      <c r="C1081" s="7"/>
-      <c r="D1081" s="17"/>
-      <c r="E1081" s="7"/>
-      <c r="F1081" s="5"/>
-    </row>
-    <row r="1082" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1082" s="5"/>
-      <c r="B1082" s="6"/>
-      <c r="C1082" s="7"/>
-      <c r="D1082" s="17"/>
-      <c r="E1082" s="7"/>
-      <c r="F1082" s="5"/>
-    </row>
-    <row r="1083" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1083" s="5"/>
-      <c r="B1083" s="6"/>
-      <c r="C1083" s="7"/>
-      <c r="D1083" s="17"/>
-      <c r="E1083" s="7"/>
-      <c r="F1083" s="5"/>
-    </row>
-    <row r="1084" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1084" s="5"/>
-      <c r="B1084" s="6"/>
-      <c r="C1084" s="7"/>
-      <c r="D1084" s="17"/>
-      <c r="E1084" s="7"/>
-      <c r="F1084" s="5"/>
-    </row>
-    <row r="1085" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1085" s="5"/>
-      <c r="B1085" s="6"/>
-      <c r="C1085" s="7"/>
-      <c r="D1085" s="17"/>
-      <c r="E1085" s="7"/>
-      <c r="F1085" s="5"/>
-    </row>
-    <row r="1086" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1086" s="5"/>
-      <c r="B1086" s="6"/>
-      <c r="C1086" s="7"/>
-      <c r="D1086" s="17"/>
-      <c r="E1086" s="7"/>
-      <c r="F1086" s="5"/>
-    </row>
-    <row r="1087" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1087" s="5"/>
-      <c r="B1087" s="6"/>
-      <c r="C1087" s="7"/>
-      <c r="D1087" s="17"/>
-      <c r="E1087" s="7"/>
-      <c r="F1087" s="5"/>
-    </row>
-    <row r="1088" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1088" s="5"/>
-      <c r="B1088" s="6"/>
-      <c r="C1088" s="7"/>
-      <c r="D1088" s="17"/>
-      <c r="E1088" s="7"/>
-      <c r="F1088" s="5"/>
-    </row>
-    <row r="1089" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1089" s="5"/>
-      <c r="B1089" s="6"/>
-      <c r="C1089" s="7"/>
-      <c r="D1089" s="17"/>
-      <c r="E1089" s="7"/>
-      <c r="F1089" s="5"/>
-    </row>
-    <row r="1090" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1090" s="5"/>
-      <c r="B1090" s="6"/>
-      <c r="C1090" s="7"/>
-      <c r="D1090" s="17"/>
-      <c r="E1090" s="7"/>
-      <c r="F1090" s="5"/>
-    </row>
-    <row r="1091" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1091" s="5"/>
-      <c r="B1091" s="6"/>
-      <c r="C1091" s="7"/>
-      <c r="D1091" s="17"/>
-      <c r="E1091" s="7"/>
-      <c r="F1091" s="5"/>
-    </row>
-    <row r="1092" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1092" s="5"/>
-      <c r="B1092" s="6"/>
-      <c r="C1092" s="7"/>
-      <c r="D1092" s="17"/>
-      <c r="E1092" s="7"/>
-      <c r="F1092" s="5"/>
-    </row>
-    <row r="1093" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1093" s="5"/>
-      <c r="B1093" s="6"/>
-      <c r="C1093" s="7"/>
-      <c r="D1093" s="17"/>
-      <c r="E1093" s="7"/>
-      <c r="F1093" s="5"/>
-    </row>
-    <row r="1094" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1094" s="5"/>
-      <c r="B1094" s="6"/>
-      <c r="C1094" s="7"/>
-      <c r="D1094" s="17"/>
-      <c r="E1094" s="7"/>
-      <c r="F1094" s="5"/>
-    </row>
-    <row r="1095" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1095" s="5"/>
-      <c r="B1095" s="6"/>
-      <c r="C1095" s="7"/>
-      <c r="D1095" s="17"/>
-      <c r="E1095" s="7"/>
-      <c r="F1095" s="5"/>
-    </row>
-    <row r="1096" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1096" s="5"/>
-      <c r="B1096" s="6"/>
-      <c r="C1096" s="7"/>
-      <c r="D1096" s="17"/>
-      <c r="E1096" s="7"/>
-      <c r="F1096" s="5"/>
-    </row>
-    <row r="1097" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1097" s="5"/>
-      <c r="B1097" s="6"/>
-      <c r="C1097" s="7"/>
-      <c r="D1097" s="17"/>
-      <c r="E1097" s="7"/>
-      <c r="F1097" s="5"/>
-    </row>
-    <row r="1098" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1098" s="5"/>
-      <c r="B1098" s="6"/>
-      <c r="C1098" s="7"/>
-      <c r="D1098" s="17"/>
-      <c r="E1098" s="7"/>
-      <c r="F1098" s="5"/>
-    </row>
-    <row r="1099" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1099" s="5"/>
-      <c r="B1099" s="6"/>
-      <c r="C1099" s="7"/>
-      <c r="D1099" s="17"/>
-      <c r="E1099" s="7"/>
-      <c r="F1099" s="5"/>
-    </row>
-    <row r="1100" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1100" s="5"/>
-      <c r="B1100" s="6"/>
-      <c r="C1100" s="7"/>
-      <c r="D1100" s="17"/>
-      <c r="E1100" s="7"/>
-      <c r="F1100" s="5"/>
-    </row>
-    <row r="1101" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1101" s="5"/>
-      <c r="B1101" s="6"/>
-      <c r="C1101" s="7"/>
-      <c r="D1101" s="17"/>
-      <c r="E1101" s="7"/>
-      <c r="F1101" s="5"/>
-    </row>
-    <row r="1102" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1102" s="5"/>
-      <c r="B1102" s="6"/>
-      <c r="C1102" s="7"/>
-      <c r="D1102" s="17"/>
-      <c r="E1102" s="7"/>
-      <c r="F1102" s="5"/>
-    </row>
-    <row r="1103" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1103" s="5"/>
-      <c r="B1103" s="6"/>
-      <c r="C1103" s="7"/>
-      <c r="D1103" s="17"/>
-      <c r="E1103" s="7"/>
-      <c r="F1103" s="5"/>
-    </row>
-    <row r="1104" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1104" s="5"/>
-      <c r="B1104" s="6"/>
-      <c r="C1104" s="7"/>
-      <c r="D1104" s="17"/>
-      <c r="E1104" s="7"/>
-      <c r="F1104" s="5"/>
-    </row>
-    <row r="1105" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1105" s="5"/>
-      <c r="B1105" s="6"/>
-      <c r="C1105" s="7"/>
-      <c r="D1105" s="17"/>
-      <c r="E1105" s="7"/>
-      <c r="F1105" s="5"/>
-    </row>
-    <row r="1106" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1106" s="5"/>
-      <c r="B1106" s="6"/>
-      <c r="C1106" s="7"/>
-      <c r="D1106" s="17"/>
-      <c r="E1106" s="7"/>
-      <c r="F1106" s="5"/>
-    </row>
-    <row r="1107" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1107" s="5"/>
-      <c r="B1107" s="6"/>
-      <c r="C1107" s="7"/>
-      <c r="D1107" s="17"/>
-      <c r="E1107" s="7"/>
-      <c r="F1107" s="5"/>
-    </row>
-    <row r="1108" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1108" s="5"/>
-      <c r="B1108" s="6"/>
-      <c r="C1108" s="7"/>
-      <c r="D1108" s="17"/>
-      <c r="E1108" s="7"/>
-      <c r="F1108" s="5"/>
-    </row>
-    <row r="1109" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1109" s="5"/>
-      <c r="B1109" s="6"/>
-      <c r="C1109" s="7"/>
-      <c r="D1109" s="17"/>
-      <c r="E1109" s="7"/>
-      <c r="F1109" s="5"/>
-    </row>
-    <row r="1110" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1110" s="5"/>
-      <c r="B1110" s="6"/>
-      <c r="C1110" s="7"/>
-      <c r="D1110" s="17"/>
-      <c r="E1110" s="7"/>
-      <c r="F1110" s="5"/>
-    </row>
-    <row r="1111" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1111" s="5"/>
-      <c r="B1111" s="6"/>
-      <c r="C1111" s="7"/>
-      <c r="D1111" s="17"/>
-      <c r="E1111" s="7"/>
-      <c r="F1111" s="5"/>
-    </row>
-    <row r="1112" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1112" s="5"/>
-      <c r="B1112" s="6"/>
-      <c r="C1112" s="7"/>
-      <c r="D1112" s="17"/>
-      <c r="E1112" s="7"/>
-      <c r="F1112" s="5"/>
-    </row>
-    <row r="1113" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1113" s="5"/>
-      <c r="B1113" s="6"/>
-      <c r="C1113" s="7"/>
-      <c r="D1113" s="17"/>
-      <c r="E1113" s="7"/>
-      <c r="F1113" s="5"/>
-    </row>
-    <row r="1114" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1114" s="5"/>
-      <c r="B1114" s="6"/>
-      <c r="C1114" s="7"/>
-      <c r="D1114" s="17"/>
-      <c r="E1114" s="7"/>
-      <c r="F1114" s="5"/>
-    </row>
-    <row r="1115" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1115" s="5"/>
-      <c r="B1115" s="6"/>
-      <c r="C1115" s="7"/>
-      <c r="D1115" s="17"/>
-      <c r="E1115" s="7"/>
-      <c r="F1115" s="5"/>
-    </row>
-    <row r="1116" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1116" s="5"/>
-      <c r="B1116" s="6"/>
-      <c r="C1116" s="7"/>
-      <c r="D1116" s="17"/>
-      <c r="E1116" s="7"/>
-      <c r="F1116" s="5"/>
-    </row>
-    <row r="1117" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1117" s="5"/>
-      <c r="B1117" s="6"/>
-      <c r="C1117" s="7"/>
-      <c r="D1117" s="17"/>
-      <c r="E1117" s="7"/>
-      <c r="F1117" s="5"/>
-    </row>
-    <row r="1118" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1118" s="5"/>
-      <c r="B1118" s="6"/>
-      <c r="C1118" s="7"/>
-      <c r="D1118" s="17"/>
-      <c r="E1118" s="7"/>
-      <c r="F1118" s="5"/>
-    </row>
-    <row r="1119" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1119" s="5"/>
-      <c r="B1119" s="6"/>
-      <c r="C1119" s="7"/>
-      <c r="D1119" s="17"/>
-      <c r="E1119" s="7"/>
-      <c r="F1119" s="5"/>
-    </row>
-    <row r="1120" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1120" s="5"/>
-      <c r="B1120" s="6"/>
-      <c r="C1120" s="7"/>
-      <c r="D1120" s="17"/>
-      <c r="E1120" s="7"/>
-      <c r="F1120" s="5"/>
-    </row>
-    <row r="1121" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1121" s="5"/>
-      <c r="B1121" s="6"/>
-      <c r="C1121" s="7"/>
-      <c r="D1121" s="17"/>
-      <c r="E1121" s="7"/>
-      <c r="F1121" s="5"/>
-    </row>
-    <row r="1122" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1122" s="5"/>
-      <c r="B1122" s="6"/>
-      <c r="C1122" s="7"/>
-      <c r="D1122" s="17"/>
-      <c r="E1122" s="7"/>
-      <c r="F1122" s="5"/>
-    </row>
-    <row r="1123" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1123" s="5"/>
-      <c r="B1123" s="6"/>
-      <c r="C1123" s="7"/>
-      <c r="D1123" s="17"/>
-      <c r="E1123" s="7"/>
-      <c r="F1123" s="5"/>
-    </row>
-    <row r="1124" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1124" s="5"/>
-      <c r="B1124" s="6"/>
-      <c r="C1124" s="7"/>
-      <c r="D1124" s="17"/>
-      <c r="E1124" s="7"/>
-      <c r="F1124" s="5"/>
-    </row>
-    <row r="1125" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1125" s="5"/>
-      <c r="B1125" s="6"/>
-      <c r="C1125" s="7"/>
-      <c r="D1125" s="17"/>
-      <c r="E1125" s="7"/>
-      <c r="F1125" s="5"/>
-    </row>
-    <row r="1126" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1126" s="5"/>
-      <c r="B1126" s="6"/>
-      <c r="C1126" s="7"/>
-      <c r="D1126" s="17"/>
-      <c r="E1126" s="7"/>
-      <c r="F1126" s="5"/>
-    </row>
-    <row r="1127" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1127" s="5"/>
-      <c r="B1127" s="6"/>
-      <c r="C1127" s="7"/>
-      <c r="D1127" s="17"/>
-      <c r="E1127" s="7"/>
-      <c r="F1127" s="5"/>
-    </row>
-    <row r="1128" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1128" s="5"/>
-      <c r="B1128" s="6"/>
-      <c r="C1128" s="7"/>
-      <c r="D1128" s="17"/>
-      <c r="E1128" s="7"/>
-      <c r="F1128" s="5"/>
-    </row>
-    <row r="1129" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1129" s="5"/>
-      <c r="B1129" s="6"/>
-      <c r="C1129" s="7"/>
-      <c r="D1129" s="17"/>
-      <c r="E1129" s="7"/>
-      <c r="F1129" s="5"/>
-    </row>
-    <row r="1130" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1130" s="5"/>
-      <c r="B1130" s="6"/>
-      <c r="C1130" s="7"/>
-      <c r="D1130" s="17"/>
-      <c r="E1130" s="7"/>
-      <c r="F1130" s="5"/>
-    </row>
-    <row r="1131" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1131" s="5"/>
-      <c r="B1131" s="6"/>
-      <c r="C1131" s="7"/>
-      <c r="D1131" s="17"/>
-      <c r="E1131" s="7"/>
-      <c r="F1131" s="5"/>
-    </row>
-    <row r="1132" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1132" s="5"/>
-      <c r="B1132" s="6"/>
-      <c r="C1132" s="7"/>
-      <c r="D1132" s="17"/>
-      <c r="E1132" s="7"/>
-      <c r="F1132" s="5"/>
-    </row>
-    <row r="1133" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1133" s="5"/>
-      <c r="B1133" s="6"/>
-      <c r="C1133" s="7"/>
-      <c r="D1133" s="17"/>
-      <c r="E1133" s="7"/>
-      <c r="F1133" s="5"/>
-    </row>
-    <row r="1134" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1134" s="5"/>
-      <c r="B1134" s="6"/>
-      <c r="C1134" s="7"/>
-      <c r="D1134" s="17"/>
-      <c r="E1134" s="7"/>
-      <c r="F1134" s="5"/>
-    </row>
-    <row r="1135" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1135" s="5"/>
-      <c r="B1135" s="6"/>
-      <c r="C1135" s="7"/>
-      <c r="D1135" s="17"/>
-      <c r="E1135" s="7"/>
-      <c r="F1135" s="5"/>
-    </row>
-    <row r="1136" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1136" s="5"/>
-      <c r="B1136" s="6"/>
-      <c r="C1136" s="7"/>
-      <c r="D1136" s="17"/>
-      <c r="E1136" s="7"/>
-      <c r="F1136" s="5"/>
-    </row>
-    <row r="1137" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1137" s="5"/>
-      <c r="B1137" s="6"/>
-      <c r="C1137" s="7"/>
-      <c r="D1137" s="17"/>
-      <c r="E1137" s="7"/>
-      <c r="F1137" s="5"/>
-    </row>
-    <row r="1138" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1138" s="5"/>
-      <c r="B1138" s="6"/>
-      <c r="C1138" s="7"/>
-      <c r="D1138" s="17"/>
-      <c r="E1138" s="7"/>
-      <c r="F1138" s="5"/>
-    </row>
-    <row r="1139" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1139" s="5"/>
-      <c r="B1139" s="6"/>
-      <c r="C1139" s="7"/>
-      <c r="D1139" s="17"/>
-      <c r="E1139" s="7"/>
-      <c r="F1139" s="5"/>
-    </row>
-    <row r="1140" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1140" s="5"/>
-      <c r="B1140" s="6"/>
-      <c r="C1140" s="7"/>
-      <c r="D1140" s="17"/>
-      <c r="E1140" s="7"/>
-      <c r="F1140" s="5"/>
-    </row>
-    <row r="1141" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1141" s="5"/>
-      <c r="B1141" s="6"/>
-      <c r="C1141" s="7"/>
-      <c r="D1141" s="17"/>
-      <c r="E1141" s="7"/>
-      <c r="F1141" s="5"/>
-    </row>
-    <row r="1142" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1142" s="5"/>
-      <c r="B1142" s="6"/>
-      <c r="C1142" s="7"/>
-      <c r="D1142" s="17"/>
-      <c r="E1142" s="7"/>
-      <c r="F1142" s="5"/>
-    </row>
-    <row r="1143" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1143" s="5"/>
-      <c r="B1143" s="6"/>
-      <c r="C1143" s="7"/>
-      <c r="D1143" s="17"/>
-      <c r="E1143" s="7"/>
-      <c r="F1143" s="5"/>
-    </row>
-    <row r="1144" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1144" s="5"/>
-      <c r="B1144" s="6"/>
-      <c r="C1144" s="7"/>
-      <c r="D1144" s="17"/>
-      <c r="E1144" s="7"/>
-      <c r="F1144" s="5"/>
-    </row>
-    <row r="1145" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1145" s="5"/>
-      <c r="B1145" s="6"/>
-      <c r="C1145" s="7"/>
-      <c r="D1145" s="17"/>
-      <c r="E1145" s="7"/>
-      <c r="F1145" s="5"/>
-    </row>
-    <row r="1146" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1146" s="5"/>
-      <c r="B1146" s="6"/>
-      <c r="C1146" s="7"/>
-      <c r="D1146" s="17"/>
-      <c r="E1146" s="7"/>
-      <c r="F1146" s="5"/>
-    </row>
-    <row r="1147" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1147" s="5"/>
-      <c r="B1147" s="6"/>
-      <c r="C1147" s="7"/>
-      <c r="D1147" s="17"/>
-      <c r="E1147" s="7"/>
-      <c r="F1147" s="5"/>
-    </row>
-    <row r="1148" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1148" s="5"/>
-      <c r="B1148" s="6"/>
-      <c r="C1148" s="7"/>
-      <c r="D1148" s="17"/>
-      <c r="E1148" s="7"/>
-      <c r="F1148" s="5"/>
-    </row>
-    <row r="1149" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1149" s="5"/>
-      <c r="B1149" s="6"/>
-      <c r="C1149" s="7"/>
-      <c r="D1149" s="17"/>
-      <c r="E1149" s="7"/>
-      <c r="F1149" s="5"/>
-    </row>
-    <row r="1150" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1150" s="5"/>
-      <c r="B1150" s="6"/>
-      <c r="C1150" s="7"/>
-      <c r="D1150" s="17"/>
-      <c r="E1150" s="7"/>
-      <c r="F1150" s="5"/>
-    </row>
-    <row r="1151" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1151" s="5"/>
-      <c r="B1151" s="6"/>
-      <c r="C1151" s="7"/>
-      <c r="D1151" s="17"/>
-      <c r="E1151" s="7"/>
-      <c r="F1151" s="5"/>
-    </row>
-    <row r="1152" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1152" s="5"/>
-      <c r="B1152" s="6"/>
-      <c r="C1152" s="7"/>
-      <c r="D1152" s="17"/>
-      <c r="E1152" s="7"/>
-      <c r="F1152" s="5"/>
-    </row>
-    <row r="1153" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1153" s="5"/>
-      <c r="B1153" s="6"/>
-      <c r="C1153" s="7"/>
-      <c r="D1153" s="17"/>
-      <c r="E1153" s="7"/>
-      <c r="F1153" s="5"/>
-    </row>
-    <row r="1154" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1154" s="5"/>
-      <c r="B1154" s="6"/>
-      <c r="C1154" s="7"/>
-      <c r="D1154" s="17"/>
-      <c r="E1154" s="7"/>
-      <c r="F1154" s="5"/>
-    </row>
-    <row r="1155" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1155" s="5"/>
-      <c r="B1155" s="6"/>
-      <c r="C1155" s="7"/>
-      <c r="D1155" s="17"/>
-      <c r="E1155" s="7"/>
-      <c r="F1155" s="5"/>
-    </row>
-    <row r="1156" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1156" s="5"/>
-      <c r="B1156" s="6"/>
-      <c r="C1156" s="7"/>
-      <c r="D1156" s="17"/>
-      <c r="E1156" s="7"/>
-      <c r="F1156" s="5"/>
-    </row>
-    <row r="1157" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1157" s="5"/>
-      <c r="B1157" s="6"/>
-      <c r="C1157" s="7"/>
-      <c r="D1157" s="17"/>
-      <c r="E1157" s="7"/>
-      <c r="F1157" s="5"/>
-    </row>
-    <row r="1158" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1158" s="5"/>
-      <c r="B1158" s="6"/>
-      <c r="C1158" s="7"/>
-      <c r="D1158" s="17"/>
-      <c r="E1158" s="7"/>
-      <c r="F1158" s="5"/>
-    </row>
-    <row r="1159" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1159" s="5"/>
-      <c r="B1159" s="6"/>
-      <c r="C1159" s="7"/>
-      <c r="D1159" s="17"/>
-      <c r="E1159" s="7"/>
-      <c r="F1159" s="5"/>
-    </row>
-    <row r="1160" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1160" s="5"/>
-      <c r="B1160" s="6"/>
-      <c r="C1160" s="7"/>
-      <c r="D1160" s="17"/>
-      <c r="E1160" s="7"/>
-      <c r="F1160" s="5"/>
-    </row>
-    <row r="1161" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1161" s="5"/>
-      <c r="B1161" s="6"/>
-      <c r="C1161" s="7"/>
-      <c r="D1161" s="17"/>
-      <c r="E1161" s="7"/>
-      <c r="F1161" s="5"/>
-    </row>
-    <row r="1162" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1162" s="5"/>
-      <c r="B1162" s="6"/>
-      <c r="C1162" s="7"/>
-      <c r="D1162" s="17"/>
-      <c r="E1162" s="7"/>
-      <c r="F1162" s="5"/>
-    </row>
-    <row r="1163" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1163" s="5"/>
-      <c r="B1163" s="6"/>
-      <c r="C1163" s="7"/>
-      <c r="D1163" s="17"/>
-      <c r="E1163" s="7"/>
-      <c r="F1163" s="5"/>
-    </row>
-    <row r="1164" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1164" s="5"/>
-      <c r="B1164" s="6"/>
-      <c r="C1164" s="7"/>
-      <c r="D1164" s="17"/>
-      <c r="E1164" s="7"/>
-      <c r="F1164" s="5"/>
-    </row>
-    <row r="1165" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1165" s="5"/>
-      <c r="B1165" s="6"/>
-      <c r="C1165" s="7"/>
-      <c r="D1165" s="17"/>
-      <c r="E1165" s="7"/>
-      <c r="F1165" s="5"/>
-    </row>
-    <row r="1166" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1166" s="5"/>
-      <c r="B1166" s="6"/>
-      <c r="C1166" s="7"/>
-      <c r="D1166" s="17"/>
-      <c r="E1166" s="7"/>
-      <c r="F1166" s="5"/>
-    </row>
-    <row r="1167" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1167" s="5"/>
-      <c r="B1167" s="6"/>
-      <c r="C1167" s="7"/>
-      <c r="D1167" s="17"/>
-      <c r="E1167" s="7"/>
-      <c r="F1167" s="5"/>
-    </row>
-    <row r="1168" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1168" s="5"/>
-      <c r="B1168" s="6"/>
-      <c r="C1168" s="7"/>
-      <c r="D1168" s="17"/>
-      <c r="E1168" s="7"/>
-      <c r="F1168" s="5"/>
-    </row>
-    <row r="1169" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1169" s="5"/>
-      <c r="B1169" s="6"/>
-      <c r="C1169" s="7"/>
-      <c r="D1169" s="17"/>
-      <c r="E1169" s="7"/>
-      <c r="F1169" s="5"/>
-    </row>
-    <row r="1170" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1170" s="5"/>
-      <c r="B1170" s="6"/>
-      <c r="C1170" s="7"/>
-      <c r="D1170" s="17"/>
-      <c r="E1170" s="7"/>
-      <c r="F1170" s="5"/>
-    </row>
-    <row r="1171" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1171" s="5"/>
-      <c r="B1171" s="6"/>
-      <c r="C1171" s="7"/>
-      <c r="D1171" s="17"/>
-      <c r="E1171" s="7"/>
-      <c r="F1171" s="5"/>
-    </row>
-    <row r="1172" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1172" s="5"/>
-      <c r="B1172" s="6"/>
-      <c r="C1172" s="7"/>
-      <c r="D1172" s="17"/>
-      <c r="E1172" s="7"/>
-      <c r="F1172" s="5"/>
-    </row>
-    <row r="1173" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1173" s="5"/>
-      <c r="B1173" s="6"/>
-      <c r="C1173" s="7"/>
-      <c r="D1173" s="17"/>
-      <c r="E1173" s="7"/>
-      <c r="F1173" s="5"/>
-    </row>
-    <row r="1174" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1174" s="5"/>
-      <c r="B1174" s="6"/>
-      <c r="C1174" s="7"/>
-      <c r="D1174" s="17"/>
-      <c r="E1174" s="7"/>
-      <c r="F1174" s="5"/>
-    </row>
-    <row r="1175" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1175" s="5"/>
-      <c r="B1175" s="6"/>
-      <c r="C1175" s="7"/>
-      <c r="D1175" s="17"/>
-      <c r="E1175" s="7"/>
-      <c r="F1175" s="5"/>
-    </row>
-    <row r="1176" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1176" s="5"/>
-      <c r="B1176" s="6"/>
-      <c r="C1176" s="7"/>
-      <c r="D1176" s="17"/>
-      <c r="E1176" s="7"/>
-      <c r="F1176" s="5"/>
-    </row>
-    <row r="1177" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1177" s="5"/>
-      <c r="B1177" s="6"/>
-      <c r="C1177" s="7"/>
-      <c r="D1177" s="17"/>
-      <c r="E1177" s="7"/>
-      <c r="F1177" s="5"/>
-    </row>
-    <row r="1178" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1178" s="5"/>
-      <c r="B1178" s="6"/>
-      <c r="C1178" s="7"/>
-      <c r="D1178" s="17"/>
-      <c r="E1178" s="7"/>
-      <c r="F1178" s="5"/>
-    </row>
-    <row r="1179" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1179" s="5"/>
-      <c r="B1179" s="6"/>
-      <c r="C1179" s="7"/>
-      <c r="D1179" s="17"/>
-      <c r="E1179" s="7"/>
-      <c r="F1179" s="5"/>
-    </row>
-    <row r="1180" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1180" s="5"/>
-      <c r="B1180" s="6"/>
-      <c r="C1180" s="7"/>
-      <c r="D1180" s="17"/>
-      <c r="E1180" s="7"/>
-      <c r="F1180" s="5"/>
-    </row>
-    <row r="1181" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1181" s="5"/>
-      <c r="B1181" s="6"/>
-      <c r="C1181" s="7"/>
-      <c r="D1181" s="17"/>
-      <c r="E1181" s="7"/>
-      <c r="F1181" s="5"/>
-    </row>
-    <row r="1182" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1182" s="5"/>
-      <c r="B1182" s="6"/>
-      <c r="C1182" s="7"/>
-      <c r="D1182" s="17"/>
-      <c r="E1182" s="7"/>
-      <c r="F1182" s="5"/>
-    </row>
-    <row r="1183" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1183" s="5"/>
-      <c r="B1183" s="6"/>
-      <c r="C1183" s="7"/>
-      <c r="D1183" s="17"/>
-      <c r="E1183" s="7"/>
-      <c r="F1183" s="5"/>
-    </row>
-    <row r="1184" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1184" s="5"/>
-      <c r="B1184" s="6"/>
-      <c r="C1184" s="7"/>
-      <c r="D1184" s="17"/>
-      <c r="E1184" s="7"/>
-      <c r="F1184" s="5"/>
-    </row>
-    <row r="1185" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1185" s="5"/>
-      <c r="B1185" s="6"/>
-      <c r="C1185" s="7"/>
-      <c r="D1185" s="17"/>
-      <c r="E1185" s="7"/>
-      <c r="F1185" s="5"/>
-    </row>
-    <row r="1186" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1186" s="5"/>
-      <c r="B1186" s="6"/>
-      <c r="C1186" s="7"/>
-      <c r="D1186" s="17"/>
-      <c r="E1186" s="7"/>
-      <c r="F1186" s="5"/>
-    </row>
-    <row r="1187" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1187" s="5"/>
-      <c r="B1187" s="6"/>
-      <c r="C1187" s="7"/>
-      <c r="D1187" s="17"/>
-      <c r="E1187" s="7"/>
-      <c r="F1187" s="5"/>
-    </row>
-    <row r="1188" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1188" s="5"/>
-      <c r="B1188" s="6"/>
-      <c r="C1188" s="7"/>
-      <c r="D1188" s="17"/>
-      <c r="E1188" s="7"/>
-      <c r="F1188" s="5"/>
-    </row>
-    <row r="1189" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1189" s="5"/>
-      <c r="B1189" s="6"/>
-      <c r="C1189" s="7"/>
-      <c r="D1189" s="17"/>
-      <c r="E1189" s="7"/>
-      <c r="F1189" s="5"/>
-    </row>
-    <row r="1190" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1190" s="5"/>
-      <c r="B1190" s="6"/>
-      <c r="C1190" s="7"/>
-      <c r="D1190" s="17"/>
-      <c r="E1190" s="7"/>
-      <c r="F1190" s="5"/>
-    </row>
-    <row r="1191" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1191" s="5"/>
-      <c r="B1191" s="6"/>
-      <c r="C1191" s="7"/>
-      <c r="D1191" s="17"/>
-      <c r="E1191" s="7"/>
-      <c r="F1191" s="5"/>
-    </row>
-    <row r="1192" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1192" s="5"/>
-      <c r="B1192" s="6"/>
-      <c r="C1192" s="7"/>
-      <c r="D1192" s="17"/>
-      <c r="E1192" s="7"/>
-      <c r="F1192" s="5"/>
-    </row>
-    <row r="1193" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1193" s="5"/>
-      <c r="B1193" s="6"/>
-      <c r="C1193" s="7"/>
-      <c r="D1193" s="17"/>
-      <c r="E1193" s="7"/>
-      <c r="F1193" s="5"/>
-    </row>
-    <row r="1194" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1194" s="5"/>
-      <c r="B1194" s="6"/>
-      <c r="C1194" s="7"/>
-      <c r="D1194" s="17"/>
-      <c r="E1194" s="7"/>
-      <c r="F1194" s="5"/>
-    </row>
-    <row r="1195" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1195" s="5"/>
-      <c r="B1195" s="6"/>
-      <c r="C1195" s="7"/>
-      <c r="D1195" s="17"/>
-      <c r="E1195" s="7"/>
-      <c r="F1195" s="5"/>
-    </row>
-    <row r="1196" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1196" s="5"/>
-      <c r="B1196" s="6"/>
-      <c r="C1196" s="7"/>
-      <c r="D1196" s="17"/>
-      <c r="E1196" s="7"/>
-      <c r="F1196" s="5"/>
-    </row>
-    <row r="1197" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1197" s="5"/>
-      <c r="B1197" s="6"/>
-      <c r="C1197" s="7"/>
-      <c r="D1197" s="17"/>
-      <c r="E1197" s="7"/>
-      <c r="F1197" s="5"/>
-    </row>
-    <row r="1198" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1198" s="5"/>
-      <c r="B1198" s="6"/>
-      <c r="C1198" s="7"/>
-      <c r="D1198" s="17"/>
-      <c r="E1198" s="7"/>
-      <c r="F1198" s="5"/>
-    </row>
-    <row r="1199" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1199" s="5"/>
-      <c r="B1199" s="6"/>
-      <c r="C1199" s="7"/>
-      <c r="D1199" s="17"/>
-      <c r="E1199" s="7"/>
-      <c r="F1199" s="5"/>
-    </row>
-    <row r="1200" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1200" s="5"/>
-      <c r="B1200" s="6"/>
-      <c r="C1200" s="7"/>
-      <c r="D1200" s="17"/>
-      <c r="E1200" s="7"/>
-      <c r="F1200" s="5"/>
-    </row>
-    <row r="1201" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1201" s="5"/>
-      <c r="B1201" s="6"/>
-      <c r="C1201" s="7"/>
-      <c r="D1201" s="17"/>
-      <c r="E1201" s="7"/>
-      <c r="F1201" s="5"/>
-    </row>
-    <row r="1202" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1202" s="5"/>
-      <c r="B1202" s="6"/>
-      <c r="C1202" s="7"/>
-      <c r="D1202" s="17"/>
-      <c r="E1202" s="7"/>
-      <c r="F1202" s="5"/>
-    </row>
-    <row r="1203" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1203" s="5"/>
-      <c r="B1203" s="6"/>
-      <c r="C1203" s="7"/>
-      <c r="D1203" s="17"/>
-      <c r="E1203" s="7"/>
-      <c r="F1203" s="5"/>
-    </row>
-    <row r="1204" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1204" s="5"/>
-      <c r="B1204" s="6"/>
-      <c r="C1204" s="7"/>
-      <c r="D1204" s="17"/>
-      <c r="E1204" s="7"/>
-      <c r="F1204" s="5"/>
-    </row>
-    <row r="1205" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1205" s="5"/>
-      <c r="B1205" s="6"/>
-      <c r="C1205" s="7"/>
-      <c r="D1205" s="17"/>
-      <c r="E1205" s="7"/>
-      <c r="F1205" s="5"/>
-    </row>
-    <row r="1206" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1206" s="5"/>
-      <c r="B1206" s="6"/>
-      <c r="C1206" s="7"/>
-      <c r="D1206" s="17"/>
-      <c r="E1206" s="7"/>
-      <c r="F1206" s="5"/>
-    </row>
-    <row r="1207" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1207" s="5"/>
-      <c r="B1207" s="6"/>
-      <c r="C1207" s="7"/>
-      <c r="D1207" s="17"/>
-      <c r="E1207" s="7"/>
-      <c r="F1207" s="5"/>
-    </row>
-    <row r="1208" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1208" s="5"/>
-      <c r="B1208" s="6"/>
-      <c r="C1208" s="7"/>
-      <c r="D1208" s="17"/>
-      <c r="E1208" s="7"/>
-      <c r="F1208" s="5"/>
-    </row>
-    <row r="1209" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1209" s="5"/>
-      <c r="B1209" s="6"/>
-      <c r="C1209" s="7"/>
-      <c r="D1209" s="17"/>
-      <c r="E1209" s="7"/>
-      <c r="F1209" s="5"/>
-    </row>
-    <row r="1210" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1210" s="5"/>
-      <c r="B1210" s="6"/>
-      <c r="C1210" s="7"/>
-      <c r="D1210" s="17"/>
-      <c r="E1210" s="7"/>
-      <c r="F1210" s="5"/>
-    </row>
-    <row r="1211" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1211" s="5"/>
-      <c r="B1211" s="6"/>
-      <c r="C1211" s="7"/>
-      <c r="D1211" s="17"/>
-      <c r="E1211" s="7"/>
-      <c r="F1211" s="5"/>
-    </row>
-    <row r="1212" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1212" s="5"/>
-      <c r="B1212" s="6"/>
-      <c r="C1212" s="7"/>
-      <c r="D1212" s="17"/>
-      <c r="E1212" s="7"/>
-      <c r="F1212" s="5"/>
-    </row>
-    <row r="1213" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1213" s="5"/>
-      <c r="B1213" s="6"/>
-      <c r="C1213" s="7"/>
-      <c r="D1213" s="17"/>
-      <c r="E1213" s="7"/>
-      <c r="F1213" s="5"/>
-    </row>
-    <row r="1214" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1214" s="5"/>
-      <c r="B1214" s="6"/>
-      <c r="C1214" s="7"/>
-      <c r="D1214" s="17"/>
-      <c r="E1214" s="7"/>
-      <c r="F1214" s="5"/>
-    </row>
-    <row r="1215" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1215" s="5"/>
-      <c r="B1215" s="6"/>
-      <c r="C1215" s="7"/>
-      <c r="D1215" s="17"/>
-      <c r="E1215" s="7"/>
-      <c r="F1215" s="5"/>
-    </row>
-    <row r="1216" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1216" s="5"/>
-      <c r="B1216" s="6"/>
-      <c r="C1216" s="7"/>
-      <c r="D1216" s="17"/>
-      <c r="E1216" s="7"/>
-      <c r="F1216" s="5"/>
-    </row>
-    <row r="1217" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1217" s="5"/>
-      <c r="B1217" s="6"/>
-      <c r="C1217" s="7"/>
-      <c r="D1217" s="17"/>
-      <c r="E1217" s="7"/>
-      <c r="F1217" s="5"/>
-    </row>
-    <row r="1218" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1218" s="5"/>
-      <c r="B1218" s="6"/>
-      <c r="C1218" s="7"/>
-      <c r="D1218" s="17"/>
-      <c r="E1218" s="7"/>
-      <c r="F1218" s="5"/>
-    </row>
-    <row r="1219" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1219" s="5"/>
-      <c r="B1219" s="6"/>
-      <c r="C1219" s="7"/>
-      <c r="D1219" s="17"/>
-      <c r="E1219" s="7"/>
-      <c r="F1219" s="5"/>
-    </row>
-    <row r="1220" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1220" s="5"/>
-      <c r="B1220" s="6"/>
-      <c r="C1220" s="7"/>
-      <c r="D1220" s="17"/>
-      <c r="E1220" s="7"/>
-      <c r="F1220" s="5"/>
-    </row>
-    <row r="1221" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1221" s="5"/>
-      <c r="B1221" s="6"/>
-      <c r="C1221" s="7"/>
-      <c r="D1221" s="17"/>
-      <c r="E1221" s="7"/>
-      <c r="F1221" s="5"/>
-    </row>
-    <row r="1222" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1222" s="5"/>
-      <c r="B1222" s="6"/>
-      <c r="C1222" s="7"/>
-      <c r="D1222" s="17"/>
-      <c r="E1222" s="7"/>
-      <c r="F1222" s="5"/>
-    </row>
-    <row r="1223" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1223" s="5"/>
-      <c r="B1223" s="6"/>
-      <c r="C1223" s="7"/>
-      <c r="D1223" s="17"/>
-      <c r="E1223" s="7"/>
-      <c r="F1223" s="5"/>
-    </row>
-    <row r="1224" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1224" s="5"/>
-      <c r="B1224" s="6"/>
-      <c r="C1224" s="7"/>
-      <c r="D1224" s="17"/>
-      <c r="E1224" s="7"/>
-      <c r="F1224" s="5"/>
-    </row>
-    <row r="1225" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1225" s="5"/>
-      <c r="B1225" s="6"/>
-      <c r="C1225" s="7"/>
-      <c r="D1225" s="17"/>
-      <c r="E1225" s="7"/>
-      <c r="F1225" s="5"/>
-    </row>
-    <row r="1226" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1226" s="5"/>
-      <c r="B1226" s="6"/>
-      <c r="C1226" s="7"/>
-      <c r="D1226" s="17"/>
-      <c r="E1226" s="7"/>
-      <c r="F1226" s="5"/>
-    </row>
-    <row r="1227" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1227" s="5"/>
-      <c r="B1227" s="6"/>
-      <c r="C1227" s="7"/>
-      <c r="D1227" s="17"/>
-      <c r="E1227" s="7"/>
-      <c r="F1227" s="5"/>
-    </row>
-    <row r="1228" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1228" s="5"/>
-      <c r="B1228" s="6"/>
-      <c r="C1228" s="7"/>
-      <c r="D1228" s="17"/>
-      <c r="E1228" s="7"/>
-      <c r="F1228" s="5"/>
-    </row>
-    <row r="1229" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1229" s="5"/>
-      <c r="B1229" s="6"/>
-      <c r="C1229" s="7"/>
-      <c r="D1229" s="17"/>
-      <c r="E1229" s="7"/>
-      <c r="F1229" s="5"/>
-    </row>
-    <row r="1230" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1230" s="5"/>
-      <c r="B1230" s="6"/>
-      <c r="C1230" s="7"/>
-      <c r="D1230" s="17"/>
-      <c r="E1230" s="7"/>
-      <c r="F1230" s="5"/>
-    </row>
-    <row r="1231" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1231" s="5"/>
-      <c r="B1231" s="6"/>
-      <c r="C1231" s="7"/>
-      <c r="D1231" s="17"/>
-      <c r="E1231" s="7"/>
-      <c r="F1231" s="5"/>
-    </row>
-    <row r="1232" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1232" s="5"/>
-      <c r="B1232" s="6"/>
-      <c r="C1232" s="7"/>
-      <c r="D1232" s="17"/>
-      <c r="E1232" s="7"/>
-      <c r="F1232" s="5"/>
-    </row>
-    <row r="1233" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1233" s="5"/>
-      <c r="B1233" s="6"/>
-      <c r="C1233" s="7"/>
-      <c r="D1233" s="17"/>
-      <c r="E1233" s="7"/>
-      <c r="F1233" s="5"/>
-    </row>
-    <row r="1234" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1234" s="5"/>
-      <c r="B1234" s="6"/>
-      <c r="C1234" s="7"/>
-      <c r="D1234" s="17"/>
-      <c r="E1234" s="7"/>
-      <c r="F1234" s="5"/>
-    </row>
-    <row r="1235" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1235" s="5"/>
-      <c r="B1235" s="6"/>
-      <c r="C1235" s="7"/>
-      <c r="D1235" s="17"/>
-      <c r="E1235" s="7"/>
-      <c r="F1235" s="5"/>
-    </row>
-    <row r="1236" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1236" s="5"/>
-      <c r="B1236" s="6"/>
-      <c r="C1236" s="7"/>
-      <c r="D1236" s="17"/>
-      <c r="E1236" s="7"/>
-      <c r="F1236" s="5"/>
-    </row>
-    <row r="1237" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1237" s="5"/>
-      <c r="B1237" s="6"/>
-      <c r="C1237" s="7"/>
-      <c r="D1237" s="17"/>
-      <c r="E1237" s="7"/>
-      <c r="F1237" s="5"/>
-    </row>
-    <row r="1238" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1238" s="5"/>
-      <c r="B1238" s="6"/>
-      <c r="C1238" s="7"/>
-      <c r="D1238" s="17"/>
-      <c r="E1238" s="7"/>
-      <c r="F1238" s="5"/>
-    </row>
-    <row r="1239" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1239" s="5"/>
-      <c r="B1239" s="6"/>
-      <c r="C1239" s="7"/>
-      <c r="D1239" s="17"/>
-      <c r="E1239" s="7"/>
-      <c r="F1239" s="5"/>
-    </row>
-    <row r="1240" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1240" s="5"/>
-      <c r="B1240" s="6"/>
-      <c r="C1240" s="7"/>
-      <c r="D1240" s="17"/>
-      <c r="E1240" s="7"/>
-      <c r="F1240" s="5"/>
-    </row>
-    <row r="1241" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1241" s="5"/>
-      <c r="B1241" s="6"/>
-      <c r="C1241" s="7"/>
-      <c r="D1241" s="17"/>
-      <c r="E1241" s="7"/>
-      <c r="F1241" s="5"/>
-    </row>
-    <row r="1242" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1242" s="5"/>
-      <c r="B1242" s="6"/>
-      <c r="C1242" s="7"/>
-      <c r="D1242" s="17"/>
-      <c r="E1242" s="7"/>
-      <c r="F1242" s="5"/>
-    </row>
-    <row r="1243" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1243" s="5"/>
-      <c r="B1243" s="6"/>
-      <c r="C1243" s="7"/>
-      <c r="D1243" s="17"/>
-      <c r="E1243" s="7"/>
-      <c r="F1243" s="5"/>
-    </row>
-    <row r="1244" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1244" s="5"/>
-      <c r="B1244" s="6"/>
-      <c r="C1244" s="7"/>
-      <c r="D1244" s="17"/>
-      <c r="E1244" s="7"/>
-      <c r="F1244" s="5"/>
-    </row>
-    <row r="1245" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1245" s="5"/>
-      <c r="B1245" s="6"/>
-      <c r="C1245" s="7"/>
-      <c r="D1245" s="17"/>
-      <c r="E1245" s="7"/>
-      <c r="F1245" s="5"/>
-    </row>
-    <row r="1246" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1246" s="5"/>
-      <c r="B1246" s="6"/>
-      <c r="C1246" s="7"/>
-      <c r="D1246" s="17"/>
-      <c r="E1246" s="7"/>
-      <c r="F1246" s="5"/>
-    </row>
-    <row r="1247" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1247" s="5"/>
-      <c r="B1247" s="6"/>
-      <c r="C1247" s="7"/>
-      <c r="D1247" s="17"/>
-      <c r="E1247" s="7"/>
-      <c r="F1247" s="5"/>
-    </row>
-    <row r="1248" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1248" s="5"/>
-      <c r="B1248" s="6"/>
-      <c r="C1248" s="7"/>
-      <c r="D1248" s="17"/>
-      <c r="E1248" s="7"/>
-      <c r="F1248" s="5"/>
-    </row>
-    <row r="1249" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1249" s="5"/>
-      <c r="B1249" s="6"/>
-      <c r="C1249" s="7"/>
-      <c r="D1249" s="17"/>
-      <c r="E1249" s="7"/>
-      <c r="F1249" s="5"/>
-    </row>
-    <row r="1250" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1250" s="5"/>
-      <c r="B1250" s="6"/>
-      <c r="C1250" s="7"/>
-      <c r="D1250" s="17"/>
-      <c r="E1250" s="7"/>
-      <c r="F1250" s="5"/>
-    </row>
-    <row r="1251" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1251" s="5"/>
-      <c r="B1251" s="6"/>
-      <c r="C1251" s="7"/>
-      <c r="D1251" s="17"/>
-      <c r="E1251" s="7"/>
-      <c r="F1251" s="5"/>
-    </row>
-    <row r="1252" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1252" s="5"/>
-      <c r="B1252" s="6"/>
-      <c r="C1252" s="7"/>
-      <c r="D1252" s="17"/>
-      <c r="E1252" s="7"/>
-      <c r="F1252" s="5"/>
-    </row>
-    <row r="1253" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1253" s="5"/>
-      <c r="B1253" s="6"/>
-      <c r="C1253" s="7"/>
-      <c r="D1253" s="17"/>
-      <c r="E1253" s="7"/>
-      <c r="F1253" s="5"/>
-    </row>
-    <row r="1254" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1254" s="5"/>
-      <c r="B1254" s="6"/>
-      <c r="C1254" s="7"/>
-      <c r="D1254" s="17"/>
-      <c r="E1254" s="7"/>
-      <c r="F1254" s="5"/>
-    </row>
-    <row r="1255" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1255" s="5"/>
-      <c r="B1255" s="6"/>
-      <c r="C1255" s="7"/>
-      <c r="D1255" s="17"/>
-      <c r="E1255" s="7"/>
-      <c r="F1255" s="5"/>
-    </row>
-    <row r="1256" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1256" s="5"/>
-      <c r="B1256" s="6"/>
-      <c r="C1256" s="7"/>
-      <c r="D1256" s="17"/>
-      <c r="E1256" s="7"/>
-      <c r="F1256" s="5"/>
-    </row>
-    <row r="1257" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1257" s="5"/>
-      <c r="B1257" s="6"/>
-      <c r="C1257" s="7"/>
-      <c r="D1257" s="17"/>
-      <c r="E1257" s="7"/>
-      <c r="F1257" s="5"/>
-    </row>
-    <row r="1258" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1258" s="5"/>
-      <c r="B1258" s="6"/>
-      <c r="C1258" s="7"/>
-      <c r="D1258" s="17"/>
-      <c r="E1258" s="7"/>
-      <c r="F1258" s="5"/>
-    </row>
-    <row r="1259" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1259" s="5"/>
-      <c r="B1259" s="6"/>
-      <c r="C1259" s="7"/>
-      <c r="D1259" s="17"/>
-      <c r="E1259" s="7"/>
-      <c r="F1259" s="5"/>
-    </row>
-    <row r="1260" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1260" s="5"/>
-      <c r="B1260" s="6"/>
-      <c r="C1260" s="7"/>
-      <c r="D1260" s="17"/>
-      <c r="E1260" s="7"/>
-      <c r="F1260" s="5"/>
-    </row>
-    <row r="1261" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1261" s="5"/>
-      <c r="B1261" s="6"/>
-      <c r="C1261" s="7"/>
-      <c r="D1261" s="17"/>
-      <c r="E1261" s="7"/>
-      <c r="F1261" s="5"/>
-    </row>
-    <row r="1262" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1262" s="5"/>
-      <c r="B1262" s="6"/>
-      <c r="C1262" s="7"/>
-      <c r="D1262" s="17"/>
-      <c r="E1262" s="7"/>
-      <c r="F1262" s="5"/>
-    </row>
-    <row r="1263" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1263" s="5"/>
-      <c r="B1263" s="6"/>
-      <c r="C1263" s="7"/>
-      <c r="D1263" s="17"/>
-      <c r="E1263" s="7"/>
-      <c r="F1263" s="5"/>
-    </row>
-    <row r="1264" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1264" s="5"/>
-      <c r="B1264" s="6"/>
-      <c r="C1264" s="7"/>
-      <c r="D1264" s="17"/>
-      <c r="E1264" s="7"/>
-      <c r="F1264" s="5"/>
-    </row>
-    <row r="1265" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1265" s="5"/>
-      <c r="B1265" s="6"/>
-      <c r="C1265" s="7"/>
-      <c r="D1265" s="17"/>
-      <c r="E1265" s="7"/>
-      <c r="F1265" s="5"/>
-    </row>
-    <row r="1266" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1266" s="5"/>
-      <c r="B1266" s="6"/>
-      <c r="C1266" s="7"/>
-      <c r="D1266" s="17"/>
-      <c r="E1266" s="7"/>
-      <c r="F1266" s="5"/>
-    </row>
-    <row r="1267" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1267" s="5"/>
-      <c r="B1267" s="6"/>
-      <c r="C1267" s="7"/>
-      <c r="D1267" s="17"/>
-      <c r="E1267" s="7"/>
-      <c r="F1267" s="5"/>
-    </row>
-    <row r="1268" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1268" s="5"/>
-      <c r="B1268" s="6"/>
-      <c r="C1268" s="7"/>
-      <c r="D1268" s="17"/>
-      <c r="E1268" s="7"/>
-      <c r="F1268" s="5"/>
-    </row>
-    <row r="1269" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1269" s="5"/>
-      <c r="B1269" s="6"/>
-      <c r="C1269" s="7"/>
-      <c r="D1269" s="17"/>
-      <c r="E1269" s="7"/>
-      <c r="F1269" s="5"/>
-    </row>
-    <row r="1270" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1270" s="5"/>
-      <c r="B1270" s="6"/>
-      <c r="C1270" s="7"/>
-      <c r="D1270" s="17"/>
-      <c r="E1270" s="7"/>
-      <c r="F1270" s="5"/>
-    </row>
-    <row r="1271" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1271" s="5"/>
-      <c r="B1271" s="6"/>
-      <c r="C1271" s="7"/>
-      <c r="D1271" s="17"/>
-      <c r="E1271" s="7"/>
-      <c r="F1271" s="5"/>
-    </row>
-    <row r="1272" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1272" s="5"/>
-      <c r="B1272" s="6"/>
-      <c r="C1272" s="7"/>
-      <c r="D1272" s="17"/>
-      <c r="E1272" s="7"/>
-      <c r="F1272" s="5"/>
-    </row>
-    <row r="1273" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1273" s="5"/>
-      <c r="B1273" s="6"/>
-      <c r="C1273" s="7"/>
-      <c r="D1273" s="17"/>
-      <c r="E1273" s="7"/>
-      <c r="F1273" s="5"/>
-    </row>
-    <row r="1274" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1274" s="5"/>
-      <c r="B1274" s="6"/>
-      <c r="C1274" s="7"/>
-      <c r="D1274" s="17"/>
-      <c r="E1274" s="7"/>
-      <c r="F1274" s="5"/>
-    </row>
-    <row r="1275" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1275" s="5"/>
-      <c r="B1275" s="6"/>
-      <c r="C1275" s="7"/>
-      <c r="D1275" s="17"/>
-      <c r="E1275" s="7"/>
-      <c r="F1275" s="5"/>
-    </row>
-    <row r="1276" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1276" s="5"/>
-      <c r="B1276" s="6"/>
-      <c r="C1276" s="7"/>
-      <c r="D1276" s="17"/>
-      <c r="E1276" s="7"/>
-      <c r="F1276" s="5"/>
-    </row>
-    <row r="1277" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1277" s="5"/>
-      <c r="B1277" s="6"/>
-      <c r="C1277" s="7"/>
-      <c r="D1277" s="17"/>
-      <c r="E1277" s="7"/>
-      <c r="F1277" s="5"/>
-    </row>
-    <row r="1278" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1278" s="5"/>
-      <c r="B1278" s="6"/>
-      <c r="C1278" s="7"/>
-      <c r="D1278" s="17"/>
-      <c r="E1278" s="7"/>
-      <c r="F1278" s="5"/>
-    </row>
-    <row r="1279" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1279" s="5"/>
-      <c r="B1279" s="6"/>
-      <c r="C1279" s="7"/>
-      <c r="D1279" s="17"/>
-      <c r="E1279" s="7"/>
-      <c r="F1279" s="5"/>
-    </row>
-    <row r="1280" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1280" s="5"/>
-      <c r="B1280" s="6"/>
-      <c r="C1280" s="7"/>
-      <c r="D1280" s="17"/>
-      <c r="E1280" s="7"/>
-      <c r="F1280" s="5"/>
-    </row>
-    <row r="1281" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1281" s="5"/>
-      <c r="B1281" s="6"/>
-      <c r="C1281" s="7"/>
-      <c r="D1281" s="17"/>
-      <c r="E1281" s="7"/>
-      <c r="F1281" s="5"/>
-    </row>
-    <row r="1282" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1282" s="5"/>
-      <c r="B1282" s="6"/>
-      <c r="C1282" s="7"/>
-      <c r="D1282" s="17"/>
-      <c r="E1282" s="7"/>
-      <c r="F1282" s="5"/>
-    </row>
-    <row r="1283" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1283" s="5"/>
-      <c r="B1283" s="6"/>
-      <c r="C1283" s="7"/>
-      <c r="D1283" s="17"/>
-      <c r="E1283" s="7"/>
-      <c r="F1283" s="5"/>
-    </row>
-    <row r="1284" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1284" s="5"/>
-      <c r="B1284" s="6"/>
-      <c r="C1284" s="7"/>
-      <c r="D1284" s="17"/>
-      <c r="E1284" s="7"/>
-      <c r="F1284" s="5"/>
-    </row>
-    <row r="1285" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1285" s="5"/>
-      <c r="B1285" s="6"/>
-      <c r="C1285" s="7"/>
-      <c r="D1285" s="17"/>
-      <c r="E1285" s="7"/>
-      <c r="F1285" s="5"/>
-    </row>
-    <row r="1286" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1286" s="5"/>
-      <c r="B1286" s="6"/>
-      <c r="C1286" s="7"/>
-      <c r="D1286" s="17"/>
-      <c r="E1286" s="7"/>
-      <c r="F1286" s="5"/>
-    </row>
-    <row r="1287" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1287" s="5"/>
-      <c r="B1287" s="6"/>
-      <c r="C1287" s="7"/>
-      <c r="D1287" s="17"/>
-      <c r="E1287" s="7"/>
-      <c r="F1287" s="5"/>
-    </row>
-    <row r="1288" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1288" s="5"/>
-      <c r="B1288" s="6"/>
-      <c r="C1288" s="7"/>
-      <c r="D1288" s="17"/>
-      <c r="E1288" s="7"/>
-      <c r="F1288" s="5"/>
-    </row>
-    <row r="1289" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1289" s="5"/>
-      <c r="B1289" s="6"/>
-      <c r="C1289" s="7"/>
-      <c r="D1289" s="17"/>
-      <c r="E1289" s="7"/>
-      <c r="F1289" s="5"/>
-    </row>
-    <row r="1290" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1290" s="5"/>
-      <c r="B1290" s="6"/>
-      <c r="C1290" s="7"/>
-      <c r="D1290" s="17"/>
-      <c r="E1290" s="7"/>
-      <c r="F1290" s="5"/>
-    </row>
-    <row r="1291" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1291" s="5"/>
-      <c r="B1291" s="6"/>
-      <c r="C1291" s="7"/>
-      <c r="D1291" s="17"/>
-      <c r="E1291" s="7"/>
-      <c r="F1291" s="5"/>
-    </row>
-    <row r="1292" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1292" s="5"/>
-      <c r="B1292" s="6"/>
-      <c r="C1292" s="7"/>
-      <c r="D1292" s="17"/>
-      <c r="E1292" s="7"/>
-      <c r="F1292" s="5"/>
-    </row>
-    <row r="1293" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1293" s="5"/>
-      <c r="B1293" s="6"/>
-      <c r="C1293" s="7"/>
-      <c r="D1293" s="17"/>
-      <c r="E1293" s="7"/>
-      <c r="F1293" s="5"/>
-    </row>
-    <row r="1294" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1294" s="5"/>
-      <c r="B1294" s="6"/>
-      <c r="C1294" s="7"/>
-      <c r="D1294" s="17"/>
-      <c r="E1294" s="7"/>
-      <c r="F1294" s="5"/>
-    </row>
-    <row r="1295" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1295" s="5"/>
-      <c r="B1295" s="6"/>
-      <c r="C1295" s="7"/>
-      <c r="D1295" s="17"/>
-      <c r="E1295" s="7"/>
-      <c r="F1295" s="5"/>
-    </row>
-    <row r="1296" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1296" s="5"/>
-      <c r="B1296" s="6"/>
-      <c r="C1296" s="7"/>
-      <c r="D1296" s="17"/>
-      <c r="E1296" s="7"/>
-      <c r="F1296" s="5"/>
-    </row>
-    <row r="1297" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1297" s="5"/>
-      <c r="B1297" s="6"/>
-      <c r="C1297" s="7"/>
-      <c r="D1297" s="17"/>
-      <c r="E1297" s="7"/>
-      <c r="F1297" s="5"/>
-    </row>
-    <row r="1298" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1298" s="5"/>
-      <c r="B1298" s="6"/>
-      <c r="C1298" s="7"/>
-      <c r="D1298" s="17"/>
-      <c r="E1298" s="7"/>
-      <c r="F1298" s="5"/>
-    </row>
-    <row r="1299" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1299" s="5"/>
-      <c r="B1299" s="6"/>
-      <c r="C1299" s="7"/>
-      <c r="D1299" s="17"/>
-      <c r="E1299" s="7"/>
-      <c r="F1299" s="5"/>
-    </row>
-    <row r="1300" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1300" s="5"/>
-      <c r="B1300" s="6"/>
-      <c r="C1300" s="7"/>
-      <c r="D1300" s="17"/>
-      <c r="E1300" s="7"/>
-      <c r="F1300" s="5"/>
-    </row>
-    <row r="1301" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1301" s="5"/>
-      <c r="B1301" s="6"/>
-      <c r="C1301" s="7"/>
-      <c r="D1301" s="17"/>
-      <c r="E1301" s="7"/>
-      <c r="F1301" s="5"/>
-    </row>
-    <row r="1302" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1302" s="5"/>
-      <c r="B1302" s="6"/>
-      <c r="C1302" s="7"/>
-      <c r="D1302" s="17"/>
-      <c r="E1302" s="7"/>
-      <c r="F1302" s="5"/>
-    </row>
-    <row r="1303" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1303" s="5"/>
-      <c r="B1303" s="6"/>
-      <c r="C1303" s="7"/>
-      <c r="D1303" s="17"/>
-      <c r="E1303" s="7"/>
-      <c r="F1303" s="5"/>
-    </row>
-    <row r="1304" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1304" s="5"/>
-      <c r="B1304" s="6"/>
-      <c r="C1304" s="7"/>
-      <c r="D1304" s="17"/>
-      <c r="E1304" s="7"/>
-      <c r="F1304" s="5"/>
-    </row>
-    <row r="1305" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1305" s="5"/>
-      <c r="B1305" s="6"/>
-      <c r="C1305" s="7"/>
-      <c r="D1305" s="17"/>
-      <c r="E1305" s="7"/>
-      <c r="F1305" s="5"/>
-    </row>
-    <row r="1306" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1306" s="5"/>
-      <c r="B1306" s="6"/>
-      <c r="C1306" s="7"/>
-      <c r="D1306" s="17"/>
-      <c r="E1306" s="7"/>
-      <c r="F1306" s="5"/>
-    </row>
-    <row r="1307" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1307" s="5"/>
-      <c r="B1307" s="6"/>
-      <c r="C1307" s="7"/>
-      <c r="D1307" s="17"/>
-      <c r="E1307" s="7"/>
-      <c r="F1307" s="5"/>
-    </row>
-    <row r="1308" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1308" s="5"/>
-      <c r="B1308" s="6"/>
-      <c r="C1308" s="7"/>
-      <c r="D1308" s="17"/>
-      <c r="E1308" s="7"/>
-      <c r="F1308" s="5"/>
-    </row>
-    <row r="1309" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1309" s="5"/>
-      <c r="B1309" s="6"/>
-      <c r="C1309" s="7"/>
-      <c r="D1309" s="17"/>
-      <c r="E1309" s="7"/>
-      <c r="F1309" s="5"/>
-    </row>
-    <row r="1310" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1310" s="5"/>
-      <c r="B1310" s="6"/>
-      <c r="C1310" s="7"/>
-      <c r="D1310" s="17"/>
-      <c r="E1310" s="7"/>
-      <c r="F1310" s="5"/>
-    </row>
-    <row r="1311" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1311" s="5"/>
-      <c r="B1311" s="6"/>
-      <c r="C1311" s="7"/>
-      <c r="D1311" s="17"/>
-      <c r="E1311" s="7"/>
-      <c r="F1311" s="5"/>
-    </row>
-    <row r="1312" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1312" s="5"/>
-      <c r="B1312" s="6"/>
-      <c r="C1312" s="7"/>
-      <c r="D1312" s="17"/>
-      <c r="E1312" s="7"/>
-      <c r="F1312" s="5"/>
-    </row>
-    <row r="1313" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1313" s="5"/>
-      <c r="B1313" s="6"/>
-      <c r="C1313" s="7"/>
-      <c r="D1313" s="17"/>
-      <c r="E1313" s="7"/>
-      <c r="F1313" s="5"/>
-    </row>
-    <row r="1314" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1314" s="5"/>
-      <c r="B1314" s="6"/>
-      <c r="C1314" s="7"/>
-      <c r="D1314" s="17"/>
-      <c r="E1314" s="7"/>
-      <c r="F1314" s="5"/>
-    </row>
-    <row r="1315" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1315" s="5"/>
-      <c r="B1315" s="6"/>
-      <c r="C1315" s="7"/>
-      <c r="D1315" s="17"/>
-      <c r="E1315" s="7"/>
-      <c r="F1315" s="5"/>
-    </row>
-    <row r="1316" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1316" s="5"/>
-      <c r="B1316" s="6"/>
-      <c r="C1316" s="7"/>
-      <c r="D1316" s="17"/>
-      <c r="E1316" s="7"/>
-      <c r="F1316" s="5"/>
-    </row>
-    <row r="1317" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1317" s="5"/>
-      <c r="B1317" s="6"/>
-      <c r="C1317" s="7"/>
-      <c r="D1317" s="17"/>
-      <c r="E1317" s="7"/>
-      <c r="F1317" s="5"/>
-    </row>
-    <row r="1318" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1318" s="5"/>
-      <c r="B1318" s="6"/>
-      <c r="C1318" s="7"/>
-      <c r="D1318" s="17"/>
-      <c r="E1318" s="7"/>
-      <c r="F1318" s="5"/>
-    </row>
-    <row r="1319" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1319" s="5"/>
-      <c r="B1319" s="6"/>
-      <c r="C1319" s="7"/>
-      <c r="D1319" s="17"/>
-      <c r="E1319" s="7"/>
-      <c r="F1319" s="5"/>
-    </row>
-    <row r="1320" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1320" s="5"/>
-      <c r="B1320" s="6"/>
-      <c r="C1320" s="7"/>
-      <c r="D1320" s="17"/>
-      <c r="E1320" s="7"/>
-      <c r="F1320" s="5"/>
-    </row>
-    <row r="1321" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1321" s="5"/>
-      <c r="B1321" s="6"/>
-      <c r="C1321" s="7"/>
-      <c r="D1321" s="17"/>
-      <c r="E1321" s="7"/>
-      <c r="F1321" s="5"/>
-    </row>
-    <row r="1322" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1322" s="5"/>
-      <c r="B1322" s="6"/>
-      <c r="C1322" s="7"/>
-      <c r="D1322" s="17"/>
-      <c r="E1322" s="7"/>
-      <c r="F1322" s="5"/>
-    </row>
-    <row r="1323" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1323" s="5"/>
-      <c r="B1323" s="6"/>
-      <c r="C1323" s="7"/>
-      <c r="D1323" s="17"/>
-      <c r="E1323" s="7"/>
-      <c r="F1323" s="5"/>
-    </row>
-    <row r="1324" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1324" s="5"/>
-      <c r="B1324" s="6"/>
-      <c r="C1324" s="7"/>
-      <c r="D1324" s="17"/>
-      <c r="E1324" s="7"/>
-      <c r="F1324" s="5"/>
-    </row>
-    <row r="1325" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1325" s="5"/>
-      <c r="B1325" s="6"/>
-      <c r="C1325" s="7"/>
-      <c r="D1325" s="17"/>
-      <c r="E1325" s="7"/>
-      <c r="F1325" s="5"/>
-    </row>
-    <row r="1326" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1326" s="5"/>
-      <c r="B1326" s="6"/>
-      <c r="C1326" s="7"/>
-      <c r="D1326" s="17"/>
-      <c r="E1326" s="7"/>
-      <c r="F1326" s="5"/>
-    </row>
-    <row r="1327" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1327" s="5"/>
-      <c r="B1327" s="6"/>
-      <c r="C1327" s="7"/>
-      <c r="D1327" s="17"/>
-      <c r="E1327" s="7"/>
-      <c r="F1327" s="5"/>
-    </row>
-    <row r="1328" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1328" s="5"/>
-      <c r="B1328" s="6"/>
-      <c r="C1328" s="7"/>
-      <c r="D1328" s="17"/>
-      <c r="E1328" s="7"/>
-      <c r="F1328" s="5"/>
-    </row>
-    <row r="1329" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1329" s="5"/>
-      <c r="B1329" s="6"/>
-      <c r="C1329" s="7"/>
-      <c r="D1329" s="17"/>
-      <c r="E1329" s="7"/>
-      <c r="F1329" s="5"/>
-    </row>
-    <row r="1330" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1330" s="5"/>
-      <c r="B1330" s="6"/>
-      <c r="C1330" s="7"/>
-      <c r="D1330" s="17"/>
-      <c r="E1330" s="7"/>
-      <c r="F1330" s="5"/>
-    </row>
-    <row r="1331" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1331" s="5"/>
-      <c r="B1331" s="6"/>
-      <c r="C1331" s="7"/>
-      <c r="D1331" s="17"/>
-      <c r="E1331" s="7"/>
-      <c r="F1331" s="5"/>
-    </row>
-    <row r="1332" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1332" s="5"/>
-      <c r="B1332" s="6"/>
-      <c r="C1332" s="7"/>
-      <c r="D1332" s="17"/>
-      <c r="E1332" s="7"/>
-      <c r="F1332" s="5"/>
-    </row>
-    <row r="1333" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1333" s="5"/>
-      <c r="B1333" s="6"/>
-      <c r="C1333" s="7"/>
-      <c r="D1333" s="17"/>
-      <c r="E1333" s="7"/>
-      <c r="F1333" s="5"/>
-    </row>
-    <row r="1334" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1334" s="5"/>
-      <c r="B1334" s="6"/>
-      <c r="C1334" s="7"/>
-      <c r="D1334" s="17"/>
-      <c r="E1334" s="7"/>
-      <c r="F1334" s="5"/>
-    </row>
-    <row r="1335" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1335" s="5"/>
-      <c r="B1335" s="6"/>
-      <c r="C1335" s="7"/>
-      <c r="D1335" s="17"/>
-      <c r="E1335" s="7"/>
-      <c r="F1335" s="5"/>
-    </row>
-    <row r="1336" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1336" s="5"/>
-      <c r="B1336" s="6"/>
-      <c r="C1336" s="7"/>
-      <c r="D1336" s="17"/>
-      <c r="E1336" s="7"/>
-      <c r="F1336" s="5"/>
-    </row>
-    <row r="1337" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1337" s="5"/>
-      <c r="B1337" s="6"/>
-      <c r="C1337" s="7"/>
-      <c r="D1337" s="17"/>
-      <c r="E1337" s="7"/>
-      <c r="F1337" s="5"/>
-    </row>
-    <row r="1338" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1338" s="5"/>
-      <c r="B1338" s="6"/>
-      <c r="C1338" s="7"/>
-      <c r="D1338" s="17"/>
-      <c r="E1338" s="7"/>
-      <c r="F1338" s="5"/>
-    </row>
-    <row r="1339" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1339" s="5"/>
-      <c r="B1339" s="6"/>
-      <c r="C1339" s="7"/>
-      <c r="D1339" s="17"/>
-      <c r="E1339" s="7"/>
-      <c r="F1339" s="5"/>
-    </row>
-    <row r="1340" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1340" s="5"/>
-      <c r="B1340" s="6"/>
-      <c r="C1340" s="7"/>
-      <c r="D1340" s="17"/>
-      <c r="E1340" s="7"/>
-      <c r="F1340" s="5"/>
-    </row>
-    <row r="1341" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1341" s="5"/>
-      <c r="B1341" s="6"/>
-      <c r="C1341" s="7"/>
-      <c r="D1341" s="17"/>
-      <c r="E1341" s="7"/>
-      <c r="F1341" s="5"/>
-    </row>
-    <row r="1342" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1342" s="5"/>
-      <c r="B1342" s="6"/>
-      <c r="C1342" s="7"/>
-      <c r="D1342" s="17"/>
-      <c r="E1342" s="7"/>
-      <c r="F1342" s="5"/>
-    </row>
-    <row r="1343" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1343" s="5"/>
-      <c r="B1343" s="6"/>
-      <c r="C1343" s="7"/>
-      <c r="D1343" s="17"/>
-      <c r="E1343" s="7"/>
-      <c r="F1343" s="5"/>
-    </row>
-    <row r="1344" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1344" s="5"/>
-      <c r="B1344" s="6"/>
-      <c r="C1344" s="7"/>
-      <c r="D1344" s="17"/>
-      <c r="E1344" s="7"/>
-      <c r="F1344" s="5"/>
-    </row>
-    <row r="1345" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1345" s="5"/>
-      <c r="B1345" s="6"/>
-      <c r="C1345" s="7"/>
-      <c r="D1345" s="17"/>
-      <c r="E1345" s="7"/>
-      <c r="F1345" s="5"/>
-    </row>
-    <row r="1346" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1346" s="5"/>
-      <c r="B1346" s="6"/>
-      <c r="C1346" s="7"/>
-      <c r="D1346" s="17"/>
-      <c r="E1346" s="7"/>
-      <c r="F1346" s="5"/>
-    </row>
-    <row r="1347" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1347" s="5"/>
-      <c r="B1347" s="6"/>
-      <c r="C1347" s="7"/>
-      <c r="D1347" s="17"/>
-      <c r="E1347" s="7"/>
-      <c r="F1347" s="5"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F709" xr:uid="{41043218-9C94-410C-9ADE-FF0FB1887CD8}"/>
@@ -28995,7 +23932,7 @@
           <x14:formula1>
             <xm:f>technology_type!$A$2:$A$98</xm:f>
           </x14:formula1>
-          <xm:sqref>F2:F1347</xm:sqref>
+          <xm:sqref>F2:F715</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -30037,7 +24974,7 @@
       </c>
     </row>
     <row r="94" spans="1:3" ht="45" x14ac:dyDescent="0.25">
-      <c r="A94" s="22">
+      <c r="A94" s="21">
         <v>93</v>
       </c>
       <c r="B94" s="3" t="s">
@@ -30048,7 +24985,7 @@
       </c>
     </row>
     <row r="95" spans="1:3" ht="45" x14ac:dyDescent="0.25">
-      <c r="A95" s="22">
+      <c r="A95" s="21">
         <v>94</v>
       </c>
       <c r="B95" s="3" t="s">
@@ -30059,7 +24996,7 @@
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A96" s="22">
+      <c r="A96" s="21">
         <v>95</v>
       </c>
       <c r="B96" s="3" t="s">
@@ -30070,7 +25007,7 @@
       </c>
     </row>
     <row r="97" spans="1:3" ht="45" x14ac:dyDescent="0.25">
-      <c r="A97" s="22">
+      <c r="A97" s="21">
         <v>96</v>
       </c>
       <c r="B97" s="3" t="s">
@@ -30081,7 +25018,7 @@
       </c>
     </row>
     <row r="98" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A98" s="22">
+      <c r="A98" s="21">
         <v>97</v>
       </c>
       <c r="B98" s="3" t="s">

--- a/2. Components/2.1. Cloud Component/2.1.1. Autonomous_Database/3. autonomous_db_owner (wip)/4. dml/1. skill_area [13-17,5]/15. technology.xlsx
+++ b/2. Components/2.1. Cloud Component/2.1.1. Autonomous_Database/3. autonomous_db_owner (wip)/4. dml/1. skill_area [13-17,5]/15. technology.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github_projects\Tech_Hunt_Engine\2. Components\2.1. Cloud Component\2.1.1. Autonomous_Database\3. autonomous_db_owner (wip)\4. dml\1. skill_area [13-17,5]\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5DBBB51-3E7D-4944-A928-931C6482736F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD2CAA65-5BFF-46AA-9239-9414C80F7188}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
